--- a/Result/checksun_type/玻璃基板.xlsx
+++ b/Result/checksun_type/玻璃基板.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>24.78</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>26.38</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>26.78</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>26.38</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>26.78</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>3298659.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>3409647.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>3409647.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>4333083.4</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>10178782.26</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>10178782.26</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-1446674.246380107</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>3298659</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>3298659.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>24.67</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>26.62</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>26.79</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>26.62</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>26.79</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>4541875.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>3888772.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>3888772.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>4411562.6</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>10182869.32</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>10182869.32</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-1532437.84859698</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>4541875</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>4541875.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>24.85</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>26.86</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>26.79</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>26.86</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>26.79</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>1903538.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>3963383.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>3963383.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>5318222.8</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>10129541.2</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>10129541.2</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-1733429.071456906</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>1903538</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>1903538.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>25.15</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>27.22</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>26.8</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>27.22</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>26.8</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>2962769.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>5056298.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>5056298.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>5511802.7</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>10116244.0</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>10116244</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-1675972.244419054</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>2962769</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>2962769.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>27.43</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>26.81</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>27.43</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>26.81</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>4341397.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>5404572.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>5404572</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>5443936.9</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>10090356.22</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>10090356.22</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-1647523.947064298</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>4341397</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>4341397.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>25.9</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>27.58</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>26.81</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>27.58</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>26.81</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>5694285.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>5256519.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>5256519.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>5382212.9</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>10042035.4</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>10042035.4</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-1695753.524162351</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>5694285</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>5694285.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>26.46</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>27.77</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>26.82</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>27.77</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>26.82</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>4914929.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>4934352.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>4934352.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>5195209.4</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>9975089.7</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>9975089.699999999</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-1849042.579868057</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>4914929</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>4914929.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>26.72</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>27.84</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>26.81</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>27.84</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>26.81</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>7368112.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>6673062.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>6673062</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>5266881.5</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>9924938.88</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>9924938.880000001</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-1918487.281595205</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>7368112</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>7368112.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>26.86</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>27.87</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>26.79</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>27.87</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>26.79</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>4704137.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>5967307.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>5967307</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>5157190.6</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>9855538.88</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>9855538.880000001</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-2212017.631148446</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>4704137</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>4704137.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>27.03</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>27.86</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>26.76</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>27.86</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>26.76</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>3601133.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>5483301.8</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>5483301.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>5729175.2</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>9863427.64</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>9863427.640000001</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-2266920.179397777</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>3601133</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>3601133.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>27.06</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>27.82</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>26.74</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>27.82</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>26.74</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>4083451.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>5507906.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>5507906.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>6865809.6</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>10002101.52</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>10002101.52</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-2146211.956204042</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>4083451</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>4083451.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>13.32</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>13.83</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>14.41</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>14.41</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>1213.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>527.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>527.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>585.7</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>567.68</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>567.6799999999999</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>21.00387133963898</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>1213</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>1213.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>13.37</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>13.86</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>14.48</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>14.48</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>206.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>340.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>340.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>497.7</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>555.26</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>555.26</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-46.08158973532466</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>206</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>206.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>13.43</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>13.9</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>14.55</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>14.55</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>272.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>332.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>332</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>647.5</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>577.06</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>577.0599999999999</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-32.37933449472541</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>272</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>272.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>13.62</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>13.95</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>14.64</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>14.64</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>374.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>340.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>340.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>625.9</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>605.18</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>605.1799999999999</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-18.71970791905761</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>374</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>374.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>13.81</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>13.98</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>14.71</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>14.71</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>573.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>381.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>381</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>597.1</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>630.02</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>630.02</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-9.46596609956589</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>573</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>573.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>14.03</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>14.79</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>14.79</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>276.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>643.8</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>643.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>572.3</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>643.84</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>643.84</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-17.22969328245046</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>276</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>276.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>14.17</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>14.87</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>14.87</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>165.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>655.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>655.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>563.0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>675.0</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>675</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>4.116042644944969</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>165</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>165.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>14.25</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>14.02</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>14.94</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>14.94</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>314.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>963.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>963</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>565.3</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>734.12</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>734.12</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>46.35580673247603</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>314</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>314.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>14.22</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>14.02</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>15.03</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>15.03</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>577.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>911.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>911.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>580.4</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>762.26</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>762.26</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>89.0784766170749</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>577</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>577.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,21 +9657,17 @@
           <t>14.13</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>14.03</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
+      <c r="AM22" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="AO22" t="inlineStr">
         <is>
           <t>15.11</t>
         </is>
       </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>15.11</t>
-        </is>
-      </c>
       <c r="AP22" t="inlineStr">
         <is>
           <t>40.16</t>
@@ -9832,20 +9708,16 @@
           <t>1887.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>813.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>813.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>561.2</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>794.04</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>794.04</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>118.7509165730348</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>1887</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>1887.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>13.95</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>15.19</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>15.19</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>333.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>500.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>500.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>432.9</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>783.6</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>783.6</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>16.54186948965486</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>333</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>333.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>34.41</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>36.18</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>38.94</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>36.18</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>38.94</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>35345556.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>37074921.8</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>37074921.8</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>53345322.1</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>245778298.12</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>245778298.12</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-20878828.60415238</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>35345556</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>35345556.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>34.16</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>36.33</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>39.0</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>36.33</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>39</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>29401532.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>39796395.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>39796395.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>58228190.4</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>247556548.26</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>247556548.26</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-21938484.35346347</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>29401532</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>29401532.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>34.11999999999999</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>36.49</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>39.06</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>36.49</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>39.06</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>38774066.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>49474507.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>49474507.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>66401056.1</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>249662887.18</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>249662887.18</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-22031901.26842704</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>38774066</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>38774066.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>34.33</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>36.71</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>39.14</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>36.71</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>39.14</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>46179132.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>60997217.6</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>60997217.6</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>84286762.5</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>254822433.06</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>254822433.06</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-22382700.45878832</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>46179132</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>46179132.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>34.76</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>36.88</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>39.24</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>36.88</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>39.24</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>35674323.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>63924345.6</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>63924345.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>94556424.4</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>256700200.08</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>256700200.08</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-22877859.92863344</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>35674323</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>35674323.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>35.22000000000001</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>37.06</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>39.33</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>37.06</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>39.33</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>48952923.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>69615722.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>69615722.40000001</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>110580229.2</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>258176781.58</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>258176781.58</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-21642648.9238181</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>48952923</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>48952923.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>36.01000000000001</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>37.29</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>39.43</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>37.29</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>39.43</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>77792094.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>76659985.6</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>76659985.59999999</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>113715310.1</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>261926998.4</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>261926998.4</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-20527817.16965982</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>77792094</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>77792094.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>36.59</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>37.52</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>39.54</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>37.52</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>39.54</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>96387616.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>83327604.6</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>83327604.59999999</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>112354225.4</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>263764100.2</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>263764100.2</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-21291975.22908874</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>96387616</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>96387616.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>37.36</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>37.67</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>39.63</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>37.67</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>39.63</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>60814772.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>107576307.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>107576307.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>111580509.9</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>267374187.92</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>267374187.92</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-23615579.27009116</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>60814772</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>60814772.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>37.79</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>37.84</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>39.68</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>37.84</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>39.68</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>64131207.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>125188503.2</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>125188503.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>111110160.4</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>270632048.46</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>270632048.46</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-22280223.92616281</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>64131207</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>64131207.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>38.23999999999999</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>39.73</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>38</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>39.73</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>84174239.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>151544736.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>151544736</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>115345566.9</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>275611564.34</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>275611564.34</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-19932183.47318789</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>84174239</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>84174239.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>

--- a/Result/checksun_type/玻璃基板.xlsx
+++ b/Result/checksun_type/玻璃基板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>132.605</t>
+          <t>44.221</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-21.31</t>
+          <t>-32.35</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-11.07</t>
+          <t>-10.89</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>24.68</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>26.38</v>
+        <v>26.18</v>
       </c>
       <c r="AN2" t="n">
         <v>26.78</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-56.92</t>
+          <t>-39.44</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-115.12</t>
+          <t>-116.78</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>61115010.2360515</t>
+          <t>61030072.53</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3298659.0</t>
+          <t>1105744.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>3409647.6</v>
+        <v>2762517</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4333083.4</t>
+          <t>4083544.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>10178782.26</v>
+        <v>10163096.92</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-923435</t>
+          <t>-1321027</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1466127.300455383</t>
+          <t>-1473637.176334369</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1446674.246380107</t>
+          <t>-1514941.493668794</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>3298659.0</t>
+          <t>1105744.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>182.531</t>
+          <t>132.605</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-11.85</t>
+          <t>-21.31</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-11.96</t>
+          <t>-11.07</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>24.78</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>26.62</v>
+        <v>26.38</v>
       </c>
       <c r="AN3" t="n">
-        <v>26.79</v>
+        <v>26.78</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-82.30</t>
+          <t>-56.92</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-112.97</t>
+          <t>-115.12</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>61115010.2360515</t>
+          <t>61030072.53</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4541875.0</t>
+          <t>3298659.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>3888772.8</v>
+        <v>3409647.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4411562.6</t>
+          <t>4333083.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>10182869.32</v>
+        <v>10178782.26</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-522789</t>
+          <t>-923435</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1469664.21937816</t>
+          <t>-1466127.300455383</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1532437.84859698</t>
+          <t>-1446674.246380107</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>4541875.0</t>
+          <t>3298659.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>77.947</t>
+          <t>182.531</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-25.48</t>
+          <t>-11.85</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-13.04</t>
+          <t>-11.96</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-7.50</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.67</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>26.86</v>
+        <v>26.62</v>
       </c>
       <c r="AN4" t="n">
         <v>26.79</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>25.87</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-116.96</t>
+          <t>-82.30</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-110.30</t>
+          <t>-112.97</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>61115010.2360515</t>
+          <t>61030072.53</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1903538.0</t>
+          <t>4541875.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3963383.6</v>
+        <v>3888772.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>5318222.8</t>
+          <t>4411562.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>10129541.2</v>
+        <v>10182869.32</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1354839</t>
+          <t>-522789</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1458250.832247465</t>
+          <t>-1469664.21937816</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1733429.071456906</t>
+          <t>-1532437.84859698</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1903538.0</t>
+          <t>4541875.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>121.223</t>
+          <t>77.947</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-25.48</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-12.32</t>
+          <t>-13.04</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,17 +2304,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2324,53 +2324,53 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-7.61</t>
+          <t>-7.50</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>27.22</v>
+        <v>26.86</v>
       </c>
       <c r="AN5" t="n">
-        <v>26.8</v>
+        <v>26.79</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>25.87</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-165.59</t>
+          <t>-116.96</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-107.29</t>
+          <t>-110.30</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>61115010.2360515</t>
+          <t>61030072.53</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2962769.0</t>
+          <t>1903538.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>5056298.4</v>
+        <v>3963383.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>5511802.7</t>
+          <t>5318222.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>10116244</v>
+        <v>10129541.2</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-455504</t>
+          <t>-1354839</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1408218.425118476</t>
+          <t>-1458250.832247465</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1675972.244419054</t>
+          <t>-1733429.071456906</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2962769.0</t>
+          <t>1903538.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>171.268</t>
+          <t>121.223</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-9.11</t>
+          <t>-12.32</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,54 +2734,54 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-7.61</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>27.43</v>
+        <v>27.22</v>
       </c>
       <c r="AN6" t="n">
-        <v>26.81</v>
+        <v>26.8</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2790,17 +2790,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-273.08</t>
+          <t>-165.59</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.27</t>
+          <t>-107.29</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>61115010.2360515</t>
+          <t>61030072.53</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>4341397.0</t>
+          <t>2962769.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>5404572</v>
+        <v>5056298.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>5443936.9</t>
+          <t>5511802.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>10090356.22</v>
+        <v>10116244</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-39364</t>
+          <t>-455504</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1359535.912518371</t>
+          <t>-1408218.425118476</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1647523.947064298</t>
+          <t>-1675972.244419054</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>4341397.0</t>
+          <t>2962769.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>229.109</t>
+          <t>171.268</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-13.04</t>
+          <t>-9.11</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>27.58</v>
+        <v>27.43</v>
       </c>
       <c r="AN7" t="n">
         <v>26.81</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>25.84</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-960.20</t>
+          <t>-273.08</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-101.36</t>
+          <t>-104.27</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>61115010.2360515</t>
+          <t>61030072.53</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>5694285.0</t>
+          <t>4341397.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>5256519.2</v>
+        <v>5404572</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>5382212.9</t>
+          <t>5443936.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>10042035.4</v>
+        <v>10090356.22</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-125693</t>
+          <t>-39364</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1307174.451691839</t>
+          <t>-1359535.912518371</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1695753.524162351</t>
+          <t>-1647523.947064298</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>5694285.0</t>
+          <t>4341397.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>194.645</t>
+          <t>229.109</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-13.04</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3609,39 +3609,39 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>27.77</v>
+        <v>27.58</v>
       </c>
       <c r="AN8" t="n">
-        <v>26.82</v>
+        <v>26.81</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3650,17 +3650,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-545.29</t>
+          <t>-960.20</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-98.10</t>
+          <t>-101.36</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>61115010.2360515</t>
+          <t>61030072.53</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>4914929.0</t>
+          <t>5694285.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>4934352.4</v>
+        <v>5256519.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>5195209.4</t>
+          <t>5382212.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>9975089.699999999</v>
+        <v>10042035.4</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-260857</t>
+          <t>-125693</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1236523.711242655</t>
+          <t>-1307174.451691839</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1849042.579868057</t>
+          <t>-1695753.524162351</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>4914929.0</t>
+          <t>5694285.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>282.054</t>
+          <t>194.645</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>26.70</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,58 +4039,58 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>16.15</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>26.72</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>27.84</v>
+        <v>27.77</v>
       </c>
       <c r="AN9" t="n">
-        <v>26.81</v>
+        <v>26.82</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>25.84</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-207.53</t>
+          <t>-545.29</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-95.51</t>
+          <t>-98.10</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>61115010.2360515</t>
+          <t>61030072.53</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>7368112.0</t>
+          <t>4914929.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>6673062</v>
+        <v>4934352.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5266881.5</t>
+          <t>5195209.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>9924938.880000001</v>
+        <v>9975089.699999999</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1406180</t>
+          <t>-260857</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1125156.644219854</t>
+          <t>-1236523.711242655</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1918487.281595205</t>
+          <t>-1849042.579868057</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>7368112.0</t>
+          <t>4914929.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>175.583</t>
+          <t>282.054</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-7.03</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15.71</t>
+          <t>26.70</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>10.39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>16.15</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>26.72</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>27.87</v>
+        <v>27.84</v>
       </c>
       <c r="AN10" t="n">
-        <v>26.79</v>
+        <v>26.81</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>25.83</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-116.63</t>
+          <t>-207.53</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-93.19</t>
+          <t>-95.51</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>61115010.2360515</t>
+          <t>61030072.53</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>4704137.0</t>
+          <t>7368112.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>5967307</v>
+        <v>6673062</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5157190.6</t>
+          <t>5266881.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>9855538.880000001</v>
+        <v>9924938.880000001</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>810116</t>
+          <t>1406180</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-980914.7101516086</t>
+          <t>-1125156.644219854</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-2212017.631148446</t>
+          <t>-1918487.281595205</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>4704137.0</t>
+          <t>7368112.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,17 +4641,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>133.171</t>
+          <t>175.583</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-8.84</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>15.71</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>37.93</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>27.03</t>
+          <t>26.86</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>27.86</v>
+        <v>27.87</v>
       </c>
       <c r="AN11" t="n">
-        <v>26.76</v>
+        <v>26.79</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>25.81</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-89.82</t>
+          <t>-116.63</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-91.20</t>
+          <t>-93.19</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>61115010.2360515</t>
+          <t>61030072.53</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3601133.0</t>
+          <t>4704137.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>5483301.8</v>
+        <v>5967307</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5729175.2</t>
+          <t>5157190.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>9863427.640000001</v>
+        <v>9855538.880000001</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-245873</t>
+          <t>810116</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-757077.8154249107</t>
+          <t>-980914.7101516086</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-2266920.179397777</t>
+          <t>-2212017.631148446</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>3601133.0</t>
+          <t>4704137.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>150.184</t>
+          <t>133.171</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-9.04</t>
+          <t>-8.62</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-19.78</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>41.38</t>
+          <t>37.93</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>17.96</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>27.06</t>
+          <t>27.03</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>27.82</v>
+        <v>27.86</v>
       </c>
       <c r="AN12" t="n">
-        <v>26.74</v>
+        <v>26.76</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-81.86</t>
+          <t>-89.82</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-89.22</t>
+          <t>-91.20</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>61115010.2360515</t>
+          <t>61030072.53</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>4083451.0</t>
+          <t>3601133.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>5507906.6</v>
+        <v>5483301.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>6865809.6</t>
+          <t>5729175.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>10002101.52</v>
+        <v>9863427.640000001</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1357903</t>
+          <t>-245873</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-482561.0219752988</t>
+          <t>-757077.8154249107</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-2146211.956204042</t>
+          <t>-2266920.179397777</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>4083451.0</t>
+          <t>3601133.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5571,17 +5571,17 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>27.45</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>26.85</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-9.92</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,54 +5744,54 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.83</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>13.83</v>
+        <v>13.8</v>
       </c>
       <c r="AN13" t="n">
-        <v>14.41</v>
+        <v>14.35</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5800,17 +5800,17 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-12.91</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-111.98</t>
+          <t>-112.26</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>7360.958213256485</t>
+          <t>7350.869784172662</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>1213.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>527.6</v>
+        <v>459.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>585.7</t>
+          <t>420.3</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>567.6799999999999</v>
+        <v>554.86</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-58</t>
+          <t>39</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-10.38647013903138</t>
+          <t>-9.721075147084617</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>21.00387133963898</t>
+          <t>-6.061402691377396</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>1213.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-31.65</t>
+          <t>-9.92</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,54 +6174,54 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>13.86</v>
+        <v>13.83</v>
       </c>
       <c r="AN14" t="n">
-        <v>14.48</v>
+        <v>14.41</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-16.60</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-111.60</t>
+          <t>-111.98</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>7360.958213256485</t>
+          <t>7350.869784172662</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>1213.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>340.2</v>
+        <v>527.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>497.7</t>
+          <t>585.7</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>555.26</v>
+        <v>567.6799999999999</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-157</t>
+          <t>-58</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-16.09380495333509</t>
+          <t>-10.38647013903138</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-46.08158973532466</t>
+          <t>21.00387133963898</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>1213.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6426,17 +6426,17 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-48.73</t>
+          <t>-31.65</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-24.86</t>
+          <t>-22.83</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,54 +6604,54 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>13.43</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>13.9</v>
+        <v>13.86</v>
       </c>
       <c r="AN15" t="n">
-        <v>14.55</v>
+        <v>14.48</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6660,17 +6660,17 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-19.79</t>
+          <t>-16.60</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-111.11</t>
+          <t>-111.60</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>7360.958213256485</t>
+          <t>7350.869784172662</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>332</v>
+        <v>340.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>647.5</t>
+          <t>497.7</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>577.0599999999999</v>
+        <v>555.26</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-315</t>
+          <t>-157</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-10.6414804475188</t>
+          <t>-16.09380495333509</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-32.37933449472541</t>
+          <t>-46.08158973532466</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-4.30</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,17 +6791,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
+          <t>12.9</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
           <t>13.4</t>
         </is>
       </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>13.55</t>
-        </is>
-      </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-45.61</t>
+          <t>-48.73</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-23.12</t>
+          <t>-24.86</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,12 +7034,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7054,34 +7054,34 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-3.20</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>13.62</t>
+          <t>13.43</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>13.95</v>
+        <v>13.9</v>
       </c>
       <c r="AN16" t="n">
-        <v>14.64</v>
+        <v>14.55</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7090,17 +7090,17 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-19.79</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-110.56</t>
+          <t>-111.11</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>7360.958213256485</t>
+          <t>7350.869784172662</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>374.0</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>340.4</v>
+        <v>332</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>625.9</t>
+          <t>647.5</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>605.1799999999999</v>
+        <v>577.0599999999999</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-285</t>
+          <t>-315</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-6.68914334802669</t>
+          <t>-10.6414804475188</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-18.71970791905761</t>
+          <t>-32.37933449472541</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>374.0</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>13.15</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7323,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-36.19</t>
+          <t>-45.61</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-21.39</t>
+          <t>-23.12</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,12 +7464,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7484,34 +7484,34 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>13.62</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>13.98</v>
+        <v>13.95</v>
       </c>
       <c r="AN17" t="n">
-        <v>14.71</v>
+        <v>14.64</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7520,17 +7520,17 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-110.37</t>
+          <t>-110.56</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>7360.958213256485</t>
+          <t>7350.869784172662</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>374.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>381</v>
+        <v>340.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>597.1</t>
+          <t>625.9</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>630.02</v>
+        <v>605.1799999999999</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-216</t>
+          <t>-285</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-4.501767971475612</t>
+          <t>-6.68914334802669</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-9.46596609956589</t>
+          <t>-18.71970791905761</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>374.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
+          <t>13.6</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
           <t>13.65</t>
         </is>
       </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>13.95</t>
-        </is>
-      </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>13.15</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7793,12 +7793,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>-36.19</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,12 +7894,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7909,58 +7909,58 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>14</v>
+        <v>13.98</v>
       </c>
       <c r="AN18" t="n">
-        <v>14.79</v>
+        <v>14.71</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-110.48</t>
+          <t>-110.37</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>7360.958213256485</t>
+          <t>7350.869784172662</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>276.0</t>
+          <t>573.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>643.8</v>
+        <v>381</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>572.3</t>
+          <t>597.1</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>643.84</v>
+        <v>630.02</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>-216</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-3.599186493641016</t>
+          <t>-4.501767971475612</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-17.22969328245046</t>
+          <t>-9.46596609956589</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>276.0</t>
+          <t>573.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.95</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>16.38</t>
+          <t>12.49</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-21.10</t>
+          <t>-21.39</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,12 +8324,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8339,39 +8339,39 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>14.03</t>
         </is>
       </c>
       <c r="AM19" t="n">
         <v>14</v>
       </c>
       <c r="AN19" t="n">
-        <v>14.87</v>
+        <v>14.79</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8380,12 +8380,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>21.76</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-110.76</t>
+          <t>-110.48</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>7360.958213256485</t>
+          <t>7350.869784172662</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>276.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>655.2</v>
+        <v>643.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>572.3</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>675</v>
+        <v>643.84</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-1.120912532039299</t>
+          <t>-3.599186493641016</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>4.116042644944969</t>
+          <t>-17.22969328245046</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>276.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>13.95</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>70.35</t>
+          <t>16.38</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-19.36</t>
+          <t>-21.10</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-6.17</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>14.17</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>14.02</v>
+        <v>14</v>
       </c>
       <c r="AN20" t="n">
-        <v>14.94</v>
+        <v>14.87</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>15.13</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>35.24</t>
+          <t>21.76</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-111.35</t>
+          <t>-110.76</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>7360.958213256485</t>
+          <t>7350.869784172662</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>314.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>963</v>
+        <v>655.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>565.3</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>734.12</v>
+        <v>675</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>92</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-2.073086200581893</t>
+          <t>-1.120912532039299</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>46.35580673247603</t>
+          <t>4.116042644944969</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>314.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>13.95</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>13.95</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>13.95</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-6.74</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>57.03</t>
+          <t>70.35</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-17.63</t>
+          <t>-19.36</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,63 +9184,63 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-6.69</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>14.22</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AM21" t="n">
         <v>14.02</v>
       </c>
       <c r="AN21" t="n">
-        <v>15.03</v>
+        <v>14.94</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>15.12</t>
+          <t>15.13</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>35.24</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-112.35</t>
+          <t>-111.35</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>7360.958213256485</t>
+          <t>7350.869784172662</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>577.0</t>
+          <t>314.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>911.4</v>
+        <v>963</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>580.4</t>
+          <t>565.3</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>762.26</v>
+        <v>734.12</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>397</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-10.87833946113788</t>
+          <t>-2.073086200581893</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>89.0784766170749</t>
+          <t>46.35580673247603</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>577.0</t>
+          <t>314.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>13.95</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>13.95</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-10.11</t>
+          <t>-6.74</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>44.90</t>
+          <t>57.03</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-15.03</t>
+          <t>-17.63</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-7.13</t>
+          <t>-6.69</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>14.13</t>
+          <t>14.22</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>14.03</v>
+        <v>14.02</v>
       </c>
       <c r="AN22" t="n">
-        <v>15.11</v>
+        <v>15.03</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>15.12</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>40.16</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-113.64</t>
+          <t>-112.35</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>7360.958213256485</t>
+          <t>7350.869784172662</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>1887.0</t>
+          <t>577.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>813.2</v>
+        <v>911.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>561.2</t>
+          <t>580.4</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>794.04</v>
+        <v>762.26</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>331</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-29.05230602081294</t>
+          <t>-10.87833946113788</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>118.7509165730348</t>
+          <t>89.0784766170749</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>1887.0</t>
+          <t>577.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
+          <t>14.7</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
+          <t>14.7</t>
+        </is>
+      </c>
+      <c r="CF22" t="inlineStr">
+        <is>
+          <t>14.2</t>
+        </is>
+      </c>
+      <c r="CG22" t="inlineStr">
+        <is>
           <t>14.25</t>
-        </is>
-      </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>15.5</t>
-        </is>
-      </c>
-      <c r="CF22" t="inlineStr">
-        <is>
-          <t>14.25</t>
-        </is>
-      </c>
-      <c r="CG22" t="inlineStr">
-        <is>
-          <t>14.7</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-10.11</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>15.68</t>
+          <t>44.90</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-17.34</t>
+          <t>-15.03</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>8.08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,126 +10059,126 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>61.11</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-7.8</t>
+          <t>-7.13</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
+          <t>14.13</t>
+        </is>
+      </c>
+      <c r="AM23" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>15.11</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>40.16</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>-0.19</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>-0.32</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>-113.64</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>7350.869784172662</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>1887.0</t>
+        </is>
+      </c>
+      <c r="AX23" t="n">
+        <v>813.2</v>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>561.2</t>
+        </is>
+      </c>
+      <c r="AZ23" t="n">
+        <v>794.04</v>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>-29.05230602081294</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>118.7509165730348</t>
+        </is>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>1887.0</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
           <t>13.95</t>
         </is>
       </c>
-      <c r="AM23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>15.19</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>15.09</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>25.01</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="AT23" t="inlineStr">
-        <is>
-          <t>-115.01</t>
-        </is>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AV23" t="inlineStr">
-        <is>
-          <t>7360.958213256485</t>
-        </is>
-      </c>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>333.0</t>
-        </is>
-      </c>
-      <c r="AX23" t="n">
-        <v>500.8</v>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>432.9</t>
-        </is>
-      </c>
-      <c r="AZ23" t="n">
-        <v>783.6</v>
-      </c>
-      <c r="BA23" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="BB23" t="inlineStr">
-        <is>
-          <t>-55.92561921969435</t>
-        </is>
-      </c>
-      <c r="BC23" t="inlineStr">
-        <is>
-          <t>16.54186948965486</t>
-        </is>
-      </c>
-      <c r="BD23" t="inlineStr">
-        <is>
-          <t>333.0</t>
-        </is>
-      </c>
-      <c r="BE23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF23" t="inlineStr">
-        <is>
-          <t>13.95</t>
-        </is>
-      </c>
       <c r="BG23" t="inlineStr">
         <is>
           <t>2025/08/13</t>
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10343,12 +10343,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1012.048</t>
+          <t>1052.554</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-30.50</t>
+          <t>-26.38</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -10453,17 +10453,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -10474,73 +10474,73 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>48.21</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>48.28</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>34.41</t>
+          <t>34.39</t>
         </is>
       </c>
       <c r="AM24" t="n">
-        <v>36.18</v>
+        <v>36.08</v>
       </c>
       <c r="AN24" t="n">
-        <v>38.94</v>
+        <v>38.92</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>37.63</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>-131.94</t>
+          <t>-132.25</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -10560,43 +10560,43 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>233443914.7002882</t>
+          <t>233186776.6014389</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>35345556.0</t>
+          <t>36488624.0</t>
         </is>
       </c>
       <c r="AX24" t="n">
-        <v>37074921.8</v>
+        <v>37237782</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>53345322.1</t>
+          <t>50581063.8</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>245778298.12</v>
+        <v>242256442.44</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>-16270400</t>
+          <t>-13343281</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>-23530075.2025471</t>
+          <t>-22914581.90439074</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-20878828.60415238</t>
+          <t>-19529368.76453082</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>35345556.0</t>
+          <t>36488624.0</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="BM24" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN24" t="inlineStr">
@@ -10661,17 +10661,17 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS24" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="BT24" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="BY24" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -10726,22 +10726,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -10773,12 +10773,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>857.193</t>
+          <t>1012.048</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -10798,17 +10798,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-31.65</t>
+          <t>-30.50</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -10873,7 +10873,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-7.55</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -10883,17 +10883,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -10904,73 +10904,73 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>48.21</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>10.92</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>34.16</t>
+          <t>34.41</t>
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>36.33</v>
+        <v>36.18</v>
       </c>
       <c r="AN25" t="n">
-        <v>39</v>
+        <v>38.94</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>37.52</t>
+          <t>37.58</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>-131.18</t>
+          <t>-131.94</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -10990,43 +10990,43 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>233443914.7002882</t>
+          <t>233186776.6014389</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>29401532.0</t>
+          <t>35345556.0</t>
         </is>
       </c>
       <c r="AX25" t="n">
-        <v>39796395.2</v>
+        <v>37074921.8</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>58228190.4</t>
+          <t>53345322.1</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>247556548.26</v>
+        <v>245778298.12</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>-18431795</t>
+          <t>-16270400</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>-24012120.03861886</t>
+          <t>-23530075.2025471</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-21938484.35346347</t>
+          <t>-20878828.60415238</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>29401532.0</t>
+          <t>35345556.0</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -11046,7 +11046,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="BM25" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN25" t="inlineStr">
@@ -11091,17 +11091,17 @@
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS25" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BT25" t="inlineStr">
@@ -11131,12 +11131,12 @@
       </c>
       <c r="BY25" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -11156,22 +11156,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -11203,12 +11203,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1145.3</t>
+          <t>857.193</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>33.65</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -11228,17 +11228,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-25.49</t>
+          <t>-31.65</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-9.30</t>
+          <t>-7.55</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -11313,17 +11313,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -11334,73 +11334,73 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>10.92</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>-6.49</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>34.11999999999999</t>
+          <t>34.16</t>
         </is>
       </c>
       <c r="AM26" t="n">
-        <v>36.49</v>
+        <v>36.33</v>
       </c>
       <c r="AN26" t="n">
-        <v>39.06</v>
+        <v>39</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>37.47</t>
+          <t>37.52</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>-26.04</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>-129.70</t>
+          <t>-131.18</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -11420,43 +11420,43 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>233443914.7002882</t>
+          <t>233186776.6014389</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>38774066.0</t>
+          <t>29401532.0</t>
         </is>
       </c>
       <c r="AX26" t="n">
-        <v>49474507.6</v>
+        <v>39796395.2</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>66401056.1</t>
+          <t>58228190.4</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>249662887.18</v>
+        <v>247556548.26</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>-16926548</t>
+          <t>-18431795</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>-24389144.70864711</t>
+          <t>-24012120.03861886</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-22031901.26842704</t>
+          <t>-21938484.35346347</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>38774066.0</t>
+          <t>29401532.0</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="BM26" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN26" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="BS26" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="BT26" t="inlineStr">
@@ -11561,12 +11561,12 @@
       </c>
       <c r="BY26" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -11586,22 +11586,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.55</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>33.65</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -11633,12 +11633,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1345.621</t>
+          <t>1145.3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>33.65</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11658,17 +11658,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-27.63</t>
+          <t>-25.49</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-7.55</t>
+          <t>-9.30</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -11743,17 +11743,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -11764,17 +11764,17 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>13.92</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
@@ -11794,43 +11794,43 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-6.2</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>34.33</t>
+          <t>34.11999999999999</t>
         </is>
       </c>
       <c r="AM27" t="n">
-        <v>36.71</v>
+        <v>36.49</v>
       </c>
       <c r="AN27" t="n">
-        <v>39.14</v>
+        <v>39.06</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>37.43</t>
+          <t>37.47</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>-27.70</t>
+          <t>-26.04</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>-127.76</t>
+          <t>-129.70</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -11850,43 +11850,43 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>233443914.7002882</t>
+          <t>233186776.6014389</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>46179132.0</t>
+          <t>38774066.0</t>
         </is>
       </c>
       <c r="AX27" t="n">
-        <v>60997217.6</v>
+        <v>49474507.6</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>84286762.5</t>
+          <t>66401056.1</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>254822433.06</v>
+        <v>249662887.18</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>-23289544</t>
+          <t>-16926548</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>-24817734.42505076</t>
+          <t>-24389144.70864711</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-22382700.45878832</t>
+          <t>-22031901.26842704</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>46179132.0</t>
+          <t>38774066.0</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="BM27" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN27" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="BS27" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="BT27" t="inlineStr">
@@ -11991,12 +11991,12 @@
       </c>
       <c r="BY27" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -12016,22 +12016,22 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>34.05</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>33.65</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1029.736</t>
+          <t>1345.621</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -12088,17 +12088,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-32.40</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-6.20</t>
+          <t>-7.55</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -12173,17 +12173,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -12194,73 +12194,73 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>13.92</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-6.49</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-6.2</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>34.33</t>
         </is>
       </c>
       <c r="AM28" t="n">
-        <v>36.88</v>
+        <v>36.71</v>
       </c>
       <c r="AN28" t="n">
-        <v>39.24</v>
+        <v>39.14</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>37.43</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>-32.46</t>
+          <t>-27.70</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>-125.84</t>
+          <t>-127.76</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -12280,43 +12280,43 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>233443914.7002882</t>
+          <t>233186776.6014389</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>35674323.0</t>
+          <t>46179132.0</t>
         </is>
       </c>
       <c r="AX28" t="n">
-        <v>63924345.6</v>
+        <v>60997217.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>94556424.4</t>
+          <t>84286762.5</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>256700200.08</v>
+        <v>254822433.06</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>-30632078</t>
+          <t>-23289544</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>-25260467.87346211</t>
+          <t>-24817734.42505076</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-22877859.92863344</t>
+          <t>-22382700.45878832</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>35674323.0</t>
+          <t>46179132.0</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -12361,7 +12361,7 @@
       </c>
       <c r="BM28" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN28" t="inlineStr">
@@ -12381,17 +12381,17 @@
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS28" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="BT28" t="inlineStr">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="BY28" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -12446,22 +12446,22 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.05</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>34.85</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -12493,12 +12493,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1450.779</t>
+          <t>1029.736</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -12518,17 +12518,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-37.05</t>
+          <t>-32.40</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-9.03</t>
+          <t>-6.20</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -12603,17 +12603,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -12624,73 +12624,73 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>35.22000000000001</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>37.06</v>
+        <v>36.88</v>
       </c>
       <c r="AN29" t="n">
-        <v>39.33</v>
+        <v>39.24</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>37.33</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>-41.33</t>
+          <t>-32.46</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>-123.74</t>
+          <t>-125.84</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -12710,43 +12710,43 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>233443914.7002882</t>
+          <t>233186776.6014389</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>48952923.0</t>
+          <t>35674323.0</t>
         </is>
       </c>
       <c r="AX29" t="n">
-        <v>69615722.40000001</v>
+        <v>63924345.6</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>110580229.2</t>
+          <t>94556424.4</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>258176781.58</v>
+        <v>256700200.08</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>-40964506</t>
+          <t>-30632078</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>-25693669.31797642</t>
+          <t>-25260467.87346211</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>-21642648.9238181</t>
+          <t>-22877859.92863344</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>48952923.0</t>
+          <t>35674323.0</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="BM29" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN29" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS29" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="BT29" t="inlineStr">
@@ -12851,12 +12851,12 @@
       </c>
       <c r="BY29" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ29" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="CA29" t="inlineStr">
@@ -12876,22 +12876,22 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2260.366</t>
+          <t>1450.779</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -12938,7 +12938,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -12948,17 +12948,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-32.59</t>
+          <t>-37.05</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -13023,7 +13023,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-8.09</t>
+          <t>-9.03</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -13033,17 +13033,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -13054,12 +13054,12 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -13074,53 +13074,53 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>36.01000000000001</t>
+          <t>35.22000000000001</t>
         </is>
       </c>
       <c r="AM30" t="n">
-        <v>37.29</v>
+        <v>37.06</v>
       </c>
       <c r="AN30" t="n">
-        <v>39.43</v>
+        <v>39.33</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.33</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>-37.57</t>
+          <t>-41.33</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>-121.29</t>
+          <t>-123.74</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -13140,43 +13140,43 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>233443914.7002882</t>
+          <t>233186776.6014389</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>77792094.0</t>
+          <t>48952923.0</t>
         </is>
       </c>
       <c r="AX30" t="n">
-        <v>76659985.59999999</v>
+        <v>69615722.40000001</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>113715310.1</t>
+          <t>110580229.2</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>261926998.4</v>
+        <v>258176781.58</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>-37055324</t>
+          <t>-40964506</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>-26430218.48055065</t>
+          <t>-25693669.31797642</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>-20527817.16965982</t>
+          <t>-21642648.9238181</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>77792094.0</t>
+          <t>48952923.0</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
@@ -13196,7 +13196,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -13221,7 +13221,7 @@
       </c>
       <c r="BM30" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN30" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="BS30" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="BT30" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="BY30" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ30" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="CA30" t="inlineStr">
@@ -13306,22 +13306,22 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
         <is>
-          <t>35.25</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2726.249</t>
+          <t>2260.366</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -13378,17 +13378,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-25.83</t>
+          <t>-32.59</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-6.47</t>
+          <t>-8.09</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -13463,17 +13463,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>-6.20</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -13484,12 +13484,12 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -13499,58 +13499,58 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>36.59</t>
+          <t>36.01000000000001</t>
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>37.52</v>
+        <v>37.29</v>
       </c>
       <c r="AN31" t="n">
-        <v>39.54</v>
+        <v>39.43</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>37.26</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>-26.44</t>
+          <t>-37.57</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>-119.29</t>
+          <t>-121.29</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -13570,43 +13570,43 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>233443914.7002882</t>
+          <t>233186776.6014389</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>96387616.0</t>
+          <t>77792094.0</t>
         </is>
       </c>
       <c r="AX31" t="n">
-        <v>83327604.59999999</v>
+        <v>76659985.59999999</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>112354225.4</t>
+          <t>113715310.1</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>263764100.2</v>
+        <v>261926998.4</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>-29026620</t>
+          <t>-37055324</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>-27503382.35525808</t>
+          <t>-26430218.48055065</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>-21291975.22908874</t>
+          <t>-20527817.16965982</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>96387616.0</t>
+          <t>77792094.0</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="BM31" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN31" t="inlineStr">
@@ -13676,12 +13676,12 @@
       </c>
       <c r="BR31" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS31" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="BT31" t="inlineStr">
@@ -13711,12 +13711,12 @@
       </c>
       <c r="BY31" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ31" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="CA31" t="inlineStr">
@@ -13736,22 +13736,22 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>35.25</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -13783,12 +13783,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1669.175</t>
+          <t>2726.249</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -13798,7 +13798,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13808,17 +13808,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-25.83</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -13893,17 +13893,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-6.20</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -13914,12 +13914,12 @@
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -13929,58 +13929,58 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-5.1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>37.36</t>
+          <t>36.59</t>
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>37.67</v>
+        <v>37.52</v>
       </c>
       <c r="AN32" t="n">
-        <v>39.63</v>
+        <v>39.54</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>37.21</t>
+          <t>37.26</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>-7.99</t>
+          <t>-26.44</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>-118.02</t>
+          <t>-119.29</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -14000,43 +14000,43 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>233443914.7002882</t>
+          <t>233186776.6014389</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>60814772.0</t>
+          <t>96387616.0</t>
         </is>
       </c>
       <c r="AX32" t="n">
-        <v>107576307.4</v>
+        <v>83327604.59999999</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>111580509.9</t>
+          <t>112354225.4</t>
         </is>
       </c>
       <c r="AZ32" t="n">
-        <v>267374187.92</v>
+        <v>263764100.2</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>-4004202</t>
+          <t>-29026620</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>-28632729.10547069</t>
+          <t>-27503382.35525808</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>-23615579.27009116</t>
+          <t>-21291975.22908874</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>60814772.0</t>
+          <t>96387616.0</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
@@ -14081,7 +14081,7 @@
       </c>
       <c r="BM32" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN32" t="inlineStr">
@@ -14101,17 +14101,17 @@
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS32" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="BT32" t="inlineStr">
@@ -14141,12 +14141,12 @@
       </c>
       <c r="BY32" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ32" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="CA32" t="inlineStr">
@@ -14171,17 +14171,17 @@
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CF32" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="CG32" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="CH32" t="inlineStr">
@@ -14213,12 +14213,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1717.738</t>
+          <t>1669.175</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -14228,72 +14228,72 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
+          <t>36.45</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-5.04</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>-3.59</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>37.7</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
           <t>37.1</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>-6.0</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>12.67</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>37.7</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>37.1</t>
-        </is>
-      </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
@@ -14308,12 +14308,12 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -14323,17 +14323,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -14344,73 +14344,73 @@
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>28.16</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>37.79</t>
+          <t>37.36</t>
         </is>
       </c>
       <c r="AM33" t="n">
-        <v>37.84</v>
+        <v>37.67</v>
       </c>
       <c r="AN33" t="n">
-        <v>39.68</v>
+        <v>39.63</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>37.21</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-7.99</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -14420,7 +14420,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>-117.66</t>
+          <t>-118.02</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -14430,48 +14430,48 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>233443914.7002882</t>
+          <t>233186776.6014389</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>64131207.0</t>
+          <t>60814772.0</t>
         </is>
       </c>
       <c r="AX33" t="n">
-        <v>125188503.2</v>
+        <v>107576307.4</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>111110160.4</t>
+          <t>111580509.9</t>
         </is>
       </c>
       <c r="AZ33" t="n">
-        <v>270632048.46</v>
+        <v>267374187.92</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>14078342</t>
+          <t>-4004202</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>-29544938.16644878</t>
+          <t>-28632729.10547069</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>-22280223.92616281</t>
+          <t>-23615579.27009116</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>64131207.0</t>
+          <t>60814772.0</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr">
@@ -14486,7 +14486,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -14511,7 +14511,7 @@
       </c>
       <c r="BM33" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN33" t="inlineStr">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR33" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
@@ -14571,12 +14571,12 @@
       </c>
       <c r="BY33" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ33" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="CA33" t="inlineStr">
@@ -14596,22 +14596,22 @@
       </c>
       <c r="CD33" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="CE33" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CF33" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CG33" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.45</t>
         </is>
       </c>
       <c r="CH33" t="inlineStr">
@@ -14633,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -14643,12 +14643,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2218.713</t>
+          <t>1717.738</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14658,74 +14658,74 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>37.1</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-6.92</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>12.67</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
           <t>37.7</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>-7.71</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>31.38</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>37.1</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
         <is>
           <t>37.7</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>37.1</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>37.7</t>
-        </is>
-      </c>
       <c r="T34" t="inlineStr">
         <is>
           <t>41.9</t>
@@ -14738,14 +14738,14 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
+          <t>-1.59</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
       <c r="X34" t="inlineStr">
         <is>
           <t>-11.40</t>
@@ -14753,17 +14753,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -14774,73 +14774,73 @@
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>22.41</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>44.83</t>
+          <t>28.16</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>38.23999999999999</t>
+          <t>37.79</t>
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>38</v>
+        <v>37.84</v>
       </c>
       <c r="AN34" t="n">
-        <v>39.73</v>
+        <v>39.68</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>-117.63</t>
+          <t>-117.66</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -14860,43 +14860,43 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>233443914.7002882</t>
+          <t>233186776.6014389</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>84174239.0</t>
+          <t>64131207.0</t>
         </is>
       </c>
       <c r="AX34" t="n">
-        <v>151544736</v>
+        <v>125188503.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>115345566.9</t>
+          <t>111110160.4</t>
         </is>
       </c>
       <c r="AZ34" t="n">
-        <v>275611564.34</v>
+        <v>270632048.46</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>36199169</t>
+          <t>14078342</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>-30865795.30104623</t>
+          <t>-29544938.16644878</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>-19932183.47318789</t>
+          <t>-22280223.92616281</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>84174239.0</t>
+          <t>64131207.0</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
@@ -14941,7 +14941,7 @@
       </c>
       <c r="BM34" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN34" t="inlineStr">
@@ -14961,7 +14961,7 @@
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
@@ -14971,7 +14971,7 @@
       </c>
       <c r="BS34" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="BT34" t="inlineStr">
@@ -15001,12 +15001,12 @@
       </c>
       <c r="BY34" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ34" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="CA34" t="inlineStr">
@@ -15026,22 +15026,22 @@
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CE34" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CF34" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CG34" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CH34" t="inlineStr">

--- a/Result/checksun_type/玻璃基板.xlsx
+++ b/Result/checksun_type/玻璃基板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.221</t>
+          <t>129.907</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-32.35</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-10.89</t>
+          <t>-9.82</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>26.18</v>
+        <v>26.04</v>
       </c>
       <c r="AN2" t="n">
-        <v>26.78</v>
+        <v>26.79</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-39.44</t>
+          <t>-23.75</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-116.78</t>
+          <t>-117.83</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>61030072.53</t>
+          <t>60949966.30527817</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1105744.0</t>
+          <t>3250406.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2762517</v>
+        <v>2820044.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4083544.5</t>
+          <t>3938171.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>10163096.92</v>
+        <v>10185422.26</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1321027</t>
+          <t>-1118127</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1473637.176334369</t>
+          <t>-1456770.746041259</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1514941.493668794</t>
+          <t>-1364005.379429155</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1105744.0</t>
+          <t>3250406.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>132.605</t>
+          <t>44.221</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-21.31</t>
+          <t>-32.35</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-11.07</t>
+          <t>-10.89</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>24.68</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>26.38</v>
+        <v>26.18</v>
       </c>
       <c r="AN3" t="n">
         <v>26.78</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-56.92</t>
+          <t>-39.44</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-115.12</t>
+          <t>-116.78</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>61030072.53</t>
+          <t>60949966.30527817</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3298659.0</t>
+          <t>1105744.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>3409647.6</v>
+        <v>2762517</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4333083.4</t>
+          <t>4083544.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>10178782.26</v>
+        <v>10163096.92</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-923435</t>
+          <t>-1321027</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1466127.300455383</t>
+          <t>-1473637.176334369</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1446674.246380107</t>
+          <t>-1514941.493668794</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>3298659.0</t>
+          <t>1105744.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>182.531</t>
+          <t>132.605</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-11.85</t>
+          <t>-21.31</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-11.96</t>
+          <t>-11.07</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>24.78</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>26.62</v>
+        <v>26.38</v>
       </c>
       <c r="AN4" t="n">
-        <v>26.79</v>
+        <v>26.78</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-82.30</t>
+          <t>-56.92</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-112.97</t>
+          <t>-115.12</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>61030072.53</t>
+          <t>60949966.30527817</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4541875.0</t>
+          <t>3298659.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3888772.8</v>
+        <v>3409647.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>4411562.6</t>
+          <t>4333083.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>10182869.32</v>
+        <v>10178782.26</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-522789</t>
+          <t>-923435</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1469664.21937816</t>
+          <t>-1466127.300455383</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1532437.84859698</t>
+          <t>-1446674.246380107</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>4541875.0</t>
+          <t>3298659.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>77.947</t>
+          <t>182.531</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-25.48</t>
+          <t>-11.85</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-13.04</t>
+          <t>-11.96</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-7.50</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.67</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>26.86</v>
+        <v>26.62</v>
       </c>
       <c r="AN5" t="n">
         <v>26.79</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>25.87</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-116.96</t>
+          <t>-82.30</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-110.30</t>
+          <t>-112.97</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>61030072.53</t>
+          <t>60949966.30527817</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1903538.0</t>
+          <t>4541875.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3963383.6</v>
+        <v>3888772.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>5318222.8</t>
+          <t>4411562.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>10129541.2</v>
+        <v>10182869.32</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1354839</t>
+          <t>-522789</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1458250.832247465</t>
+          <t>-1469664.21937816</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1733429.071456906</t>
+          <t>-1532437.84859698</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1903538.0</t>
+          <t>4541875.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>121.223</t>
+          <t>77.947</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-25.48</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-12.32</t>
+          <t>-13.04</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,17 +2734,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2754,53 +2754,53 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-7.61</t>
+          <t>-7.50</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>27.22</v>
+        <v>26.86</v>
       </c>
       <c r="AN6" t="n">
-        <v>26.8</v>
+        <v>26.79</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>25.87</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-165.59</t>
+          <t>-116.96</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-107.29</t>
+          <t>-110.30</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>61030072.53</t>
+          <t>60949966.30527817</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2962769.0</t>
+          <t>1903538.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>5056298.4</v>
+        <v>3963383.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>5511802.7</t>
+          <t>5318222.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>10116244</v>
+        <v>10129541.2</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-455504</t>
+          <t>-1354839</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1408218.425118476</t>
+          <t>-1458250.832247465</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1675972.244419054</t>
+          <t>-1733429.071456906</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2962769.0</t>
+          <t>1903538.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>171.268</t>
+          <t>121.223</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-9.11</t>
+          <t>-12.32</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,54 +3164,54 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-7.61</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>27.43</v>
+        <v>27.22</v>
       </c>
       <c r="AN7" t="n">
-        <v>26.81</v>
+        <v>26.8</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3220,17 +3220,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-273.08</t>
+          <t>-165.59</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.27</t>
+          <t>-107.29</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>61030072.53</t>
+          <t>60949966.30527817</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>4341397.0</t>
+          <t>2962769.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>5404572</v>
+        <v>5056298.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>5443936.9</t>
+          <t>5511802.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>10090356.22</v>
+        <v>10116244</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-39364</t>
+          <t>-455504</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1359535.912518371</t>
+          <t>-1408218.425118476</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1647523.947064298</t>
+          <t>-1675972.244419054</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>4341397.0</t>
+          <t>2962769.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>229.109</t>
+          <t>171.268</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-13.04</t>
+          <t>-9.11</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>27.58</v>
+        <v>27.43</v>
       </c>
       <c r="AN8" t="n">
         <v>26.81</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>25.84</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-960.20</t>
+          <t>-273.08</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-101.36</t>
+          <t>-104.27</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>61030072.53</t>
+          <t>60949966.30527817</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>5694285.0</t>
+          <t>4341397.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>5256519.2</v>
+        <v>5404572</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>5382212.9</t>
+          <t>5443936.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>10042035.4</v>
+        <v>10090356.22</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-125693</t>
+          <t>-39364</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1307174.451691839</t>
+          <t>-1359535.912518371</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1695753.524162351</t>
+          <t>-1647523.947064298</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>5694285.0</t>
+          <t>4341397.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>194.645</t>
+          <t>229.109</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-13.04</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,39 +4039,39 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>27.77</v>
+        <v>27.58</v>
       </c>
       <c r="AN9" t="n">
-        <v>26.82</v>
+        <v>26.81</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4080,17 +4080,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-545.29</t>
+          <t>-960.20</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-98.10</t>
+          <t>-101.36</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>61030072.53</t>
+          <t>60949966.30527817</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>4914929.0</t>
+          <t>5694285.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>4934352.4</v>
+        <v>5256519.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5195209.4</t>
+          <t>5382212.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>9975089.699999999</v>
+        <v>10042035.4</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-260857</t>
+          <t>-125693</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1236523.711242655</t>
+          <t>-1307174.451691839</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1849042.579868057</t>
+          <t>-1695753.524162351</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>4914929.0</t>
+          <t>5694285.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>282.054</t>
+          <t>194.645</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>26.70</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,58 +4469,58 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>16.15</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>26.72</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>27.84</v>
+        <v>27.77</v>
       </c>
       <c r="AN10" t="n">
-        <v>26.81</v>
+        <v>26.82</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>25.84</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-207.53</t>
+          <t>-545.29</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-95.51</t>
+          <t>-98.10</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>61030072.53</t>
+          <t>60949966.30527817</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>7368112.0</t>
+          <t>4914929.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>6673062</v>
+        <v>4934352.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5266881.5</t>
+          <t>5195209.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>9924938.880000001</v>
+        <v>9975089.699999999</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1406180</t>
+          <t>-260857</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1125156.644219854</t>
+          <t>-1236523.711242655</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1918487.281595205</t>
+          <t>-1849042.579868057</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>7368112.0</t>
+          <t>4914929.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>175.583</t>
+          <t>282.054</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>15.71</t>
+          <t>26.70</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>10.39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>16.15</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>26.72</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>27.87</v>
+        <v>27.84</v>
       </c>
       <c r="AN11" t="n">
-        <v>26.79</v>
+        <v>26.81</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>25.83</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-116.63</t>
+          <t>-207.53</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-93.19</t>
+          <t>-95.51</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>61030072.53</t>
+          <t>60949966.30527817</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>4704137.0</t>
+          <t>7368112.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>5967307</v>
+        <v>6673062</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5157190.6</t>
+          <t>5266881.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>9855538.880000001</v>
+        <v>9924938.880000001</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>810116</t>
+          <t>1406180</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-980914.7101516086</t>
+          <t>-1125156.644219854</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-2212017.631148446</t>
+          <t>-1918487.281595205</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>4704137.0</t>
+          <t>7368112.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>133.171</t>
+          <t>175.583</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-8.62</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>15.71</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>37.93</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>27.03</t>
+          <t>26.86</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>27.86</v>
+        <v>27.87</v>
       </c>
       <c r="AN12" t="n">
-        <v>26.76</v>
+        <v>26.79</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>25.81</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-89.82</t>
+          <t>-116.63</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-91.20</t>
+          <t>-93.19</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>61030072.53</t>
+          <t>60949966.30527817</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3601133.0</t>
+          <t>4704137.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>5483301.8</v>
+        <v>5967307</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5729175.2</t>
+          <t>5157190.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>9863427.640000001</v>
+        <v>9855538.880000001</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-245873</t>
+          <t>810116</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-757077.8154249107</t>
+          <t>-980914.7101516086</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-2266920.179397777</t>
+          <t>-2212017.631148446</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>3601133.0</t>
+          <t>4704137.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,42 +5613,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>13.45</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>13.35</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-22.83</t>
+          <t>-22.25</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,54 +5744,54 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>13.8</v>
+        <v>13.77</v>
       </c>
       <c r="AN13" t="n">
-        <v>14.35</v>
+        <v>14.31</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5800,12 +5800,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-112.26</t>
+          <t>-112.36</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>7350.869784172662</t>
+          <t>7341.631465517241</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>459.6</v>
+        <v>507.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>420.3</t>
+          <t>424.0</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>554.86</v>
+        <v>517.4400000000001</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-9.721075147084617</t>
+          <t>-7.653303500733839</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-6.061402691377396</t>
+          <t>3.719440554195444</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-4.30</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>509</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-9.92</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,54 +6174,54 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.83</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>13.83</v>
+        <v>13.8</v>
       </c>
       <c r="AN14" t="n">
-        <v>14.41</v>
+        <v>14.35</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6230,17 +6230,17 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-12.91</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-111.98</t>
+          <t>-112.26</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>7350.869784172662</t>
+          <t>7341.631465517241</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>1213.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>527.6</v>
+        <v>459.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>585.7</t>
+          <t>420.3</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>567.6799999999999</v>
+        <v>554.86</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-58</t>
+          <t>39</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-10.38647013903138</t>
+          <t>-9.721075147084617</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>21.00387133963898</t>
+          <t>-6.061402691377396</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>1213.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>509</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-31.65</t>
+          <t>-9.92</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,54 +6604,54 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>13.86</v>
+        <v>13.83</v>
       </c>
       <c r="AN15" t="n">
-        <v>14.48</v>
+        <v>14.41</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-16.60</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-111.60</t>
+          <t>-111.98</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>7350.869784172662</t>
+          <t>7341.631465517241</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>1213.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>340.2</v>
+        <v>527.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>497.7</t>
+          <t>585.7</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>555.26</v>
+        <v>567.6799999999999</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-157</t>
+          <t>-58</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-16.09380495333509</t>
+          <t>-10.38647013903138</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-46.08158973532466</t>
+          <t>21.00387133963898</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>1213.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>509</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,17 +6856,17 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-48.73</t>
+          <t>-31.65</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-24.86</t>
+          <t>-22.83</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,54 +7034,54 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>13.43</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>13.9</v>
+        <v>13.86</v>
       </c>
       <c r="AN16" t="n">
-        <v>14.55</v>
+        <v>14.48</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7090,17 +7090,17 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-19.79</t>
+          <t>-16.60</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-111.11</t>
+          <t>-111.60</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>7350.869784172662</t>
+          <t>7341.631465517241</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>332</v>
+        <v>340.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>647.5</t>
+          <t>497.7</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>577.0599999999999</v>
+        <v>555.26</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-315</t>
+          <t>-157</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-10.6414804475188</t>
+          <t>-16.09380495333509</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-32.37933449472541</t>
+          <t>-46.08158973532466</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-4.30</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,17 +7221,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>509</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
+          <t>12.9</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
           <t>13.4</t>
         </is>
       </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>13.55</t>
-        </is>
-      </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-45.61</t>
+          <t>-48.73</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-23.12</t>
+          <t>-24.86</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,12 +7464,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7484,34 +7484,34 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-3.20</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>13.62</t>
+          <t>13.43</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>13.95</v>
+        <v>13.9</v>
       </c>
       <c r="AN17" t="n">
-        <v>14.64</v>
+        <v>14.55</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7520,17 +7520,17 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-19.79</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-110.56</t>
+          <t>-111.11</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>7350.869784172662</t>
+          <t>7341.631465517241</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>374.0</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>340.4</v>
+        <v>332</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>625.9</t>
+          <t>647.5</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>605.1799999999999</v>
+        <v>577.0599999999999</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-285</t>
+          <t>-315</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-6.68914334802669</t>
+          <t>-10.6414804475188</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-18.71970791905761</t>
+          <t>-32.37933449472541</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>374.0</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>509</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>13.15</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7753,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-36.19</t>
+          <t>-45.61</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-21.39</t>
+          <t>-23.12</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,12 +7894,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7914,34 +7914,34 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>13.62</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>13.98</v>
+        <v>13.95</v>
       </c>
       <c r="AN18" t="n">
-        <v>14.71</v>
+        <v>14.64</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -7950,17 +7950,17 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-110.37</t>
+          <t>-110.56</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>7350.869784172662</t>
+          <t>7341.631465517241</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>374.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>381</v>
+        <v>340.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>597.1</t>
+          <t>625.9</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>630.02</v>
+        <v>605.1799999999999</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-216</t>
+          <t>-285</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-4.501767971475612</t>
+          <t>-6.68914334802669</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-9.46596609956589</t>
+          <t>-18.71970791905761</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>374.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>509</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
+          <t>13.6</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
           <t>13.65</t>
         </is>
       </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>13.95</t>
-        </is>
-      </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>13.15</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>-36.19</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,12 +8324,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8339,58 +8339,58 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>14</v>
+        <v>13.98</v>
       </c>
       <c r="AN19" t="n">
-        <v>14.79</v>
+        <v>14.71</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-110.48</t>
+          <t>-110.37</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>7350.869784172662</t>
+          <t>7341.631465517241</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>276.0</t>
+          <t>573.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>643.8</v>
+        <v>381</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>572.3</t>
+          <t>597.1</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>643.84</v>
+        <v>630.02</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>-216</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-3.599186493641016</t>
+          <t>-4.501767971475612</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-17.22969328245046</t>
+          <t>-9.46596609956589</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>276.0</t>
+          <t>573.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>509</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.95</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>16.38</t>
+          <t>12.49</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-21.10</t>
+          <t>-21.39</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8769,39 +8769,39 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>14.03</t>
         </is>
       </c>
       <c r="AM20" t="n">
         <v>14</v>
       </c>
       <c r="AN20" t="n">
-        <v>14.87</v>
+        <v>14.79</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>21.76</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-110.76</t>
+          <t>-110.48</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>7350.869784172662</t>
+          <t>7341.631465517241</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>276.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>655.2</v>
+        <v>643.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>572.3</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>675</v>
+        <v>643.84</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-1.120912532039299</t>
+          <t>-3.599186493641016</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>4.116042644944969</t>
+          <t>-17.22969328245046</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>276.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,12 +8941,12 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>509</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>13.95</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>70.35</t>
+          <t>16.38</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-19.36</t>
+          <t>-21.10</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-6.17</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>14.17</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>14.02</v>
+        <v>14</v>
       </c>
       <c r="AN21" t="n">
-        <v>14.94</v>
+        <v>14.87</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>15.13</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>35.24</t>
+          <t>21.76</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-111.35</t>
+          <t>-110.76</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>7350.869784172662</t>
+          <t>7341.631465517241</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>314.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>963</v>
+        <v>655.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>565.3</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>734.12</v>
+        <v>675</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>92</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-2.073086200581893</t>
+          <t>-1.120912532039299</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>46.35580673247603</t>
+          <t>4.116042644944969</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>314.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,17 +9371,17 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>509</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>13.95</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>13.95</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>13.95</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-6.74</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>57.03</t>
+          <t>70.35</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-17.63</t>
+          <t>-19.36</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,63 +9614,63 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-6.69</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>14.22</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AM22" t="n">
         <v>14.02</v>
       </c>
       <c r="AN22" t="n">
-        <v>15.03</v>
+        <v>14.94</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>15.12</t>
+          <t>15.13</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>35.24</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
@@ -9680,7 +9680,7 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-112.35</t>
+          <t>-111.35</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>7350.869784172662</t>
+          <t>7341.631465517241</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>577.0</t>
+          <t>314.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>911.4</v>
+        <v>963</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>580.4</t>
+          <t>565.3</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>762.26</v>
+        <v>734.12</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>397</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-10.87833946113788</t>
+          <t>-2.073086200581893</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>89.0784766170749</t>
+          <t>46.35580673247603</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>577.0</t>
+          <t>314.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>509</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>13.95</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>13.95</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-10.11</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>44.90</t>
+          <t>57.03</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-15.03</t>
+          <t>-17.63</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-7.13</t>
+          <t>-6.69</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>14.13</t>
+          <t>14.22</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>14.03</v>
+        <v>14.02</v>
       </c>
       <c r="AN23" t="n">
-        <v>15.11</v>
+        <v>15.03</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>15.12</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>40.16</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-113.64</t>
+          <t>-112.35</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>7350.869784172662</t>
+          <t>7341.631465517241</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1887.0</t>
+          <t>577.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>813.2</v>
+        <v>911.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>561.2</t>
+          <t>580.4</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>794.04</v>
+        <v>762.26</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>331</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-29.05230602081294</t>
+          <t>-10.87833946113788</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>118.7509165730348</t>
+          <t>89.0784766170749</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>1887.0</t>
+          <t>577.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>509</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
+          <t>14.7</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
+          <t>14.7</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
+          <t>14.2</t>
+        </is>
+      </c>
+      <c r="CG23" t="inlineStr">
+        <is>
           <t>14.25</t>
-        </is>
-      </c>
-      <c r="CE23" t="inlineStr">
-        <is>
-          <t>15.5</t>
-        </is>
-      </c>
-      <c r="CF23" t="inlineStr">
-        <is>
-          <t>14.25</t>
-        </is>
-      </c>
-      <c r="CG23" t="inlineStr">
-        <is>
-          <t>14.7</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10343,12 +10343,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1052.554</t>
+          <t>652.267</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-26.38</t>
+          <t>-30.44</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10453,17 +10453,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -10474,12 +10474,12 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>652</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -10489,53 +10489,53 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>48.28</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>34.39</t>
+          <t>34.47</t>
         </is>
       </c>
       <c r="AM24" t="n">
-        <v>36.08</v>
+        <v>35.98</v>
       </c>
       <c r="AN24" t="n">
-        <v>38.92</v>
+        <v>38.91</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>37.67</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
@@ -10550,53 +10550,53 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>-132.25</t>
+          <t>-132.19</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2025/11/10</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>233186776.6014389</t>
+          <t>232900527.4525862</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>36488624.0</t>
+          <t>22638246.0</t>
         </is>
       </c>
       <c r="AX24" t="n">
-        <v>37237782</v>
+        <v>32529604.8</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>50581063.8</t>
+          <t>46763411.2</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>242256442.44</v>
+        <v>241442940.72</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>-13343281</t>
+          <t>-14233806</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>-22914581.90439074</t>
+          <t>-22333152.53566639</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-19529368.76453082</t>
+          <t>-19135291.00768245</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>36488624.0</t>
+          <t>22638246.0</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="BY24" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ24" t="inlineStr">
@@ -10726,17 +10726,17 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
@@ -10773,12 +10773,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1012.048</t>
+          <t>1052.554</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -10798,17 +10798,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-30.50</t>
+          <t>-26.38</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -10873,7 +10873,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -10883,17 +10883,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -10904,73 +10904,73 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>652</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>48.21</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>48.28</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>34.41</t>
+          <t>34.39</t>
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>36.18</v>
+        <v>36.08</v>
       </c>
       <c r="AN25" t="n">
-        <v>38.94</v>
+        <v>38.92</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>37.63</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -10980,53 +10980,53 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>-131.94</t>
+          <t>-132.25</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2025/11/10</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>233186776.6014389</t>
+          <t>232900527.4525862</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>35345556.0</t>
+          <t>36488624.0</t>
         </is>
       </c>
       <c r="AX25" t="n">
-        <v>37074921.8</v>
+        <v>37237782</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>53345322.1</t>
+          <t>50581063.8</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>245778298.12</v>
+        <v>242256442.44</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>-16270400</t>
+          <t>-13343281</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>-23530075.2025471</t>
+          <t>-22914581.90439074</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-20878828.60415238</t>
+          <t>-19529368.76453082</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>35345556.0</t>
+          <t>36488624.0</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -11046,7 +11046,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
@@ -11091,17 +11091,17 @@
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS25" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="BT25" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="BY25" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ25" t="inlineStr">
@@ -11156,22 +11156,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -11203,12 +11203,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>857.193</t>
+          <t>1012.048</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -11228,17 +11228,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-31.65</t>
+          <t>-30.50</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-7.55</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -11313,17 +11313,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -11334,73 +11334,73 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>652</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>48.21</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>10.92</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>34.16</t>
+          <t>34.41</t>
         </is>
       </c>
       <c r="AM26" t="n">
-        <v>36.33</v>
+        <v>36.18</v>
       </c>
       <c r="AN26" t="n">
-        <v>39</v>
+        <v>38.94</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>37.52</t>
+          <t>37.58</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -11410,53 +11410,53 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>-131.18</t>
+          <t>-131.94</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2025/11/10</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>233186776.6014389</t>
+          <t>232900527.4525862</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>29401532.0</t>
+          <t>35345556.0</t>
         </is>
       </c>
       <c r="AX26" t="n">
-        <v>39796395.2</v>
+        <v>37074921.8</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>58228190.4</t>
+          <t>53345322.1</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>247556548.26</v>
+        <v>245778298.12</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>-18431795</t>
+          <t>-16270400</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>-24012120.03861886</t>
+          <t>-23530075.2025471</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-21938484.35346347</t>
+          <t>-20878828.60415238</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>29401532.0</t>
+          <t>35345556.0</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -11521,17 +11521,17 @@
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS26" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BT26" t="inlineStr">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="BY26" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ26" t="inlineStr">
@@ -11586,22 +11586,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -11633,12 +11633,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1145.3</t>
+          <t>857.193</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>33.65</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11658,17 +11658,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-25.49</t>
+          <t>-31.65</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-9.30</t>
+          <t>-7.55</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -11743,17 +11743,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -11764,73 +11764,73 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>652</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>10.92</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>-6.49</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>34.11999999999999</t>
+          <t>34.16</t>
         </is>
       </c>
       <c r="AM27" t="n">
-        <v>36.49</v>
+        <v>36.33</v>
       </c>
       <c r="AN27" t="n">
-        <v>39.06</v>
+        <v>39</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>37.47</t>
+          <t>37.52</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>-26.04</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -11840,53 +11840,53 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>-129.70</t>
+          <t>-131.18</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2025/11/10</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>233186776.6014389</t>
+          <t>232900527.4525862</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>38774066.0</t>
+          <t>29401532.0</t>
         </is>
       </c>
       <c r="AX27" t="n">
-        <v>49474507.6</v>
+        <v>39796395.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>66401056.1</t>
+          <t>58228190.4</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>249662887.18</v>
+        <v>247556548.26</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>-16926548</t>
+          <t>-18431795</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>-24389144.70864711</t>
+          <t>-24012120.03861886</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-22031901.26842704</t>
+          <t>-21938484.35346347</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>38774066.0</t>
+          <t>29401532.0</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="BS27" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="BT27" t="inlineStr">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="BY27" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ27" t="inlineStr">
@@ -12016,22 +12016,22 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.55</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>33.65</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1345.621</t>
+          <t>1145.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>33.65</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -12088,17 +12088,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-27.63</t>
+          <t>-25.49</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-7.55</t>
+          <t>-9.30</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -12173,17 +12173,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -12194,17 +12194,17 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>652</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>13.92</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
@@ -12224,43 +12224,43 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-6.2</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>34.33</t>
+          <t>34.11999999999999</t>
         </is>
       </c>
       <c r="AM28" t="n">
-        <v>36.71</v>
+        <v>36.49</v>
       </c>
       <c r="AN28" t="n">
-        <v>39.14</v>
+        <v>39.06</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>37.43</t>
+          <t>37.47</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>-27.70</t>
+          <t>-26.04</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -12270,53 +12270,53 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>-127.76</t>
+          <t>-129.70</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2025/11/10</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>233186776.6014389</t>
+          <t>232900527.4525862</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>46179132.0</t>
+          <t>38774066.0</t>
         </is>
       </c>
       <c r="AX28" t="n">
-        <v>60997217.6</v>
+        <v>49474507.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>84286762.5</t>
+          <t>66401056.1</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>254822433.06</v>
+        <v>249662887.18</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>-23289544</t>
+          <t>-16926548</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>-24817734.42505076</t>
+          <t>-24389144.70864711</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-22382700.45878832</t>
+          <t>-22031901.26842704</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>46179132.0</t>
+          <t>38774066.0</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -12391,7 +12391,7 @@
       </c>
       <c r="BS28" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="BT28" t="inlineStr">
@@ -12421,7 +12421,7 @@
       </c>
       <c r="BY28" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ28" t="inlineStr">
@@ -12446,22 +12446,22 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>34.05</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>33.65</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -12493,12 +12493,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1029.736</t>
+          <t>1345.621</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -12518,102 +12518,102 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>-27.63</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>37.7</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>37.1</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>41.9</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>42.55</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>-7.55</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>-11.40</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
           <t>-0.12</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>-32.40</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>37.7</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>37.1</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>42.55</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>-6.20</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>-11.40</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>1.47</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -12624,73 +12624,73 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>652</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>13.92</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-6.49</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-6.2</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>34.33</t>
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>36.88</v>
+        <v>36.71</v>
       </c>
       <c r="AN29" t="n">
-        <v>39.24</v>
+        <v>39.14</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>37.43</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>-32.46</t>
+          <t>-27.70</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -12700,53 +12700,53 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>-125.84</t>
+          <t>-127.76</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2025/11/10</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>233186776.6014389</t>
+          <t>232900527.4525862</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>35674323.0</t>
+          <t>46179132.0</t>
         </is>
       </c>
       <c r="AX29" t="n">
-        <v>63924345.6</v>
+        <v>60997217.6</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>94556424.4</t>
+          <t>84286762.5</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>256700200.08</v>
+        <v>254822433.06</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>-30632078</t>
+          <t>-23289544</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>-25260467.87346211</t>
+          <t>-24817734.42505076</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>-22877859.92863344</t>
+          <t>-22382700.45878832</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>35674323.0</t>
+          <t>46179132.0</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS29" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="BT29" t="inlineStr">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="BY29" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ29" t="inlineStr">
@@ -12876,22 +12876,22 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.05</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>34.85</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1450.779</t>
+          <t>1029.736</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -12938,7 +12938,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -12948,17 +12948,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-37.05</t>
+          <t>-32.40</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -13023,7 +13023,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-9.03</t>
+          <t>-6.20</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -13033,17 +13033,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -13054,73 +13054,73 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>652</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>35.22000000000001</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AM30" t="n">
-        <v>37.06</v>
+        <v>36.88</v>
       </c>
       <c r="AN30" t="n">
-        <v>39.33</v>
+        <v>39.24</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>37.33</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>-41.33</t>
+          <t>-32.46</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -13130,53 +13130,53 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>-123.74</t>
+          <t>-125.84</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2025/11/10</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>233186776.6014389</t>
+          <t>232900527.4525862</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>48952923.0</t>
+          <t>35674323.0</t>
         </is>
       </c>
       <c r="AX30" t="n">
-        <v>69615722.40000001</v>
+        <v>63924345.6</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>110580229.2</t>
+          <t>94556424.4</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>258176781.58</v>
+        <v>256700200.08</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>-40964506</t>
+          <t>-30632078</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>-25693669.31797642</t>
+          <t>-25260467.87346211</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>-21642648.9238181</t>
+          <t>-22877859.92863344</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>48952923.0</t>
+          <t>35674323.0</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
@@ -13196,7 +13196,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -13241,17 +13241,17 @@
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS30" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="BT30" t="inlineStr">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="BY30" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ30" t="inlineStr">
@@ -13306,22 +13306,22 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2260.366</t>
+          <t>1450.779</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -13378,17 +13378,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-32.59</t>
+          <t>-37.05</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-8.09</t>
+          <t>-9.03</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -13463,17 +13463,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -13484,12 +13484,12 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>652</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -13504,53 +13504,53 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>36.01000000000001</t>
+          <t>35.22000000000001</t>
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>37.29</v>
+        <v>37.06</v>
       </c>
       <c r="AN31" t="n">
-        <v>39.43</v>
+        <v>39.33</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.33</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>-37.57</t>
+          <t>-41.33</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -13560,53 +13560,53 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>-121.29</t>
+          <t>-123.74</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2025/11/10</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>233186776.6014389</t>
+          <t>232900527.4525862</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>77792094.0</t>
+          <t>48952923.0</t>
         </is>
       </c>
       <c r="AX31" t="n">
-        <v>76659985.59999999</v>
+        <v>69615722.40000001</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>113715310.1</t>
+          <t>110580229.2</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>261926998.4</v>
+        <v>258176781.58</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>-37055324</t>
+          <t>-40964506</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>-26430218.48055065</t>
+          <t>-25693669.31797642</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>-20527817.16965982</t>
+          <t>-21642648.9238181</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>77792094.0</t>
+          <t>48952923.0</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -13671,7 +13671,7 @@
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="BS31" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="BT31" t="inlineStr">
@@ -13711,7 +13711,7 @@
       </c>
       <c r="BY31" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ31" t="inlineStr">
@@ -13736,22 +13736,22 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>35.25</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -13783,12 +13783,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2726.249</t>
+          <t>2260.366</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -13798,7 +13798,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13808,17 +13808,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-25.83</t>
+          <t>-32.59</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-6.47</t>
+          <t>-8.09</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -13893,17 +13893,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>-6.20</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -13914,12 +13914,12 @@
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>652</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -13929,58 +13929,58 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>36.59</t>
+          <t>36.01000000000001</t>
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>37.52</v>
+        <v>37.29</v>
       </c>
       <c r="AN32" t="n">
-        <v>39.54</v>
+        <v>39.43</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>37.26</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>-26.44</t>
+          <t>-37.57</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
@@ -13990,53 +13990,53 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>-119.29</t>
+          <t>-121.29</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2025/11/10</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>233186776.6014389</t>
+          <t>232900527.4525862</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>96387616.0</t>
+          <t>77792094.0</t>
         </is>
       </c>
       <c r="AX32" t="n">
-        <v>83327604.59999999</v>
+        <v>76659985.59999999</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>112354225.4</t>
+          <t>113715310.1</t>
         </is>
       </c>
       <c r="AZ32" t="n">
-        <v>263764100.2</v>
+        <v>261926998.4</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>-29026620</t>
+          <t>-37055324</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>-27503382.35525808</t>
+          <t>-26430218.48055065</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>-21291975.22908874</t>
+          <t>-20527817.16965982</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>96387616.0</t>
+          <t>77792094.0</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="BS32" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="BT32" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="BY32" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ32" t="inlineStr">
@@ -14166,22 +14166,22 @@
       </c>
       <c r="CD32" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>35.25</t>
         </is>
       </c>
       <c r="CF32" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="CG32" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CH32" t="inlineStr">
@@ -14213,12 +14213,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1669.175</t>
+          <t>2726.249</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -14238,17 +14238,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-25.83</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -14323,17 +14323,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-6.20</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -14344,12 +14344,12 @@
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>652</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -14359,58 +14359,58 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-5.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>37.36</t>
+          <t>36.59</t>
         </is>
       </c>
       <c r="AM33" t="n">
-        <v>37.67</v>
+        <v>37.52</v>
       </c>
       <c r="AN33" t="n">
-        <v>39.63</v>
+        <v>39.54</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>37.21</t>
+          <t>37.26</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>-7.99</t>
+          <t>-26.44</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -14420,53 +14420,53 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>-118.02</t>
+          <t>-119.29</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2025/11/10</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>233186776.6014389</t>
+          <t>232900527.4525862</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>60814772.0</t>
+          <t>96387616.0</t>
         </is>
       </c>
       <c r="AX33" t="n">
-        <v>107576307.4</v>
+        <v>83327604.59999999</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>111580509.9</t>
+          <t>112354225.4</t>
         </is>
       </c>
       <c r="AZ33" t="n">
-        <v>267374187.92</v>
+        <v>263764100.2</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>-4004202</t>
+          <t>-29026620</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>-28632729.10547069</t>
+          <t>-27503382.35525808</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>-23615579.27009116</t>
+          <t>-21291975.22908874</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>60814772.0</t>
+          <t>96387616.0</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
@@ -14486,7 +14486,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR33" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
@@ -14571,7 +14571,7 @@
       </c>
       <c r="BY33" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ33" t="inlineStr">
@@ -14601,17 +14601,17 @@
       </c>
       <c r="CE33" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CF33" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="CG33" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="CH33" t="inlineStr">
@@ -14643,12 +14643,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1717.738</t>
+          <t>1669.175</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14658,72 +14658,72 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>36.45</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-5.04</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>-3.59</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>37.7</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
           <t>37.1</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>-6.92</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>12.67</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>37.7</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>37.1</t>
-        </is>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -14738,12 +14738,12 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -14753,17 +14753,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -14774,73 +14774,73 @@
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>652</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>28.16</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>37.79</t>
+          <t>37.36</t>
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>37.84</v>
+        <v>37.67</v>
       </c>
       <c r="AN34" t="n">
-        <v>39.68</v>
+        <v>39.63</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>37.21</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-7.99</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
@@ -14850,58 +14850,58 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>-117.66</t>
+          <t>-118.02</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2025/11/10</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>233186776.6014389</t>
+          <t>232900527.4525862</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>64131207.0</t>
+          <t>60814772.0</t>
         </is>
       </c>
       <c r="AX34" t="n">
-        <v>125188503.2</v>
+        <v>107576307.4</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>111110160.4</t>
+          <t>111580509.9</t>
         </is>
       </c>
       <c r="AZ34" t="n">
-        <v>270632048.46</v>
+        <v>267374187.92</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>14078342</t>
+          <t>-4004202</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>-29544938.16644878</t>
+          <t>-28632729.10547069</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>-22280223.92616281</t>
+          <t>-23615579.27009116</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>64131207.0</t>
+          <t>60814772.0</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
@@ -14961,7 +14961,7 @@
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
@@ -14971,7 +14971,7 @@
       </c>
       <c r="BS34" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BT34" t="inlineStr">
@@ -15001,7 +15001,7 @@
       </c>
       <c r="BY34" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ34" t="inlineStr">
@@ -15026,22 +15026,22 @@
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="CE34" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CF34" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CG34" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.45</t>
         </is>
       </c>
       <c r="CH34" t="inlineStr">

--- a/Result/checksun_type/玻璃基板.xlsx
+++ b/Result/checksun_type/玻璃基板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>129.907</t>
+          <t>57.864</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.82</t>
+          <t>-11.61</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,63 +1014,63 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>50.45</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>26.04</v>
+        <v>25.88</v>
       </c>
       <c r="AN2" t="n">
-        <v>26.79</v>
+        <v>26.78</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>25.92</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-23.75</t>
+          <t>-18.27</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-117.83</t>
+          <t>-118.69</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>60949966.30527817</t>
+          <t>60866201.53205129</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3250406.0</t>
+          <t>1431397.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2820044.4</v>
+        <v>2725616.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3938171.4</t>
+          <t>3344499.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>10185422.26</v>
+        <v>10170725.72</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1118127</t>
+          <t>-618883</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1456770.746041259</t>
+          <t>-1441986.883569631</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1364005.379429155</t>
+          <t>-1360675.639975678</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>3250406.0</t>
+          <t>1431397.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>44.221</t>
+          <t>129.907</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-32.35</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-10.89</t>
+          <t>-9.82</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>26.18</v>
+        <v>26.04</v>
       </c>
       <c r="AN3" t="n">
-        <v>26.78</v>
+        <v>26.79</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-39.44</t>
+          <t>-23.75</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-116.78</t>
+          <t>-117.83</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>60949966.30527817</t>
+          <t>60866201.53205129</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1105744.0</t>
+          <t>3250406.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2762517</v>
+        <v>2820044.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4083544.5</t>
+          <t>3938171.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>10163096.92</v>
+        <v>10185422.26</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1321027</t>
+          <t>-1118127</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1473637.176334369</t>
+          <t>-1456770.746041259</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1514941.493668794</t>
+          <t>-1364005.379429155</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1105744.0</t>
+          <t>3250406.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>132.605</t>
+          <t>44.221</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-21.31</t>
+          <t>-32.35</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-11.07</t>
+          <t>-10.89</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>24.68</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>26.38</v>
+        <v>26.18</v>
       </c>
       <c r="AN4" t="n">
         <v>26.78</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-56.92</t>
+          <t>-39.44</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-115.12</t>
+          <t>-116.78</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>60949966.30527817</t>
+          <t>60866201.53205129</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3298659.0</t>
+          <t>1105744.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3409647.6</v>
+        <v>2762517</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>4333083.4</t>
+          <t>4083544.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>10178782.26</v>
+        <v>10163096.92</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-923435</t>
+          <t>-1321027</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1466127.300455383</t>
+          <t>-1473637.176334369</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1446674.246380107</t>
+          <t>-1514941.493668794</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>3298659.0</t>
+          <t>1105744.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>182.531</t>
+          <t>132.605</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-11.85</t>
+          <t>-21.31</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-11.96</t>
+          <t>-11.07</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>24.78</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>26.62</v>
+        <v>26.38</v>
       </c>
       <c r="AN5" t="n">
-        <v>26.79</v>
+        <v>26.78</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-82.30</t>
+          <t>-56.92</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-112.97</t>
+          <t>-115.12</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>60949966.30527817</t>
+          <t>60866201.53205129</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4541875.0</t>
+          <t>3298659.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3888772.8</v>
+        <v>3409647.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4411562.6</t>
+          <t>4333083.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>10182869.32</v>
+        <v>10178782.26</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-522789</t>
+          <t>-923435</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1469664.21937816</t>
+          <t>-1466127.300455383</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1532437.84859698</t>
+          <t>-1446674.246380107</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>4541875.0</t>
+          <t>3298659.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>77.947</t>
+          <t>182.531</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-25.48</t>
+          <t>-11.85</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-13.04</t>
+          <t>-11.96</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-7.50</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.67</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>26.86</v>
+        <v>26.62</v>
       </c>
       <c r="AN6" t="n">
         <v>26.79</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>25.87</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-116.96</t>
+          <t>-82.30</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-110.30</t>
+          <t>-112.97</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>60949966.30527817</t>
+          <t>60866201.53205129</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1903538.0</t>
+          <t>4541875.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3963383.6</v>
+        <v>3888772.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>5318222.8</t>
+          <t>4411562.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>10129541.2</v>
+        <v>10182869.32</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1354839</t>
+          <t>-522789</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1458250.832247465</t>
+          <t>-1469664.21937816</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1733429.071456906</t>
+          <t>-1532437.84859698</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1903538.0</t>
+          <t>4541875.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>121.223</t>
+          <t>77.947</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-25.48</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-12.32</t>
+          <t>-13.04</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,17 +3164,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,53 +3184,53 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-7.61</t>
+          <t>-7.50</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>27.22</v>
+        <v>26.86</v>
       </c>
       <c r="AN7" t="n">
-        <v>26.8</v>
+        <v>26.79</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>25.87</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-165.59</t>
+          <t>-116.96</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-107.29</t>
+          <t>-110.30</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>60949966.30527817</t>
+          <t>60866201.53205129</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2962769.0</t>
+          <t>1903538.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>5056298.4</v>
+        <v>3963383.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>5511802.7</t>
+          <t>5318222.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>10116244</v>
+        <v>10129541.2</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-455504</t>
+          <t>-1354839</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1408218.425118476</t>
+          <t>-1458250.832247465</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1675972.244419054</t>
+          <t>-1733429.071456906</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2962769.0</t>
+          <t>1903538.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>171.268</t>
+          <t>121.223</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-9.11</t>
+          <t>-12.32</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,54 +3594,54 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-7.61</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>27.43</v>
+        <v>27.22</v>
       </c>
       <c r="AN8" t="n">
-        <v>26.81</v>
+        <v>26.8</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3650,17 +3650,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-273.08</t>
+          <t>-165.59</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.27</t>
+          <t>-107.29</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>60949966.30527817</t>
+          <t>60866201.53205129</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>4341397.0</t>
+          <t>2962769.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>5404572</v>
+        <v>5056298.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>5443936.9</t>
+          <t>5511802.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>10090356.22</v>
+        <v>10116244</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-39364</t>
+          <t>-455504</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1359535.912518371</t>
+          <t>-1408218.425118476</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1647523.947064298</t>
+          <t>-1675972.244419054</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>4341397.0</t>
+          <t>2962769.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>229.109</t>
+          <t>171.268</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-13.04</t>
+          <t>-9.11</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>27.58</v>
+        <v>27.43</v>
       </c>
       <c r="AN9" t="n">
         <v>26.81</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>25.84</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-960.20</t>
+          <t>-273.08</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-101.36</t>
+          <t>-104.27</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>60949966.30527817</t>
+          <t>60866201.53205129</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>5694285.0</t>
+          <t>4341397.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>5256519.2</v>
+        <v>5404572</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5382212.9</t>
+          <t>5443936.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>10042035.4</v>
+        <v>10090356.22</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-125693</t>
+          <t>-39364</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1307174.451691839</t>
+          <t>-1359535.912518371</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1695753.524162351</t>
+          <t>-1647523.947064298</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>5694285.0</t>
+          <t>4341397.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>194.645</t>
+          <t>229.109</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-13.04</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,39 +4469,39 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>27.77</v>
+        <v>27.58</v>
       </c>
       <c r="AN10" t="n">
-        <v>26.82</v>
+        <v>26.81</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4510,17 +4510,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-545.29</t>
+          <t>-960.20</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-98.10</t>
+          <t>-101.36</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>60949966.30527817</t>
+          <t>60866201.53205129</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>4914929.0</t>
+          <t>5694285.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>4934352.4</v>
+        <v>5256519.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5195209.4</t>
+          <t>5382212.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>9975089.699999999</v>
+        <v>10042035.4</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-260857</t>
+          <t>-125693</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1236523.711242655</t>
+          <t>-1307174.451691839</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1849042.579868057</t>
+          <t>-1695753.524162351</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>4914929.0</t>
+          <t>5694285.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>282.054</t>
+          <t>194.645</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>26.70</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>16.15</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>26.72</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>27.84</v>
+        <v>27.77</v>
       </c>
       <c r="AN11" t="n">
-        <v>26.81</v>
+        <v>26.82</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>25.84</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-207.53</t>
+          <t>-545.29</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-95.51</t>
+          <t>-98.10</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>60949966.30527817</t>
+          <t>60866201.53205129</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>7368112.0</t>
+          <t>4914929.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>6673062</v>
+        <v>4934352.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5266881.5</t>
+          <t>5195209.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>9924938.880000001</v>
+        <v>9975089.699999999</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1406180</t>
+          <t>-260857</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1125156.644219854</t>
+          <t>-1236523.711242655</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1918487.281595205</t>
+          <t>-1849042.579868057</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>7368112.0</t>
+          <t>4914929.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>175.583</t>
+          <t>282.054</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-4.44</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15.71</t>
+          <t>26.70</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>10.39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>16.15</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>26.72</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>27.87</v>
+        <v>27.84</v>
       </c>
       <c r="AN12" t="n">
-        <v>26.79</v>
+        <v>26.81</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>25.83</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-116.63</t>
+          <t>-207.53</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-93.19</t>
+          <t>-95.51</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>60949966.30527817</t>
+          <t>60866201.53205129</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>4704137.0</t>
+          <t>7368112.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>5967307</v>
+        <v>6673062</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5157190.6</t>
+          <t>5266881.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>9855538.880000001</v>
+        <v>9924938.880000001</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>810116</t>
+          <t>1406180</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-980914.7101516086</t>
+          <t>-1125156.644219854</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-2212017.631148446</t>
+          <t>-1918487.281595205</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>4704137.0</t>
+          <t>7368112.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,63 +5749,63 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>60.36</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.83</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>13.77</v>
+        <v>13.74</v>
       </c>
       <c r="AN13" t="n">
-        <v>14.31</v>
+        <v>14.28</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -5820,53 +5820,53 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-112.36</t>
+          <t>-112.32</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2025/10/29</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>7341.631465517241</t>
+          <t>7331.307030129125</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>507.6</v>
+        <v>472.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>424.0</t>
+          <t>402.3</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>517.4400000000001</v>
+        <v>481.38</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-7.653303500733839</t>
+          <t>-10.83001914489146</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>3.719440554195444</t>
+          <t>-28.30195518775838</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -5996,17 +5996,17 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6043,42 +6043,42 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>13.45</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>13.35</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0.74</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-22.83</t>
+          <t>-22.25</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,49 +6179,49 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>13.8</v>
+        <v>13.77</v>
       </c>
       <c r="AN14" t="n">
-        <v>14.35</v>
+        <v>14.31</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6230,12 +6230,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -6250,53 +6250,53 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-112.26</t>
+          <t>-112.36</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2025/10/29</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>7341.631465517241</t>
+          <t>7331.307030129125</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>459.6</v>
+        <v>507.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>420.3</t>
+          <t>424.0</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>554.86</v>
+        <v>517.4400000000001</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-9.721075147084617</t>
+          <t>-7.653303500733839</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-6.061402691377396</t>
+          <t>3.719440554195444</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-4.30</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-9.92</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,49 +6609,49 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.83</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>13.83</v>
+        <v>13.8</v>
       </c>
       <c r="AN15" t="n">
-        <v>14.41</v>
+        <v>14.35</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6660,17 +6660,17 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-12.91</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,53 +6680,53 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-111.98</t>
+          <t>-112.26</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2025/10/29</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>7341.631465517241</t>
+          <t>7331.307030129125</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>1213.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>527.6</v>
+        <v>459.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>585.7</t>
+          <t>420.3</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>567.6799999999999</v>
+        <v>554.86</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-58</t>
+          <t>39</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-10.38647013903138</t>
+          <t>-9.721075147084617</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>21.00387133963898</t>
+          <t>-6.061402691377396</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>1213.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-31.65</t>
+          <t>-9.92</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,49 +7039,49 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>13.86</v>
+        <v>13.83</v>
       </c>
       <c r="AN16" t="n">
-        <v>14.48</v>
+        <v>14.41</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-16.60</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,53 +7110,53 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-111.60</t>
+          <t>-111.98</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2025/10/29</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>7341.631465517241</t>
+          <t>7331.307030129125</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>1213.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>340.2</v>
+        <v>527.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>497.7</t>
+          <t>585.7</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>555.26</v>
+        <v>567.6799999999999</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-157</t>
+          <t>-58</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-16.09380495333509</t>
+          <t>-10.38647013903138</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-46.08158973532466</t>
+          <t>21.00387133963898</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>1213.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,12 +7221,12 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7286,17 +7286,17 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-48.73</t>
+          <t>-31.65</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-24.86</t>
+          <t>-22.83</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,49 +7469,49 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>13.43</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>13.9</v>
+        <v>13.86</v>
       </c>
       <c r="AN17" t="n">
-        <v>14.55</v>
+        <v>14.48</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7520,17 +7520,17 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-19.79</t>
+          <t>-16.60</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,53 +7540,53 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-111.11</t>
+          <t>-111.60</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2025/10/29</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>7341.631465517241</t>
+          <t>7331.307030129125</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>332</v>
+        <v>340.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>647.5</t>
+          <t>497.7</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>577.0599999999999</v>
+        <v>555.26</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-315</t>
+          <t>-157</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-10.6414804475188</t>
+          <t>-16.09380495333509</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-32.37933449472541</t>
+          <t>-46.08158973532466</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-4.30</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
+          <t>12.9</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
           <t>13.4</t>
         </is>
       </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>13.55</t>
-        </is>
-      </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-45.61</t>
+          <t>-48.73</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-23.12</t>
+          <t>-24.86</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7914,34 +7914,34 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-3.20</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>13.62</t>
+          <t>13.43</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>13.95</v>
+        <v>13.9</v>
       </c>
       <c r="AN18" t="n">
-        <v>14.64</v>
+        <v>14.55</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -7950,17 +7950,17 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-19.79</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,53 +7970,53 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-110.56</t>
+          <t>-111.11</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2025/10/29</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>7341.631465517241</t>
+          <t>7331.307030129125</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>374.0</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>340.4</v>
+        <v>332</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>625.9</t>
+          <t>647.5</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>605.1799999999999</v>
+        <v>577.0599999999999</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-285</t>
+          <t>-315</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-6.68914334802669</t>
+          <t>-10.6414804475188</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-18.71970791905761</t>
+          <t>-32.37933449472541</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>374.0</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>13.15</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8183,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-36.19</t>
+          <t>-45.61</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-21.39</t>
+          <t>-23.12</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8344,34 +8344,34 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>13.62</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>13.98</v>
+        <v>13.95</v>
       </c>
       <c r="AN19" t="n">
-        <v>14.71</v>
+        <v>14.64</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8380,17 +8380,17 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,53 +8400,53 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-110.37</t>
+          <t>-110.56</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2025/10/29</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>7341.631465517241</t>
+          <t>7331.307030129125</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>374.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>381</v>
+        <v>340.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>597.1</t>
+          <t>625.9</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>630.02</v>
+        <v>605.1799999999999</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-216</t>
+          <t>-285</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-4.501767971475612</t>
+          <t>-6.68914334802669</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-9.46596609956589</t>
+          <t>-18.71970791905761</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>374.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
+          <t>13.6</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
           <t>13.65</t>
         </is>
       </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>13.95</t>
-        </is>
-      </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>13.15</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>-36.19</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8769,58 +8769,58 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>14</v>
+        <v>13.98</v>
       </c>
       <c r="AN20" t="n">
-        <v>14.79</v>
+        <v>14.71</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,53 +8830,53 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-110.48</t>
+          <t>-110.37</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2025/10/29</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>7341.631465517241</t>
+          <t>7331.307030129125</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>276.0</t>
+          <t>573.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>643.8</v>
+        <v>381</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>572.3</t>
+          <t>597.1</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>643.84</v>
+        <v>630.02</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>-216</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-3.599186493641016</t>
+          <t>-4.501767971475612</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-17.22969328245046</t>
+          <t>-9.46596609956589</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>276.0</t>
+          <t>573.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,12 +8941,12 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.95</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>16.38</t>
+          <t>12.49</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-21.10</t>
+          <t>-21.39</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9199,39 +9199,39 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>14.03</t>
         </is>
       </c>
       <c r="AM21" t="n">
         <v>14</v>
       </c>
       <c r="AN21" t="n">
-        <v>14.87</v>
+        <v>14.79</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9240,12 +9240,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>21.76</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
@@ -9260,53 +9260,53 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-110.76</t>
+          <t>-110.48</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2025/10/29</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>7341.631465517241</t>
+          <t>7331.307030129125</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>276.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>655.2</v>
+        <v>643.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>572.3</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>675</v>
+        <v>643.84</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-1.120912532039299</t>
+          <t>-3.599186493641016</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>4.116042644944969</t>
+          <t>-17.22969328245046</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>276.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9436,12 +9436,12 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>13.95</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>70.35</t>
+          <t>16.38</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-19.36</t>
+          <t>-21.10</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,68 +9619,68 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-6.17</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>14.17</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>14.02</v>
+        <v>14</v>
       </c>
       <c r="AN22" t="n">
-        <v>14.94</v>
+        <v>14.87</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>15.13</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>35.24</t>
+          <t>21.76</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,53 +9690,53 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-111.35</t>
+          <t>-110.76</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2025/10/29</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>7341.631465517241</t>
+          <t>7331.307030129125</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>314.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>963</v>
+        <v>655.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>565.3</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>734.12</v>
+        <v>675</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>92</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-2.073086200581893</t>
+          <t>-1.120912532039299</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>46.35580673247603</t>
+          <t>4.116042644944969</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>314.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>13.95</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>13.95</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>13.95</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>57.03</t>
+          <t>70.35</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-17.63</t>
+          <t>-19.36</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,58 +10049,58 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-6.69</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>14.22</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AM23" t="n">
         <v>14.02</v>
       </c>
       <c r="AN23" t="n">
-        <v>15.03</v>
+        <v>14.94</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>15.12</t>
+          <t>15.13</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>35.24</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,53 +10120,53 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-112.35</t>
+          <t>-111.35</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2025/10/29</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>7341.631465517241</t>
+          <t>7331.307030129125</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>577.0</t>
+          <t>314.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>911.4</v>
+        <v>963</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>580.4</t>
+          <t>565.3</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>762.26</v>
+        <v>734.12</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>397</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-10.87833946113788</t>
+          <t>-2.073086200581893</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>89.0784766170749</t>
+          <t>46.35580673247603</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>577.0</t>
+          <t>314.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>13.95</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>13.95</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10343,42 +10343,42 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>-2.01</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>797.737</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>652.267</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>34.7</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-30.44</t>
+          <t>-24.16</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-6.47</t>
+          <t>-8.36</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -10453,17 +10453,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -10479,58 +10479,58 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>798</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>60.49</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-7.74</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>34.47</t>
+          <t>34.54</t>
         </is>
       </c>
       <c r="AM24" t="n">
-        <v>35.98</v>
+        <v>35.81</v>
       </c>
       <c r="AN24" t="n">
-        <v>38.91</v>
+        <v>38.81</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>37.67</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
@@ -10540,7 +10540,7 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>-132.19</t>
+          <t>-132.14</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -10560,43 +10560,43 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>232900527.4525862</t>
+          <t>232624970.3608322</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>22638246.0</t>
+          <t>27224823.0</t>
         </is>
       </c>
       <c r="AX24" t="n">
-        <v>32529604.8</v>
+        <v>30219756.2</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>46763411.2</t>
+          <t>39847131.9</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>241442940.72</v>
+        <v>236001176.02</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>-14233806</t>
+          <t>-9627375</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>-22333152.53566639</t>
+          <t>-21672215.3805941</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-19135291.00768245</t>
+          <t>-18037061.02769653</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>22638246.0</t>
+          <t>27224823.0</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -10671,7 +10671,7 @@
       </c>
       <c r="BS24" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BT24" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="BY24" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -10731,17 +10731,17 @@
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -10763,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -10773,12 +10773,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1052.554</t>
+          <t>652.267</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10798,17 +10798,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-26.38</t>
+          <t>-30.44</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -10883,17 +10883,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>798</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -10919,53 +10919,53 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>48.28</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>34.39</t>
+          <t>34.47</t>
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>36.08</v>
+        <v>35.98</v>
       </c>
       <c r="AN25" t="n">
-        <v>38.92</v>
+        <v>38.91</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>37.67</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>-132.25</t>
+          <t>-132.19</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -10990,43 +10990,43 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>232900527.4525862</t>
+          <t>232624970.3608322</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>36488624.0</t>
+          <t>22638246.0</t>
         </is>
       </c>
       <c r="AX25" t="n">
-        <v>37237782</v>
+        <v>32529604.8</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>50581063.8</t>
+          <t>46763411.2</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>242256442.44</v>
+        <v>241442940.72</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>-13343281</t>
+          <t>-14233806</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>-22914581.90439074</t>
+          <t>-22333152.53566639</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-19529368.76453082</t>
+          <t>-19135291.00768245</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>36488624.0</t>
+          <t>22638246.0</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -11131,12 +11131,12 @@
       </c>
       <c r="BY25" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -11156,17 +11156,17 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
@@ -11203,12 +11203,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1012.048</t>
+          <t>1052.554</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -11228,17 +11228,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-30.50</t>
+          <t>-26.38</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -11313,17 +11313,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -11339,68 +11339,68 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>798</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>48.21</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>48.28</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>34.41</t>
+          <t>34.39</t>
         </is>
       </c>
       <c r="AM26" t="n">
-        <v>36.18</v>
+        <v>36.08</v>
       </c>
       <c r="AN26" t="n">
-        <v>38.94</v>
+        <v>38.92</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>37.63</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>-131.94</t>
+          <t>-132.25</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -11420,43 +11420,43 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>232900527.4525862</t>
+          <t>232624970.3608322</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>35345556.0</t>
+          <t>36488624.0</t>
         </is>
       </c>
       <c r="AX26" t="n">
-        <v>37074921.8</v>
+        <v>37237782</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>53345322.1</t>
+          <t>50581063.8</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>245778298.12</v>
+        <v>242256442.44</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>-16270400</t>
+          <t>-13343281</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>-23530075.2025471</t>
+          <t>-22914581.90439074</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-20878828.60415238</t>
+          <t>-19529368.76453082</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>35345556.0</t>
+          <t>36488624.0</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -11521,17 +11521,17 @@
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS26" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="BT26" t="inlineStr">
@@ -11561,12 +11561,12 @@
       </c>
       <c r="BY26" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -11586,22 +11586,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -11633,12 +11633,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>857.193</t>
+          <t>1012.048</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11658,17 +11658,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-31.65</t>
+          <t>-30.50</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-7.55</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -11743,17 +11743,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -11769,68 +11769,68 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>798</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>48.21</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>10.92</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>34.16</t>
+          <t>34.41</t>
         </is>
       </c>
       <c r="AM27" t="n">
-        <v>36.33</v>
+        <v>36.18</v>
       </c>
       <c r="AN27" t="n">
-        <v>39</v>
+        <v>38.94</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>37.52</t>
+          <t>37.58</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>-131.18</t>
+          <t>-131.94</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -11850,43 +11850,43 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>232900527.4525862</t>
+          <t>232624970.3608322</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>29401532.0</t>
+          <t>35345556.0</t>
         </is>
       </c>
       <c r="AX27" t="n">
-        <v>39796395.2</v>
+        <v>37074921.8</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>58228190.4</t>
+          <t>53345322.1</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>247556548.26</v>
+        <v>245778298.12</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>-18431795</t>
+          <t>-16270400</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>-24012120.03861886</t>
+          <t>-23530075.2025471</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-21938484.35346347</t>
+          <t>-20878828.60415238</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>29401532.0</t>
+          <t>35345556.0</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -11951,17 +11951,17 @@
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS27" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BT27" t="inlineStr">
@@ -11991,12 +11991,12 @@
       </c>
       <c r="BY27" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -12016,22 +12016,22 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1145.3</t>
+          <t>857.193</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>33.65</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -12088,17 +12088,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-25.49</t>
+          <t>-31.65</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -12108,7 +12108,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-9.30</t>
+          <t>-7.55</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -12173,17 +12173,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -12199,68 +12199,68 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>798</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>10.92</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>-6.49</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>34.11999999999999</t>
+          <t>34.16</t>
         </is>
       </c>
       <c r="AM28" t="n">
-        <v>36.49</v>
+        <v>36.33</v>
       </c>
       <c r="AN28" t="n">
-        <v>39.06</v>
+        <v>39</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>37.47</t>
+          <t>37.52</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>-26.04</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>-129.70</t>
+          <t>-131.18</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -12280,43 +12280,43 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>232900527.4525862</t>
+          <t>232624970.3608322</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>38774066.0</t>
+          <t>29401532.0</t>
         </is>
       </c>
       <c r="AX28" t="n">
-        <v>49474507.6</v>
+        <v>39796395.2</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>66401056.1</t>
+          <t>58228190.4</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>249662887.18</v>
+        <v>247556548.26</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>-16926548</t>
+          <t>-18431795</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>-24389144.70864711</t>
+          <t>-24012120.03861886</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-22031901.26842704</t>
+          <t>-21938484.35346347</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>38774066.0</t>
+          <t>29401532.0</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -12391,7 +12391,7 @@
       </c>
       <c r="BS28" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="BT28" t="inlineStr">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="BY28" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -12446,22 +12446,22 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.55</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>33.65</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -12493,12 +12493,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1345.621</t>
+          <t>1145.3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>33.65</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -12518,17 +12518,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-27.63</t>
+          <t>-25.49</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -12538,7 +12538,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-7.55</t>
+          <t>-9.30</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -12603,17 +12603,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>798</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>13.92</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
@@ -12654,43 +12654,43 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-6.2</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>34.33</t>
+          <t>34.11999999999999</t>
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>36.71</v>
+        <v>36.49</v>
       </c>
       <c r="AN29" t="n">
-        <v>39.14</v>
+        <v>39.06</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>37.43</t>
+          <t>37.47</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>-27.70</t>
+          <t>-26.04</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>-127.76</t>
+          <t>-129.70</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -12710,43 +12710,43 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>232900527.4525862</t>
+          <t>232624970.3608322</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>46179132.0</t>
+          <t>38774066.0</t>
         </is>
       </c>
       <c r="AX29" t="n">
-        <v>60997217.6</v>
+        <v>49474507.6</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>84286762.5</t>
+          <t>66401056.1</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>254822433.06</v>
+        <v>249662887.18</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>-23289544</t>
+          <t>-16926548</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>-24817734.42505076</t>
+          <t>-24389144.70864711</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>-22382700.45878832</t>
+          <t>-22031901.26842704</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>46179132.0</t>
+          <t>38774066.0</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -12811,7 +12811,7 @@
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
@@ -12821,7 +12821,7 @@
       </c>
       <c r="BS29" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="BT29" t="inlineStr">
@@ -12851,12 +12851,12 @@
       </c>
       <c r="BY29" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ29" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="CA29" t="inlineStr">
@@ -12876,22 +12876,22 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>34.05</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>33.65</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1029.736</t>
+          <t>1345.621</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -12938,7 +12938,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -12948,17 +12948,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-32.40</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -13023,7 +13023,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-6.20</t>
+          <t>-7.55</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -13033,17 +13033,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -13059,68 +13059,68 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>798</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>13.92</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-6.49</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-6.2</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>34.33</t>
         </is>
       </c>
       <c r="AM30" t="n">
-        <v>36.88</v>
+        <v>36.71</v>
       </c>
       <c r="AN30" t="n">
-        <v>39.24</v>
+        <v>39.14</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>37.43</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>-32.46</t>
+          <t>-27.70</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>-125.84</t>
+          <t>-127.76</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -13140,43 +13140,43 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>232900527.4525862</t>
+          <t>232624970.3608322</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>35674323.0</t>
+          <t>46179132.0</t>
         </is>
       </c>
       <c r="AX30" t="n">
-        <v>63924345.6</v>
+        <v>60997217.6</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>94556424.4</t>
+          <t>84286762.5</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>256700200.08</v>
+        <v>254822433.06</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>-30632078</t>
+          <t>-23289544</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>-25260467.87346211</t>
+          <t>-24817734.42505076</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>-22877859.92863344</t>
+          <t>-22382700.45878832</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>35674323.0</t>
+          <t>46179132.0</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
@@ -13196,7 +13196,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -13241,17 +13241,17 @@
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS30" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="BT30" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="BY30" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ30" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="CA30" t="inlineStr">
@@ -13306,22 +13306,22 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.05</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>34.85</t>
         </is>
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1450.779</t>
+          <t>1029.736</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -13378,17 +13378,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-37.05</t>
+          <t>-32.40</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -13398,7 +13398,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-9.03</t>
+          <t>-6.20</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -13463,17 +13463,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -13489,68 +13489,68 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>798</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>35.22000000000001</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>37.06</v>
+        <v>36.88</v>
       </c>
       <c r="AN31" t="n">
-        <v>39.33</v>
+        <v>39.24</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>37.33</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>-41.33</t>
+          <t>-32.46</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>-123.74</t>
+          <t>-125.84</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -13570,43 +13570,43 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>232900527.4525862</t>
+          <t>232624970.3608322</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>48952923.0</t>
+          <t>35674323.0</t>
         </is>
       </c>
       <c r="AX31" t="n">
-        <v>69615722.40000001</v>
+        <v>63924345.6</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>110580229.2</t>
+          <t>94556424.4</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>258176781.58</v>
+        <v>256700200.08</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>-40964506</t>
+          <t>-30632078</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>-25693669.31797642</t>
+          <t>-25260467.87346211</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>-21642648.9238181</t>
+          <t>-22877859.92863344</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>48952923.0</t>
+          <t>35674323.0</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -13671,17 +13671,17 @@
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS31" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="BT31" t="inlineStr">
@@ -13711,12 +13711,12 @@
       </c>
       <c r="BY31" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ31" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="CA31" t="inlineStr">
@@ -13736,22 +13736,22 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -13783,12 +13783,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2260.366</t>
+          <t>1450.779</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -13798,7 +13798,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13808,17 +13808,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-32.59</t>
+          <t>-37.05</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -13828,7 +13828,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-8.09</t>
+          <t>-9.03</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -13893,17 +13893,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -13919,7 +13919,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>798</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -13934,53 +13934,53 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>36.01000000000001</t>
+          <t>35.22000000000001</t>
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>37.29</v>
+        <v>37.06</v>
       </c>
       <c r="AN32" t="n">
-        <v>39.43</v>
+        <v>39.33</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.33</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>-37.57</t>
+          <t>-41.33</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>-121.29</t>
+          <t>-123.74</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -14000,43 +14000,43 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>232900527.4525862</t>
+          <t>232624970.3608322</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>77792094.0</t>
+          <t>48952923.0</t>
         </is>
       </c>
       <c r="AX32" t="n">
-        <v>76659985.59999999</v>
+        <v>69615722.40000001</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>113715310.1</t>
+          <t>110580229.2</t>
         </is>
       </c>
       <c r="AZ32" t="n">
-        <v>261926998.4</v>
+        <v>258176781.58</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>-37055324</t>
+          <t>-40964506</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>-26430218.48055065</t>
+          <t>-25693669.31797642</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>-20527817.16965982</t>
+          <t>-21642648.9238181</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>77792094.0</t>
+          <t>48952923.0</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
@@ -14101,7 +14101,7 @@
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="BS32" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="BT32" t="inlineStr">
@@ -14141,12 +14141,12 @@
       </c>
       <c r="BY32" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ32" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="CA32" t="inlineStr">
@@ -14166,22 +14166,22 @@
       </c>
       <c r="CD32" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>35.25</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="CF32" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="CG32" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CH32" t="inlineStr">
@@ -14213,12 +14213,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2726.249</t>
+          <t>2260.366</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -14238,17 +14238,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-25.83</t>
+          <t>-32.59</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -14258,7 +14258,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-6.47</t>
+          <t>-8.09</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -14323,17 +14323,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>-6.20</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -14349,7 +14349,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>798</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -14359,58 +14359,58 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>36.59</t>
+          <t>36.01000000000001</t>
         </is>
       </c>
       <c r="AM33" t="n">
-        <v>37.52</v>
+        <v>37.29</v>
       </c>
       <c r="AN33" t="n">
-        <v>39.54</v>
+        <v>39.43</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>37.26</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>-26.44</t>
+          <t>-37.57</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -14420,7 +14420,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>-119.29</t>
+          <t>-121.29</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -14430,43 +14430,43 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>232900527.4525862</t>
+          <t>232624970.3608322</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>96387616.0</t>
+          <t>77792094.0</t>
         </is>
       </c>
       <c r="AX33" t="n">
-        <v>83327604.59999999</v>
+        <v>76659985.59999999</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>112354225.4</t>
+          <t>113715310.1</t>
         </is>
       </c>
       <c r="AZ33" t="n">
-        <v>263764100.2</v>
+        <v>261926998.4</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>-29026620</t>
+          <t>-37055324</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>-27503382.35525808</t>
+          <t>-26430218.48055065</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>-21291975.22908874</t>
+          <t>-20527817.16965982</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>96387616.0</t>
+          <t>77792094.0</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
@@ -14486,7 +14486,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
@@ -14571,12 +14571,12 @@
       </c>
       <c r="BY33" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ33" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="CA33" t="inlineStr">
@@ -14596,22 +14596,22 @@
       </c>
       <c r="CD33" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CE33" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>35.25</t>
         </is>
       </c>
       <c r="CF33" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="CG33" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CH33" t="inlineStr">
@@ -14643,12 +14643,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1669.175</t>
+          <t>2726.249</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -14668,17 +14668,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-25.83</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -14688,7 +14688,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -14753,17 +14753,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-6.20</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -14779,7 +14779,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>798</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -14789,58 +14789,58 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-5.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>37.36</t>
+          <t>36.59</t>
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>37.67</v>
+        <v>37.52</v>
       </c>
       <c r="AN34" t="n">
-        <v>39.63</v>
+        <v>39.54</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>37.21</t>
+          <t>37.26</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>-7.99</t>
+          <t>-26.44</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>-118.02</t>
+          <t>-119.29</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -14860,43 +14860,43 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>232900527.4525862</t>
+          <t>232624970.3608322</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>60814772.0</t>
+          <t>96387616.0</t>
         </is>
       </c>
       <c r="AX34" t="n">
-        <v>107576307.4</v>
+        <v>83327604.59999999</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>111580509.9</t>
+          <t>112354225.4</t>
         </is>
       </c>
       <c r="AZ34" t="n">
-        <v>267374187.92</v>
+        <v>263764100.2</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>-4004202</t>
+          <t>-29026620</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>-28632729.10547069</t>
+          <t>-27503382.35525808</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>-23615579.27009116</t>
+          <t>-21291975.22908874</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>60814772.0</t>
+          <t>96387616.0</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
@@ -14961,7 +14961,7 @@
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
@@ -14971,7 +14971,7 @@
       </c>
       <c r="BS34" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="BT34" t="inlineStr">
@@ -15001,12 +15001,12 @@
       </c>
       <c r="BY34" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ34" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="CA34" t="inlineStr">
@@ -15031,17 +15031,17 @@
       </c>
       <c r="CE34" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CF34" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="CG34" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="CH34" t="inlineStr">

--- a/Result/checksun_type/玻璃基板.xlsx
+++ b/Result/checksun_type/玻璃基板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>57.864</t>
+          <t>103.242</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-24.98</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-11.61</t>
+          <t>-10.54</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>50.45</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>25.88</v>
+        <v>25.78</v>
       </c>
       <c r="AN2" t="n">
         <v>26.78</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>25.96</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-18.27</t>
+          <t>-10.00</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-118.69</t>
+          <t>-119.17</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>60866201.53205129</t>
+          <t>60785138.49644381</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1431397.0</t>
+          <t>2585925.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2725616.2</v>
+        <v>2334426.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3344499.9</t>
+          <t>3111599.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>10170725.72</v>
+        <v>10171307.16</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-618883</t>
+          <t>-777173</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1441986.883569631</t>
+          <t>-1410564.029383358</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1360675.639975678</t>
+          <t>-1237738.331358852</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1431397.0</t>
+          <t>2585925.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,42 +1313,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>57.864</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>24.75</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>129.907</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>25.25</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-2.02</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.82</t>
+          <t>-11.61</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,63 +1444,63 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>50.45</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>26.04</v>
+        <v>25.88</v>
       </c>
       <c r="AN3" t="n">
-        <v>26.79</v>
+        <v>26.78</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>25.92</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-23.75</t>
+          <t>-18.27</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-117.83</t>
+          <t>-118.69</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>60866201.53205129</t>
+          <t>60785138.49644381</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3250406.0</t>
+          <t>1431397.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2820044.4</v>
+        <v>2725616.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3938171.4</t>
+          <t>3344499.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>10185422.26</v>
+        <v>10170725.72</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1118127</t>
+          <t>-618883</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1456770.746041259</t>
+          <t>-1441986.883569631</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1364005.379429155</t>
+          <t>-1360675.639975678</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>3250406.0</t>
+          <t>1431397.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>44.221</t>
+          <t>129.907</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-32.35</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.89</t>
+          <t>-9.82</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>26.18</v>
+        <v>26.04</v>
       </c>
       <c r="AN4" t="n">
-        <v>26.78</v>
+        <v>26.79</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-39.44</t>
+          <t>-23.75</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-116.78</t>
+          <t>-117.83</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>60866201.53205129</t>
+          <t>60785138.49644381</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1105744.0</t>
+          <t>3250406.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2762517</v>
+        <v>2820044.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>4083544.5</t>
+          <t>3938171.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>10163096.92</v>
+        <v>10185422.26</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1321027</t>
+          <t>-1118127</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1473637.176334369</t>
+          <t>-1456770.746041259</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1514941.493668794</t>
+          <t>-1364005.379429155</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1105744.0</t>
+          <t>3250406.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>132.605</t>
+          <t>44.221</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-21.31</t>
+          <t>-32.35</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-11.07</t>
+          <t>-10.89</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>24.68</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>26.38</v>
+        <v>26.18</v>
       </c>
       <c r="AN5" t="n">
         <v>26.78</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-56.92</t>
+          <t>-39.44</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-115.12</t>
+          <t>-116.78</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>60866201.53205129</t>
+          <t>60785138.49644381</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3298659.0</t>
+          <t>1105744.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3409647.6</v>
+        <v>2762517</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4333083.4</t>
+          <t>4083544.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>10178782.26</v>
+        <v>10163096.92</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-923435</t>
+          <t>-1321027</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1466127.300455383</t>
+          <t>-1473637.176334369</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1446674.246380107</t>
+          <t>-1514941.493668794</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>3298659.0</t>
+          <t>1105744.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>182.531</t>
+          <t>132.605</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-11.85</t>
+          <t>-21.31</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-11.96</t>
+          <t>-11.07</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>24.78</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>26.62</v>
+        <v>26.38</v>
       </c>
       <c r="AN6" t="n">
-        <v>26.79</v>
+        <v>26.78</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-82.30</t>
+          <t>-56.92</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-112.97</t>
+          <t>-115.12</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>60866201.53205129</t>
+          <t>60785138.49644381</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>4541875.0</t>
+          <t>3298659.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3888772.8</v>
+        <v>3409647.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>4411562.6</t>
+          <t>4333083.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>10182869.32</v>
+        <v>10178782.26</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-522789</t>
+          <t>-923435</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1469664.21937816</t>
+          <t>-1466127.300455383</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1532437.84859698</t>
+          <t>-1446674.246380107</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>4541875.0</t>
+          <t>3298659.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>77.947</t>
+          <t>182.531</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-25.48</t>
+          <t>-11.85</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-13.04</t>
+          <t>-11.96</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-7.50</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.67</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>26.86</v>
+        <v>26.62</v>
       </c>
       <c r="AN7" t="n">
         <v>26.79</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>25.87</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-116.96</t>
+          <t>-82.30</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-110.30</t>
+          <t>-112.97</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>60866201.53205129</t>
+          <t>60785138.49644381</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1903538.0</t>
+          <t>4541875.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>3963383.6</v>
+        <v>3888772.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>5318222.8</t>
+          <t>4411562.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>10129541.2</v>
+        <v>10182869.32</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1354839</t>
+          <t>-522789</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1458250.832247465</t>
+          <t>-1469664.21937816</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1733429.071456906</t>
+          <t>-1532437.84859698</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1903538.0</t>
+          <t>4541875.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>121.223</t>
+          <t>77.947</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-25.48</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-12.32</t>
+          <t>-13.04</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,17 +3594,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-7.61</t>
+          <t>-7.50</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>27.22</v>
+        <v>26.86</v>
       </c>
       <c r="AN8" t="n">
-        <v>26.8</v>
+        <v>26.79</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>25.87</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-165.59</t>
+          <t>-116.96</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-107.29</t>
+          <t>-110.30</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>60866201.53205129</t>
+          <t>60785138.49644381</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2962769.0</t>
+          <t>1903538.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>5056298.4</v>
+        <v>3963383.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>5511802.7</t>
+          <t>5318222.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>10116244</v>
+        <v>10129541.2</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-455504</t>
+          <t>-1354839</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1408218.425118476</t>
+          <t>-1458250.832247465</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1675972.244419054</t>
+          <t>-1733429.071456906</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2962769.0</t>
+          <t>1903538.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>171.268</t>
+          <t>121.223</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-9.11</t>
+          <t>-12.32</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,54 +4024,54 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-7.61</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>27.43</v>
+        <v>27.22</v>
       </c>
       <c r="AN9" t="n">
-        <v>26.81</v>
+        <v>26.8</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4080,17 +4080,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-273.08</t>
+          <t>-165.59</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.27</t>
+          <t>-107.29</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>60866201.53205129</t>
+          <t>60785138.49644381</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>4341397.0</t>
+          <t>2962769.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>5404572</v>
+        <v>5056298.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5443936.9</t>
+          <t>5511802.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>10090356.22</v>
+        <v>10116244</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-39364</t>
+          <t>-455504</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1359535.912518371</t>
+          <t>-1408218.425118476</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1647523.947064298</t>
+          <t>-1675972.244419054</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>4341397.0</t>
+          <t>2962769.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>229.109</t>
+          <t>171.268</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-13.04</t>
+          <t>-9.11</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>27.58</v>
+        <v>27.43</v>
       </c>
       <c r="AN10" t="n">
         <v>26.81</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>25.84</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-960.20</t>
+          <t>-273.08</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-101.36</t>
+          <t>-104.27</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>60866201.53205129</t>
+          <t>60785138.49644381</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>5694285.0</t>
+          <t>4341397.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>5256519.2</v>
+        <v>5404572</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5382212.9</t>
+          <t>5443936.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>10042035.4</v>
+        <v>10090356.22</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-125693</t>
+          <t>-39364</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1307174.451691839</t>
+          <t>-1359535.912518371</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1695753.524162351</t>
+          <t>-1647523.947064298</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>5694285.0</t>
+          <t>4341397.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>194.645</t>
+          <t>229.109</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-13.04</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,39 +4899,39 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>27.77</v>
+        <v>27.58</v>
       </c>
       <c r="AN11" t="n">
-        <v>26.82</v>
+        <v>26.81</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -4940,17 +4940,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-545.29</t>
+          <t>-960.20</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-98.10</t>
+          <t>-101.36</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>60866201.53205129</t>
+          <t>60785138.49644381</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>4914929.0</t>
+          <t>5694285.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>4934352.4</v>
+        <v>5256519.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5195209.4</t>
+          <t>5382212.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>9975089.699999999</v>
+        <v>10042035.4</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-260857</t>
+          <t>-125693</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1236523.711242655</t>
+          <t>-1307174.451691839</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1849042.579868057</t>
+          <t>-1695753.524162351</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>4914929.0</t>
+          <t>5694285.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>282.054</t>
+          <t>194.645</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.44</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>26.70</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>16.15</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>26.72</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>27.84</v>
+        <v>27.77</v>
       </c>
       <c r="AN12" t="n">
-        <v>26.81</v>
+        <v>26.82</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>25.84</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-207.53</t>
+          <t>-545.29</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-95.51</t>
+          <t>-98.10</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>60866201.53205129</t>
+          <t>60785138.49644381</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>7368112.0</t>
+          <t>4914929.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>6673062</v>
+        <v>4934352.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5266881.5</t>
+          <t>5195209.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>9924938.880000001</v>
+        <v>9975089.699999999</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1406180</t>
+          <t>-260857</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1125156.644219854</t>
+          <t>-1236523.711242655</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1918487.281595205</t>
+          <t>-1849042.579868057</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>7368112.0</t>
+          <t>4914929.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,42 +5613,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>13.45</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-22.25</t>
+          <t>-21.97</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,49 +5749,49 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>60.36</t>
+          <t>75.85</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>13.42</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>13.74</v>
+        <v>13.71</v>
       </c>
       <c r="AN13" t="n">
-        <v>14.28</v>
+        <v>14.24</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5800,19 +5800,19 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
           <t>-0.28</t>
         </is>
       </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>-0.29</t>
-        </is>
-      </c>
       <c r="AS13" t="inlineStr">
         <is>
           <t>2.34</t>
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-112.32</t>
+          <t>-112.13</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>7331.307030129125</t>
+          <t>7321.912607449856</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>516.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>472.6</v>
+        <v>534.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>402.3</t>
+          <t>437.4</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>481.38</v>
+        <v>468.04</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>97</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-10.83001914489146</t>
+          <t>-12.02299824989772</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-28.30195518775838</t>
+          <t>-18.58438332743214</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>516.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>511</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6033,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,63 +6179,63 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>60.36</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.83</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>13.77</v>
+        <v>13.74</v>
       </c>
       <c r="AN14" t="n">
-        <v>14.31</v>
+        <v>14.28</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-112.36</t>
+          <t>-112.32</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>7331.307030129125</t>
+          <t>7321.912607449856</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>507.6</v>
+        <v>472.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>424.0</t>
+          <t>402.3</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>517.4400000000001</v>
+        <v>481.38</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-7.653303500733839</t>
+          <t>-10.83001914489146</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>3.719440554195444</t>
+          <t>-28.30195518775838</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>511</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,17 +6426,17 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-22.83</t>
+          <t>-22.25</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,49 +6609,49 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>13.8</v>
+        <v>13.77</v>
       </c>
       <c r="AN15" t="n">
-        <v>14.35</v>
+        <v>14.31</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6660,12 +6660,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-112.26</t>
+          <t>-112.36</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>7331.307030129125</t>
+          <t>7321.912607449856</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>459.6</v>
+        <v>507.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>420.3</t>
+          <t>424.0</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>554.86</v>
+        <v>517.4400000000001</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-9.721075147084617</t>
+          <t>-7.653303500733839</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-6.061402691377396</t>
+          <t>3.719440554195444</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-4.30</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>511</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-9.92</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,49 +7039,49 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.83</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>13.83</v>
+        <v>13.8</v>
       </c>
       <c r="AN16" t="n">
-        <v>14.41</v>
+        <v>14.35</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7090,17 +7090,17 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-12.91</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-111.98</t>
+          <t>-112.26</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>7331.307030129125</t>
+          <t>7321.912607449856</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>1213.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>527.6</v>
+        <v>459.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>585.7</t>
+          <t>420.3</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>567.6799999999999</v>
+        <v>554.86</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-58</t>
+          <t>39</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-10.38647013903138</t>
+          <t>-9.721075147084617</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>21.00387133963898</t>
+          <t>-6.061402691377396</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>1213.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7221,12 +7221,12 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>511</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-31.65</t>
+          <t>-9.92</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,49 +7469,49 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>13.86</v>
+        <v>13.83</v>
       </c>
       <c r="AN17" t="n">
-        <v>14.48</v>
+        <v>14.41</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-16.60</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-111.60</t>
+          <t>-111.98</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>7331.307030129125</t>
+          <t>7321.912607449856</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>1213.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>340.2</v>
+        <v>527.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>497.7</t>
+          <t>585.7</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>555.26</v>
+        <v>567.6799999999999</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-157</t>
+          <t>-58</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-16.09380495333509</t>
+          <t>-10.38647013903138</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-46.08158973532466</t>
+          <t>21.00387133963898</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>1213.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>511</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,17 +7716,17 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-48.73</t>
+          <t>-31.65</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-24.86</t>
+          <t>-22.83</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,49 +7899,49 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>13.43</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>13.9</v>
+        <v>13.86</v>
       </c>
       <c r="AN18" t="n">
-        <v>14.55</v>
+        <v>14.48</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -7950,17 +7950,17 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-19.79</t>
+          <t>-16.60</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-111.11</t>
+          <t>-111.60</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>7331.307030129125</t>
+          <t>7321.912607449856</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>332</v>
+        <v>340.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>647.5</t>
+          <t>497.7</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>577.0599999999999</v>
+        <v>555.26</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-315</t>
+          <t>-157</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-10.6414804475188</t>
+          <t>-16.09380495333509</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-32.37933449472541</t>
+          <t>-46.08158973532466</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-4.30</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,17 +8081,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>511</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
+          <t>12.9</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
           <t>13.4</t>
         </is>
       </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>13.55</t>
-        </is>
-      </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-45.61</t>
+          <t>-48.73</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-23.12</t>
+          <t>-24.86</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8344,34 +8344,34 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-3.20</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>13.62</t>
+          <t>13.43</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>13.95</v>
+        <v>13.9</v>
       </c>
       <c r="AN19" t="n">
-        <v>14.64</v>
+        <v>14.55</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8380,17 +8380,17 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-19.79</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-110.56</t>
+          <t>-111.11</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>7331.307030129125</t>
+          <t>7321.912607449856</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>374.0</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>340.4</v>
+        <v>332</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>625.9</t>
+          <t>647.5</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>605.1799999999999</v>
+        <v>577.0599999999999</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-285</t>
+          <t>-315</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-6.68914334802669</t>
+          <t>-10.6414804475188</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-18.71970791905761</t>
+          <t>-32.37933449472541</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>374.0</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>511</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>13.15</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8613,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-36.19</t>
+          <t>-45.61</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-21.39</t>
+          <t>-23.12</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,34 +8774,34 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>13.62</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>13.98</v>
+        <v>13.95</v>
       </c>
       <c r="AN20" t="n">
-        <v>14.71</v>
+        <v>14.64</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8810,17 +8810,17 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-110.37</t>
+          <t>-110.56</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>7331.307030129125</t>
+          <t>7321.912607449856</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>374.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>381</v>
+        <v>340.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>597.1</t>
+          <t>625.9</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>630.02</v>
+        <v>605.1799999999999</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-216</t>
+          <t>-285</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-4.501767971475612</t>
+          <t>-6.68914334802669</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-9.46596609956589</t>
+          <t>-18.71970791905761</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>374.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>511</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
+          <t>13.6</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
           <t>13.65</t>
         </is>
       </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>13.95</t>
-        </is>
-      </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>13.15</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>-36.19</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9199,58 +9199,58 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>14</v>
+        <v>13.98</v>
       </c>
       <c r="AN21" t="n">
-        <v>14.79</v>
+        <v>14.71</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-110.48</t>
+          <t>-110.37</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>7331.307030129125</t>
+          <t>7321.912607449856</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>276.0</t>
+          <t>573.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>643.8</v>
+        <v>381</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>572.3</t>
+          <t>597.1</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>643.84</v>
+        <v>630.02</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>-216</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-3.599186493641016</t>
+          <t>-4.501767971475612</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-17.22969328245046</t>
+          <t>-9.46596609956589</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>276.0</t>
+          <t>573.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9371,12 +9371,12 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>511</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,12 +9436,12 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.95</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>16.38</t>
+          <t>12.49</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-21.10</t>
+          <t>-21.39</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9629,39 +9629,39 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>14.03</t>
         </is>
       </c>
       <c r="AM22" t="n">
         <v>14</v>
       </c>
       <c r="AN22" t="n">
-        <v>14.87</v>
+        <v>14.79</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>21.76</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-110.76</t>
+          <t>-110.48</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>7331.307030129125</t>
+          <t>7321.912607449856</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>276.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>655.2</v>
+        <v>643.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>572.3</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>675</v>
+        <v>643.84</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-1.120912532039299</t>
+          <t>-3.599186493641016</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>4.116042644944969</t>
+          <t>-17.22969328245046</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>276.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>511</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,12 +9866,12 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>13.95</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>70.35</t>
+          <t>16.38</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-19.36</t>
+          <t>-21.10</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,68 +10049,68 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-6.17</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>14.17</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>14.02</v>
+        <v>14</v>
       </c>
       <c r="AN23" t="n">
-        <v>14.94</v>
+        <v>14.87</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>15.13</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>35.24</t>
+          <t>21.76</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-111.35</t>
+          <t>-110.76</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>7331.307030129125</t>
+          <t>7321.912607449856</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>314.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>963</v>
+        <v>655.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>565.3</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>734.12</v>
+        <v>675</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>92</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-2.073086200581893</t>
+          <t>-1.120912532039299</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>46.35580673247603</t>
+          <t>4.116042644944969</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>314.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>511</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>13.95</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>13.95</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10343,12 +10343,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>797.737</t>
+          <t>908.595</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-24.16</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-8.36</t>
+          <t>-9.03</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -10453,17 +10453,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -10474,63 +10474,63 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>909</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>60.49</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-7.74</t>
+          <t>-7.84</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>34.43</t>
         </is>
       </c>
       <c r="AM24" t="n">
-        <v>35.81</v>
+        <v>35.67</v>
       </c>
       <c r="AN24" t="n">
-        <v>38.81</v>
+        <v>38.71</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.74</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>-132.14</t>
+          <t>-132.13</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -10560,43 +10560,43 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>232624970.3608322</t>
+          <t>232357841.1296562</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>27224823.0</t>
+          <t>30779178.0</t>
         </is>
       </c>
       <c r="AX24" t="n">
-        <v>30219756.2</v>
+        <v>30495285.4</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>39847131.9</t>
+          <t>35145840.3</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>236001176.02</v>
+        <v>228943265.06</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>-9627375</t>
+          <t>-4650554</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>-21672215.3805941</t>
+          <t>-20884304.84373562</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-18037061.02769653</t>
+          <t>-16550796.89101397</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>27224823.0</t>
+          <t>30779178.0</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -10671,7 +10671,7 @@
       </c>
       <c r="BS24" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="BT24" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="BY24" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -10726,22 +10726,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -10773,12 +10773,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>652.267</t>
+          <t>797.737</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -10798,17 +10798,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-30.44</t>
+          <t>-24.16</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -10873,7 +10873,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-6.47</t>
+          <t>-8.36</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -10883,17 +10883,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -10904,63 +10904,63 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>909</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>60.49</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-7.74</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>34.47</t>
+          <t>34.54</t>
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>35.98</v>
+        <v>35.81</v>
       </c>
       <c r="AN25" t="n">
-        <v>38.91</v>
+        <v>38.81</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>37.67</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
@@ -10970,7 +10970,7 @@
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>-132.19</t>
+          <t>-132.14</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -10990,43 +10990,43 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>232624970.3608322</t>
+          <t>232357841.1296562</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>22638246.0</t>
+          <t>27224823.0</t>
         </is>
       </c>
       <c r="AX25" t="n">
-        <v>32529604.8</v>
+        <v>30219756.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>46763411.2</t>
+          <t>39847131.9</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>241442940.72</v>
+        <v>236001176.02</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>-14233806</t>
+          <t>-9627375</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>-22333152.53566639</t>
+          <t>-21672215.3805941</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-19135291.00768245</t>
+          <t>-18037061.02769653</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>22638246.0</t>
+          <t>27224823.0</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -11046,7 +11046,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="BS25" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BT25" t="inlineStr">
@@ -11131,12 +11131,12 @@
       </c>
       <c r="BY25" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -11161,17 +11161,17 @@
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -11193,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11203,12 +11203,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1052.554</t>
+          <t>652.267</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11228,17 +11228,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-26.38</t>
+          <t>-30.44</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -11313,17 +11313,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -11334,12 +11334,12 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>909</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -11349,53 +11349,53 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>48.28</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>34.39</t>
+          <t>34.47</t>
         </is>
       </c>
       <c r="AM26" t="n">
-        <v>36.08</v>
+        <v>35.98</v>
       </c>
       <c r="AN26" t="n">
-        <v>38.92</v>
+        <v>38.91</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>37.67</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>-132.25</t>
+          <t>-132.19</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -11420,43 +11420,43 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>232624970.3608322</t>
+          <t>232357841.1296562</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>36488624.0</t>
+          <t>22638246.0</t>
         </is>
       </c>
       <c r="AX26" t="n">
-        <v>37237782</v>
+        <v>32529604.8</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>50581063.8</t>
+          <t>46763411.2</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>242256442.44</v>
+        <v>241442940.72</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>-13343281</t>
+          <t>-14233806</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>-22914581.90439074</t>
+          <t>-22333152.53566639</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-19529368.76453082</t>
+          <t>-19135291.00768245</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>36488624.0</t>
+          <t>22638246.0</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -11561,12 +11561,12 @@
       </c>
       <c r="BY26" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -11586,17 +11586,17 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
@@ -11633,12 +11633,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1012.048</t>
+          <t>1052.554</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11658,17 +11658,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-30.50</t>
+          <t>-26.38</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -11743,17 +11743,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -11764,73 +11764,73 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>909</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>48.21</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>48.28</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>34.41</t>
+          <t>34.39</t>
         </is>
       </c>
       <c r="AM27" t="n">
-        <v>36.18</v>
+        <v>36.08</v>
       </c>
       <c r="AN27" t="n">
-        <v>38.94</v>
+        <v>38.92</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>37.63</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>-131.94</t>
+          <t>-132.25</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -11850,43 +11850,43 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>232624970.3608322</t>
+          <t>232357841.1296562</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>35345556.0</t>
+          <t>36488624.0</t>
         </is>
       </c>
       <c r="AX27" t="n">
-        <v>37074921.8</v>
+        <v>37237782</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>53345322.1</t>
+          <t>50581063.8</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>245778298.12</v>
+        <v>242256442.44</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>-16270400</t>
+          <t>-13343281</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>-23530075.2025471</t>
+          <t>-22914581.90439074</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-20878828.60415238</t>
+          <t>-19529368.76453082</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>35345556.0</t>
+          <t>36488624.0</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -11951,17 +11951,17 @@
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS27" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="BT27" t="inlineStr">
@@ -11991,12 +11991,12 @@
       </c>
       <c r="BY27" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -12016,22 +12016,22 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>857.193</t>
+          <t>1012.048</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -12088,17 +12088,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-31.65</t>
+          <t>-30.50</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-7.55</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -12173,17 +12173,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -12194,73 +12194,73 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>909</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>48.21</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>10.92</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>34.16</t>
+          <t>34.41</t>
         </is>
       </c>
       <c r="AM28" t="n">
-        <v>36.33</v>
+        <v>36.18</v>
       </c>
       <c r="AN28" t="n">
-        <v>39</v>
+        <v>38.94</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>37.52</t>
+          <t>37.58</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>-131.18</t>
+          <t>-131.94</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -12280,43 +12280,43 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>232624970.3608322</t>
+          <t>232357841.1296562</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>29401532.0</t>
+          <t>35345556.0</t>
         </is>
       </c>
       <c r="AX28" t="n">
-        <v>39796395.2</v>
+        <v>37074921.8</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>58228190.4</t>
+          <t>53345322.1</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>247556548.26</v>
+        <v>245778298.12</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>-18431795</t>
+          <t>-16270400</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>-24012120.03861886</t>
+          <t>-23530075.2025471</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-21938484.35346347</t>
+          <t>-20878828.60415238</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>29401532.0</t>
+          <t>35345556.0</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -12381,17 +12381,17 @@
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS28" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BT28" t="inlineStr">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="BY28" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -12446,22 +12446,22 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -12493,12 +12493,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1145.3</t>
+          <t>857.193</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>33.65</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -12518,17 +12518,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-25.49</t>
+          <t>-31.65</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-9.30</t>
+          <t>-7.55</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -12603,17 +12603,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -12624,73 +12624,73 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>909</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>10.92</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>-6.49</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>34.11999999999999</t>
+          <t>34.16</t>
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>36.49</v>
+        <v>36.33</v>
       </c>
       <c r="AN29" t="n">
-        <v>39.06</v>
+        <v>39</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>37.47</t>
+          <t>37.52</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>-26.04</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>-129.70</t>
+          <t>-131.18</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -12710,43 +12710,43 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>232624970.3608322</t>
+          <t>232357841.1296562</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>38774066.0</t>
+          <t>29401532.0</t>
         </is>
       </c>
       <c r="AX29" t="n">
-        <v>49474507.6</v>
+        <v>39796395.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>66401056.1</t>
+          <t>58228190.4</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>249662887.18</v>
+        <v>247556548.26</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>-16926548</t>
+          <t>-18431795</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>-24389144.70864711</t>
+          <t>-24012120.03861886</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>-22031901.26842704</t>
+          <t>-21938484.35346347</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>38774066.0</t>
+          <t>29401532.0</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -12811,7 +12811,7 @@
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
@@ -12821,7 +12821,7 @@
       </c>
       <c r="BS29" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="BT29" t="inlineStr">
@@ -12851,12 +12851,12 @@
       </c>
       <c r="BY29" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ29" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="CA29" t="inlineStr">
@@ -12876,22 +12876,22 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.55</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>33.65</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1345.621</t>
+          <t>1145.3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -12938,7 +12938,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>33.65</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -12948,17 +12948,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-27.63</t>
+          <t>-25.49</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -13023,7 +13023,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-7.55</t>
+          <t>-9.30</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -13033,17 +13033,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -13054,17 +13054,17 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>909</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>13.92</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
@@ -13074,7 +13074,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
@@ -13084,43 +13084,43 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-6.2</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>34.33</t>
+          <t>34.11999999999999</t>
         </is>
       </c>
       <c r="AM30" t="n">
-        <v>36.71</v>
+        <v>36.49</v>
       </c>
       <c r="AN30" t="n">
-        <v>39.14</v>
+        <v>39.06</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>37.43</t>
+          <t>37.47</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>-27.70</t>
+          <t>-26.04</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>-127.76</t>
+          <t>-129.70</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -13140,43 +13140,43 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>232624970.3608322</t>
+          <t>232357841.1296562</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>46179132.0</t>
+          <t>38774066.0</t>
         </is>
       </c>
       <c r="AX30" t="n">
-        <v>60997217.6</v>
+        <v>49474507.6</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>84286762.5</t>
+          <t>66401056.1</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>254822433.06</v>
+        <v>249662887.18</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>-23289544</t>
+          <t>-16926548</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>-24817734.42505076</t>
+          <t>-24389144.70864711</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>-22382700.45878832</t>
+          <t>-22031901.26842704</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>46179132.0</t>
+          <t>38774066.0</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
@@ -13196,7 +13196,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="BS30" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="BT30" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="BY30" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ30" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="CA30" t="inlineStr">
@@ -13306,22 +13306,22 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>34.05</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>33.65</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1029.736</t>
+          <t>1345.621</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -13378,17 +13378,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-32.40</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-6.20</t>
+          <t>-7.55</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -13463,17 +13463,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -13484,73 +13484,73 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>909</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>13.92</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-6.49</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-6.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>34.33</t>
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>36.88</v>
+        <v>36.71</v>
       </c>
       <c r="AN31" t="n">
-        <v>39.24</v>
+        <v>39.14</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>37.43</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>-32.46</t>
+          <t>-27.70</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>-125.84</t>
+          <t>-127.76</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -13570,43 +13570,43 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>232624970.3608322</t>
+          <t>232357841.1296562</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>35674323.0</t>
+          <t>46179132.0</t>
         </is>
       </c>
       <c r="AX31" t="n">
-        <v>63924345.6</v>
+        <v>60997217.6</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>94556424.4</t>
+          <t>84286762.5</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>256700200.08</v>
+        <v>254822433.06</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>-30632078</t>
+          <t>-23289544</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>-25260467.87346211</t>
+          <t>-24817734.42505076</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>-22877859.92863344</t>
+          <t>-22382700.45878832</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>35674323.0</t>
+          <t>46179132.0</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -13671,17 +13671,17 @@
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS31" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="BT31" t="inlineStr">
@@ -13711,12 +13711,12 @@
       </c>
       <c r="BY31" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ31" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="CA31" t="inlineStr">
@@ -13736,22 +13736,22 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.05</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>34.85</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -13783,12 +13783,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1450.779</t>
+          <t>1029.736</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -13798,7 +13798,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13808,17 +13808,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-37.05</t>
+          <t>-32.40</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-9.03</t>
+          <t>-6.20</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -13893,17 +13893,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -13914,73 +13914,73 @@
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>909</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>35.22000000000001</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>37.06</v>
+        <v>36.88</v>
       </c>
       <c r="AN32" t="n">
-        <v>39.33</v>
+        <v>39.24</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>37.33</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>-41.33</t>
+          <t>-32.46</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>-123.74</t>
+          <t>-125.84</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -14000,43 +14000,43 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>232624970.3608322</t>
+          <t>232357841.1296562</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>48952923.0</t>
+          <t>35674323.0</t>
         </is>
       </c>
       <c r="AX32" t="n">
-        <v>69615722.40000001</v>
+        <v>63924345.6</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>110580229.2</t>
+          <t>94556424.4</t>
         </is>
       </c>
       <c r="AZ32" t="n">
-        <v>258176781.58</v>
+        <v>256700200.08</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>-40964506</t>
+          <t>-30632078</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>-25693669.31797642</t>
+          <t>-25260467.87346211</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>-21642648.9238181</t>
+          <t>-22877859.92863344</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>48952923.0</t>
+          <t>35674323.0</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
@@ -14101,17 +14101,17 @@
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS32" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="BT32" t="inlineStr">
@@ -14141,12 +14141,12 @@
       </c>
       <c r="BY32" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ32" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="CA32" t="inlineStr">
@@ -14166,22 +14166,22 @@
       </c>
       <c r="CD32" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="CF32" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CG32" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CH32" t="inlineStr">
@@ -14213,12 +14213,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2260.366</t>
+          <t>1450.779</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -14238,17 +14238,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-32.59</t>
+          <t>-37.05</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-8.09</t>
+          <t>-9.03</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -14323,17 +14323,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -14344,12 +14344,12 @@
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>909</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -14364,53 +14364,53 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>36.01000000000001</t>
+          <t>35.22000000000001</t>
         </is>
       </c>
       <c r="AM33" t="n">
-        <v>37.29</v>
+        <v>37.06</v>
       </c>
       <c r="AN33" t="n">
-        <v>39.43</v>
+        <v>39.33</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.33</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>-37.57</t>
+          <t>-41.33</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -14420,7 +14420,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>-121.29</t>
+          <t>-123.74</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -14430,43 +14430,43 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>232624970.3608322</t>
+          <t>232357841.1296562</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>77792094.0</t>
+          <t>48952923.0</t>
         </is>
       </c>
       <c r="AX33" t="n">
-        <v>76659985.59999999</v>
+        <v>69615722.40000001</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>113715310.1</t>
+          <t>110580229.2</t>
         </is>
       </c>
       <c r="AZ33" t="n">
-        <v>261926998.4</v>
+        <v>258176781.58</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>-37055324</t>
+          <t>-40964506</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>-26430218.48055065</t>
+          <t>-25693669.31797642</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>-20527817.16965982</t>
+          <t>-21642648.9238181</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>77792094.0</t>
+          <t>48952923.0</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
@@ -14486,7 +14486,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR33" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
@@ -14571,12 +14571,12 @@
       </c>
       <c r="BY33" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ33" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="CA33" t="inlineStr">
@@ -14596,22 +14596,22 @@
       </c>
       <c r="CD33" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CE33" t="inlineStr">
         <is>
-          <t>35.25</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="CF33" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="CG33" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CH33" t="inlineStr">
@@ -14643,12 +14643,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2726.249</t>
+          <t>2260.366</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -14668,17 +14668,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-25.83</t>
+          <t>-32.59</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-6.47</t>
+          <t>-8.09</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -14753,17 +14753,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>-6.20</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -14774,12 +14774,12 @@
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>909</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -14789,58 +14789,58 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>36.59</t>
+          <t>36.01000000000001</t>
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>37.52</v>
+        <v>37.29</v>
       </c>
       <c r="AN34" t="n">
-        <v>39.54</v>
+        <v>39.43</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>37.26</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>-26.44</t>
+          <t>-37.57</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>-119.29</t>
+          <t>-121.29</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -14860,43 +14860,43 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>232624970.3608322</t>
+          <t>232357841.1296562</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>96387616.0</t>
+          <t>77792094.0</t>
         </is>
       </c>
       <c r="AX34" t="n">
-        <v>83327604.59999999</v>
+        <v>76659985.59999999</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>112354225.4</t>
+          <t>113715310.1</t>
         </is>
       </c>
       <c r="AZ34" t="n">
-        <v>263764100.2</v>
+        <v>261926998.4</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>-29026620</t>
+          <t>-37055324</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>-27503382.35525808</t>
+          <t>-26430218.48055065</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>-21291975.22908874</t>
+          <t>-20527817.16965982</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>96387616.0</t>
+          <t>77792094.0</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
@@ -14971,7 +14971,7 @@
       </c>
       <c r="BS34" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="BT34" t="inlineStr">
@@ -15001,12 +15001,12 @@
       </c>
       <c r="BY34" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ34" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="CA34" t="inlineStr">
@@ -15026,22 +15026,22 @@
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CE34" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>35.25</t>
         </is>
       </c>
       <c r="CF34" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="CG34" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CH34" t="inlineStr">

--- a/Result/checksun_type/玻璃基板.xlsx
+++ b/Result/checksun_type/玻璃基板.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>103.242</t>
+          <t>405.481</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-24.98</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-10.54</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>405</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>25.78</v>
+        <v>25.75</v>
       </c>
       <c r="AN2" t="n">
-        <v>26.78</v>
+        <v>26.79</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>25.96</t>
+          <t>25.99</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-10.00</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,53 +1090,53 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-119.17</t>
+          <t>-118.68</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/10/22</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>60785138.49644381</t>
+          <t>60721536.49644886</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2585925.0</t>
+          <t>10672887.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2334426.2</v>
+        <v>3809271.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3111599.5</t>
+          <t>3609459.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>10171307.16</v>
+        <v>10245696.52</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-777173</t>
+          <t>199812</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1410564.029383358</t>
+          <t>-1272664.425946395</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1237738.331358852</t>
+          <t>-514216.6070431024</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2585925.0</t>
+          <t>10672887.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>27.05</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>57.864</t>
+          <t>103.242</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-24.98</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-11.61</t>
+          <t>-10.54</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>405</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>50.45</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>25.88</v>
+        <v>25.78</v>
       </c>
       <c r="AN3" t="n">
         <v>26.78</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>25.96</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-18.27</t>
+          <t>-10.00</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,53 +1520,53 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-118.69</t>
+          <t>-119.17</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/10/22</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>60785138.49644381</t>
+          <t>60721536.49644886</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1431397.0</t>
+          <t>2585925.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2725616.2</v>
+        <v>2334426.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3344499.9</t>
+          <t>3111599.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>10170725.72</v>
+        <v>10171307.16</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-618883</t>
+          <t>-777173</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1441986.883569631</t>
+          <t>-1410564.029383358</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1360675.639975678</t>
+          <t>-1237738.331358852</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1431397.0</t>
+          <t>2585925.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>129.907</t>
+          <t>57.864</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-9.82</t>
+          <t>-11.61</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,63 +1874,63 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>405</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>50.45</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>26.04</v>
+        <v>25.88</v>
       </c>
       <c r="AN4" t="n">
-        <v>26.79</v>
+        <v>26.78</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>25.92</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-23.75</t>
+          <t>-18.27</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,53 +1950,53 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-117.83</t>
+          <t>-118.69</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/10/22</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>60785138.49644381</t>
+          <t>60721536.49644886</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3250406.0</t>
+          <t>1431397.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2820044.4</v>
+        <v>2725616.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3938171.4</t>
+          <t>3344499.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>10185422.26</v>
+        <v>10170725.72</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1118127</t>
+          <t>-618883</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1456770.746041259</t>
+          <t>-1441986.883569631</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1364005.379429155</t>
+          <t>-1360675.639975678</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>3250406.0</t>
+          <t>1431397.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44.221</t>
+          <t>129.907</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-32.35</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.89</t>
+          <t>-9.82</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>405</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>26.18</v>
+        <v>26.04</v>
       </c>
       <c r="AN5" t="n">
-        <v>26.78</v>
+        <v>26.79</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-39.44</t>
+          <t>-23.75</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,53 +2380,53 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-116.78</t>
+          <t>-117.83</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/10/22</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>60785138.49644381</t>
+          <t>60721536.49644886</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1105744.0</t>
+          <t>3250406.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>2762517</v>
+        <v>2820044.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4083544.5</t>
+          <t>3938171.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>10163096.92</v>
+        <v>10185422.26</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1321027</t>
+          <t>-1118127</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1473637.176334369</t>
+          <t>-1456770.746041259</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1514941.493668794</t>
+          <t>-1364005.379429155</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1105744.0</t>
+          <t>3250406.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>132.605</t>
+          <t>44.221</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-21.31</t>
+          <t>-32.35</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-11.07</t>
+          <t>-10.89</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>405</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>24.68</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>26.38</v>
+        <v>26.18</v>
       </c>
       <c r="AN6" t="n">
         <v>26.78</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-56.92</t>
+          <t>-39.44</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,53 +2810,53 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-115.12</t>
+          <t>-116.78</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/10/22</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>60785138.49644381</t>
+          <t>60721536.49644886</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3298659.0</t>
+          <t>1105744.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3409647.6</v>
+        <v>2762517</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>4333083.4</t>
+          <t>4083544.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>10178782.26</v>
+        <v>10163096.92</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-923435</t>
+          <t>-1321027</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1466127.300455383</t>
+          <t>-1473637.176334369</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1446674.246380107</t>
+          <t>-1514941.493668794</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>3298659.0</t>
+          <t>1105744.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>182.531</t>
+          <t>132.605</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-11.85</t>
+          <t>-21.31</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-11.96</t>
+          <t>-11.07</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>405</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>24.78</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>26.62</v>
+        <v>26.38</v>
       </c>
       <c r="AN7" t="n">
-        <v>26.79</v>
+        <v>26.78</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-82.30</t>
+          <t>-56.92</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,53 +3240,53 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-112.97</t>
+          <t>-115.12</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/10/22</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>60785138.49644381</t>
+          <t>60721536.49644886</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>4541875.0</t>
+          <t>3298659.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>3888772.8</v>
+        <v>3409647.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>4411562.6</t>
+          <t>4333083.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>10182869.32</v>
+        <v>10178782.26</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-522789</t>
+          <t>-923435</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1469664.21937816</t>
+          <t>-1466127.300455383</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1532437.84859698</t>
+          <t>-1446674.246380107</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>4541875.0</t>
+          <t>3298659.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3453,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>77.947</t>
+          <t>182.531</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-25.48</t>
+          <t>-11.85</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-13.04</t>
+          <t>-11.96</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>405</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-7.50</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.67</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>26.86</v>
+        <v>26.62</v>
       </c>
       <c r="AN8" t="n">
         <v>26.79</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>25.87</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-116.96</t>
+          <t>-82.30</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,53 +3670,53 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-110.30</t>
+          <t>-112.97</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/10/22</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>60785138.49644381</t>
+          <t>60721536.49644886</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1903538.0</t>
+          <t>4541875.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>3963383.6</v>
+        <v>3888772.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>5318222.8</t>
+          <t>4411562.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>10129541.2</v>
+        <v>10182869.32</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1354839</t>
+          <t>-522789</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1458250.832247465</t>
+          <t>-1469664.21937816</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1733429.071456906</t>
+          <t>-1532437.84859698</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1903538.0</t>
+          <t>4541875.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>121.223</t>
+          <t>77.947</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-25.48</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-12.32</t>
+          <t>-13.04</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,17 +4024,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>405</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-7.61</t>
+          <t>-7.50</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>27.22</v>
+        <v>26.86</v>
       </c>
       <c r="AN9" t="n">
-        <v>26.8</v>
+        <v>26.79</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>25.87</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-165.59</t>
+          <t>-116.96</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,53 +4100,53 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-107.29</t>
+          <t>-110.30</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/10/22</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>60785138.49644381</t>
+          <t>60721536.49644886</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2962769.0</t>
+          <t>1903538.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>5056298.4</v>
+        <v>3963383.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5511802.7</t>
+          <t>5318222.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>10116244</v>
+        <v>10129541.2</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-455504</t>
+          <t>-1354839</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1408218.425118476</t>
+          <t>-1458250.832247465</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1675972.244419054</t>
+          <t>-1733429.071456906</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>2962769.0</t>
+          <t>1903538.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>171.268</t>
+          <t>121.223</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-9.11</t>
+          <t>-12.32</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,54 +4454,54 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>405</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-7.61</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>27.43</v>
+        <v>27.22</v>
       </c>
       <c r="AN10" t="n">
-        <v>26.81</v>
+        <v>26.8</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4510,17 +4510,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-273.08</t>
+          <t>-165.59</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,53 +4530,53 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.27</t>
+          <t>-107.29</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/10/22</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>60785138.49644381</t>
+          <t>60721536.49644886</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>4341397.0</t>
+          <t>2962769.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>5404572</v>
+        <v>5056298.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5443936.9</t>
+          <t>5511802.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>10090356.22</v>
+        <v>10116244</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-39364</t>
+          <t>-455504</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1359535.912518371</t>
+          <t>-1408218.425118476</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1647523.947064298</t>
+          <t>-1675972.244419054</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>4341397.0</t>
+          <t>2962769.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>229.109</t>
+          <t>171.268</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-13.04</t>
+          <t>-9.11</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>405</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>27.58</v>
+        <v>27.43</v>
       </c>
       <c r="AN11" t="n">
         <v>26.81</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>25.84</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-960.20</t>
+          <t>-273.08</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,53 +4960,53 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-101.36</t>
+          <t>-104.27</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/10/22</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>60785138.49644381</t>
+          <t>60721536.49644886</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>5694285.0</t>
+          <t>4341397.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>5256519.2</v>
+        <v>5404572</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5382212.9</t>
+          <t>5443936.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>10042035.4</v>
+        <v>10090356.22</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-125693</t>
+          <t>-39364</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1307174.451691839</t>
+          <t>-1359535.912518371</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1695753.524162351</t>
+          <t>-1647523.947064298</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>5694285.0</t>
+          <t>4341397.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>194.645</t>
+          <t>229.109</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-13.04</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>405</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,39 +5329,39 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>27.77</v>
+        <v>27.58</v>
       </c>
       <c r="AN12" t="n">
-        <v>26.82</v>
+        <v>26.81</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5370,17 +5370,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-545.29</t>
+          <t>-960.20</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,53 +5390,53 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-98.10</t>
+          <t>-101.36</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/10/22</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>60785138.49644381</t>
+          <t>60721536.49644886</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>4914929.0</t>
+          <t>5694285.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>4934352.4</v>
+        <v>5256519.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5195209.4</t>
+          <t>5382212.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>9975089.699999999</v>
+        <v>10042035.4</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-260857</t>
+          <t>-125693</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1236523.711242655</t>
+          <t>-1307174.451691839</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1849042.579868057</t>
+          <t>-1695753.524162351</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>4914929.0</t>
+          <t>5694285.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>-18.88</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-21.97</t>
+          <t>-19.94</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,49 +5749,49 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>75.85</t>
+          <t>86.11</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-6.16</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>13.52</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>13.71</v>
+        <v>13.7</v>
       </c>
       <c r="AN13" t="n">
-        <v>14.24</v>
+        <v>14.21</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5800,19 +5800,19 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>18.80</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
           <t>-0.27</t>
         </is>
       </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
       <c r="AS13" t="inlineStr">
         <is>
           <t>2.34</t>
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-112.13</t>
+          <t>-111.58</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>7321.912607449856</t>
+          <t>7312.167381974248</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>516.0</t>
+          <t>340.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>534.6</v>
+        <v>360</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>437.4</t>
+          <t>443.8</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>468.04</v>
+        <v>464.82</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>-83</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-12.02299824989772</t>
+          <t>-13.94522520253159</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-18.58438332743214</t>
+          <t>-24.51747344201789</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>516.0</t>
+          <t>340.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.78</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>524</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5991,27 +5991,27 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>14.05</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-22.25</t>
+          <t>-21.97</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,49 +6179,49 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>60.36</t>
+          <t>75.85</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>13.42</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>13.74</v>
+        <v>13.71</v>
       </c>
       <c r="AN14" t="n">
-        <v>14.28</v>
+        <v>14.24</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6230,19 +6230,19 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
           <t>-0.28</t>
         </is>
       </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>-0.29</t>
-        </is>
-      </c>
       <c r="AS14" t="inlineStr">
         <is>
           <t>2.34</t>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-112.32</t>
+          <t>-112.13</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>7321.912607449856</t>
+          <t>7312.167381974248</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>516.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>472.6</v>
+        <v>534.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>402.3</t>
+          <t>437.4</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>481.38</v>
+        <v>468.04</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>97</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-10.83001914489146</t>
+          <t>-12.02299824989772</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-28.30195518775838</t>
+          <t>-18.58438332743214</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>516.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.78</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>524</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6463,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,63 +6609,63 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>60.36</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.83</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>13.77</v>
+        <v>13.74</v>
       </c>
       <c r="AN15" t="n">
-        <v>14.31</v>
+        <v>14.28</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-112.36</t>
+          <t>-112.32</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>7321.912607449856</t>
+          <t>7312.167381974248</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>507.6</v>
+        <v>472.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>424.0</t>
+          <t>402.3</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>517.4400000000001</v>
+        <v>481.38</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-7.653303500733839</t>
+          <t>-10.83001914489146</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>3.719440554195444</t>
+          <t>-28.30195518775838</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.78</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>524</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6851,22 +6851,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-22.83</t>
+          <t>-22.25</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,49 +7039,49 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>13.8</v>
+        <v>13.77</v>
       </c>
       <c r="AN16" t="n">
-        <v>14.35</v>
+        <v>14.31</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7090,12 +7090,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-112.26</t>
+          <t>-112.36</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>7321.912607449856</t>
+          <t>7312.167381974248</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>459.6</v>
+        <v>507.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>420.3</t>
+          <t>424.0</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>554.86</v>
+        <v>517.4400000000001</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-9.721075147084617</t>
+          <t>-7.653303500733839</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-6.061402691377396</t>
+          <t>3.719440554195444</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-4.30</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.78</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>524</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7281,27 +7281,27 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-9.92</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,49 +7469,49 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.83</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>13.83</v>
+        <v>13.8</v>
       </c>
       <c r="AN17" t="n">
-        <v>14.41</v>
+        <v>14.35</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7520,17 +7520,17 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-12.91</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-111.98</t>
+          <t>-112.26</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>7321.912607449856</t>
+          <t>7312.167381974248</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>1213.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>527.6</v>
+        <v>459.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>585.7</t>
+          <t>420.3</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>567.6799999999999</v>
+        <v>554.86</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-58</t>
+          <t>39</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-10.38647013903138</t>
+          <t>-9.721075147084617</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>21.00387133963898</t>
+          <t>-6.061402691377396</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>1213.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.78</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>524</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7711,12 +7711,12 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-31.65</t>
+          <t>-9.92</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,49 +7899,49 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>13.86</v>
+        <v>13.83</v>
       </c>
       <c r="AN18" t="n">
-        <v>14.48</v>
+        <v>14.41</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-16.60</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-111.60</t>
+          <t>-111.98</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>7321.912607449856</t>
+          <t>7312.167381974248</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>1213.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>340.2</v>
+        <v>527.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>497.7</t>
+          <t>585.7</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>555.26</v>
+        <v>567.6799999999999</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-157</t>
+          <t>-58</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-16.09380495333509</t>
+          <t>-10.38647013903138</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-46.08158973532466</t>
+          <t>21.00387133963898</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>1213.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.78</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>524</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8141,22 +8141,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-48.73</t>
+          <t>-31.65</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-24.86</t>
+          <t>-22.83</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,49 +8329,49 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>13.43</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>13.9</v>
+        <v>13.86</v>
       </c>
       <c r="AN19" t="n">
-        <v>14.55</v>
+        <v>14.48</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8380,17 +8380,17 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-19.79</t>
+          <t>-16.60</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-111.11</t>
+          <t>-111.60</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>7321.912607449856</t>
+          <t>7312.167381974248</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>332</v>
+        <v>340.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>647.5</t>
+          <t>497.7</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>577.0599999999999</v>
+        <v>555.26</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-315</t>
+          <t>-157</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-10.6414804475188</t>
+          <t>-16.09380495333509</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-32.37933449472541</t>
+          <t>-46.08158973532466</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-4.30</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,17 +8511,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.78</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>524</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8571,27 +8571,27 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
+          <t>12.9</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
           <t>13.4</t>
         </is>
       </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>13.55</t>
-        </is>
-      </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-45.61</t>
+          <t>-48.73</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-23.12</t>
+          <t>-24.86</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,34 +8774,34 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-3.20</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>13.62</t>
+          <t>13.43</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>13.95</v>
+        <v>13.9</v>
       </c>
       <c r="AN20" t="n">
-        <v>14.64</v>
+        <v>14.55</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8810,17 +8810,17 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-19.79</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-110.56</t>
+          <t>-111.11</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>7321.912607449856</t>
+          <t>7312.167381974248</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>374.0</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>340.4</v>
+        <v>332</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>625.9</t>
+          <t>647.5</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>605.1799999999999</v>
+        <v>577.0599999999999</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-285</t>
+          <t>-315</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-6.68914334802669</t>
+          <t>-10.6414804475188</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-18.71970791905761</t>
+          <t>-32.37933449472541</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>374.0</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.78</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>524</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9001,27 +9001,27 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>13.15</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9043,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-36.19</t>
+          <t>-45.61</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-21.39</t>
+          <t>-23.12</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,34 +9204,34 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>13.62</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>13.98</v>
+        <v>13.95</v>
       </c>
       <c r="AN21" t="n">
-        <v>14.71</v>
+        <v>14.64</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9240,17 +9240,17 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-110.37</t>
+          <t>-110.56</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>7321.912607449856</t>
+          <t>7312.167381974248</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>374.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>381</v>
+        <v>340.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>597.1</t>
+          <t>625.9</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>630.02</v>
+        <v>605.1799999999999</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-216</t>
+          <t>-285</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-4.501767971475612</t>
+          <t>-6.68914334802669</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-9.46596609956589</t>
+          <t>-18.71970791905761</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>374.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.78</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>524</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9431,27 +9431,27 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
+          <t>13.6</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
           <t>13.65</t>
         </is>
       </c>
-      <c r="CE21" t="inlineStr">
-        <is>
-          <t>13.95</t>
-        </is>
-      </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>13.15</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>-36.19</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9629,58 +9629,58 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>14</v>
+        <v>13.98</v>
       </c>
       <c r="AN22" t="n">
-        <v>14.79</v>
+        <v>14.71</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-110.48</t>
+          <t>-110.37</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>7321.912607449856</t>
+          <t>7312.167381974248</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>276.0</t>
+          <t>573.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>643.8</v>
+        <v>381</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>572.3</t>
+          <t>597.1</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>643.84</v>
+        <v>630.02</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>-216</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-3.599186493641016</t>
+          <t>-4.501767971475612</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-17.22969328245046</t>
+          <t>-9.46596609956589</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>276.0</t>
+          <t>573.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.78</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>524</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9861,17 +9861,17 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.95</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>16.38</t>
+          <t>12.49</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-21.10</t>
+          <t>-21.39</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,39 +10059,39 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>14.03</t>
         </is>
       </c>
       <c r="AM23" t="n">
         <v>14</v>
       </c>
       <c r="AN23" t="n">
-        <v>14.87</v>
+        <v>14.79</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10100,12 +10100,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>21.76</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-110.76</t>
+          <t>-110.48</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>7321.912607449856</t>
+          <t>7312.167381974248</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>276.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>655.2</v>
+        <v>643.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>572.3</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>675</v>
+        <v>643.84</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-1.120912532039299</t>
+          <t>-3.599186493641016</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>4.116042644944969</t>
+          <t>-17.22969328245046</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>276.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.78</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>524</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10291,17 +10291,17 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
@@ -10311,7 +10311,7 @@
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10343,12 +10343,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>908.595</t>
+          <t>680.189</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-13.85</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-9.03</t>
+          <t>-8.36</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -10453,17 +10453,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -10474,75 +10474,75 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>680</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-7.85</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AM24" t="n">
-        <v>35.67</v>
+        <v>35.52</v>
       </c>
       <c r="AN24" t="n">
-        <v>38.71</v>
+        <v>38.55</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>37.74</t>
+          <t>37.78</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
           <t>-1.17</t>
         </is>
       </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>-1.17</t>
-        </is>
-      </c>
       <c r="AS24" t="inlineStr">
         <is>
           <t>3.65</t>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>-132.13</t>
+          <t>-131.97</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -10560,43 +10560,43 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>232357841.1296562</t>
+          <t>232075095.6437768</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>30779178.0</t>
+          <t>23145831.0</t>
         </is>
       </c>
       <c r="AX24" t="n">
-        <v>30495285.4</v>
+        <v>28055340.4</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>35145840.3</t>
+          <t>32565131.1</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>228943265.06</v>
+        <v>214383272.46</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>-4650554</t>
+          <t>-4509790</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>-20884304.84373562</t>
+          <t>-20081972.26747796</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-16550796.89101397</t>
+          <t>-15669143.09806082</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>30779178.0</t>
+          <t>23145831.0</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -10671,7 +10671,7 @@
       </c>
       <c r="BS24" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BT24" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="BY24" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
@@ -10736,12 +10736,12 @@
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -10773,12 +10773,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>797.737</t>
+          <t>908.595</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -10798,17 +10798,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-24.16</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -10873,7 +10873,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-8.36</t>
+          <t>-9.03</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -10883,17 +10883,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -10904,63 +10904,63 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>680</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>60.49</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>-7.74</t>
+          <t>-7.84</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>34.43</t>
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>35.81</v>
+        <v>35.67</v>
       </c>
       <c r="AN25" t="n">
-        <v>38.81</v>
+        <v>38.71</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.74</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>-132.14</t>
+          <t>-132.13</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -10990,43 +10990,43 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>232357841.1296562</t>
+          <t>232075095.6437768</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>27224823.0</t>
+          <t>30779178.0</t>
         </is>
       </c>
       <c r="AX25" t="n">
-        <v>30219756.2</v>
+        <v>30495285.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>39847131.9</t>
+          <t>35145840.3</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>236001176.02</v>
+        <v>228943265.06</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>-9627375</t>
+          <t>-4650554</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>-21672215.3805941</t>
+          <t>-20884304.84373562</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-18037061.02769653</t>
+          <t>-16550796.89101397</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>27224823.0</t>
+          <t>30779178.0</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -11046,7 +11046,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="BS25" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="BT25" t="inlineStr">
@@ -11131,12 +11131,12 @@
       </c>
       <c r="BY25" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -11156,22 +11156,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -11203,42 +11203,42 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>-2.01</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>797.737</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>652.267</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>34.7</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>-2.81</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-30.44</t>
+          <t>-24.16</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-6.47</t>
+          <t>-8.36</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -11313,17 +11313,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -11334,63 +11334,63 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>680</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>60.49</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-7.74</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>34.47</t>
+          <t>34.54</t>
         </is>
       </c>
       <c r="AM26" t="n">
-        <v>35.98</v>
+        <v>35.81</v>
       </c>
       <c r="AN26" t="n">
-        <v>38.91</v>
+        <v>38.81</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>37.67</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>-132.19</t>
+          <t>-132.14</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -11420,43 +11420,43 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>232357841.1296562</t>
+          <t>232075095.6437768</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>22638246.0</t>
+          <t>27224823.0</t>
         </is>
       </c>
       <c r="AX26" t="n">
-        <v>32529604.8</v>
+        <v>30219756.2</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>46763411.2</t>
+          <t>39847131.9</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>241442940.72</v>
+        <v>236001176.02</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>-14233806</t>
+          <t>-9627375</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>-22333152.53566639</t>
+          <t>-21672215.3805941</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-19135291.00768245</t>
+          <t>-18037061.02769653</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>22638246.0</t>
+          <t>27224823.0</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="BS26" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BT26" t="inlineStr">
@@ -11561,12 +11561,12 @@
       </c>
       <c r="BY26" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -11591,17 +11591,17 @@
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -11623,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11633,12 +11633,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1052.554</t>
+          <t>652.267</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11658,17 +11658,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-26.38</t>
+          <t>-30.44</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -11743,17 +11743,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -11764,12 +11764,12 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>680</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -11779,53 +11779,53 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>48.28</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>34.39</t>
+          <t>34.47</t>
         </is>
       </c>
       <c r="AM27" t="n">
-        <v>36.08</v>
+        <v>35.98</v>
       </c>
       <c r="AN27" t="n">
-        <v>38.92</v>
+        <v>38.91</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>37.67</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>-132.25</t>
+          <t>-132.19</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -11850,43 +11850,43 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>232357841.1296562</t>
+          <t>232075095.6437768</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>36488624.0</t>
+          <t>22638246.0</t>
         </is>
       </c>
       <c r="AX27" t="n">
-        <v>37237782</v>
+        <v>32529604.8</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>50581063.8</t>
+          <t>46763411.2</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>242256442.44</v>
+        <v>241442940.72</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>-13343281</t>
+          <t>-14233806</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>-22914581.90439074</t>
+          <t>-22333152.53566639</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-19529368.76453082</t>
+          <t>-19135291.00768245</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>36488624.0</t>
+          <t>22638246.0</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -11991,12 +11991,12 @@
       </c>
       <c r="BY27" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -12016,17 +12016,17 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1012.048</t>
+          <t>1052.554</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -12088,17 +12088,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-30.50</t>
+          <t>-26.38</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -12173,17 +12173,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -12194,73 +12194,73 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>680</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>48.21</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>48.28</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>34.41</t>
+          <t>34.39</t>
         </is>
       </c>
       <c r="AM28" t="n">
-        <v>36.18</v>
+        <v>36.08</v>
       </c>
       <c r="AN28" t="n">
-        <v>38.94</v>
+        <v>38.92</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>37.63</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>-131.94</t>
+          <t>-132.25</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -12280,43 +12280,43 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>232357841.1296562</t>
+          <t>232075095.6437768</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>35345556.0</t>
+          <t>36488624.0</t>
         </is>
       </c>
       <c r="AX28" t="n">
-        <v>37074921.8</v>
+        <v>37237782</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>53345322.1</t>
+          <t>50581063.8</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>245778298.12</v>
+        <v>242256442.44</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>-16270400</t>
+          <t>-13343281</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>-23530075.2025471</t>
+          <t>-22914581.90439074</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-20878828.60415238</t>
+          <t>-19529368.76453082</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>35345556.0</t>
+          <t>36488624.0</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -12381,17 +12381,17 @@
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS28" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="BT28" t="inlineStr">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="BY28" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -12446,22 +12446,22 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -12493,12 +12493,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>857.193</t>
+          <t>1012.048</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -12518,17 +12518,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-31.65</t>
+          <t>-30.50</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-7.55</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -12603,17 +12603,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -12624,73 +12624,73 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>680</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>48.21</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>10.92</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>34.16</t>
+          <t>34.41</t>
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>36.33</v>
+        <v>36.18</v>
       </c>
       <c r="AN29" t="n">
-        <v>39</v>
+        <v>38.94</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>37.52</t>
+          <t>37.58</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>-131.18</t>
+          <t>-131.94</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -12710,43 +12710,43 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>232357841.1296562</t>
+          <t>232075095.6437768</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>29401532.0</t>
+          <t>35345556.0</t>
         </is>
       </c>
       <c r="AX29" t="n">
-        <v>39796395.2</v>
+        <v>37074921.8</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>58228190.4</t>
+          <t>53345322.1</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>247556548.26</v>
+        <v>245778298.12</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>-18431795</t>
+          <t>-16270400</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>-24012120.03861886</t>
+          <t>-23530075.2025471</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>-21938484.35346347</t>
+          <t>-20878828.60415238</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>29401532.0</t>
+          <t>35345556.0</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS29" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BT29" t="inlineStr">
@@ -12851,12 +12851,12 @@
       </c>
       <c r="BY29" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ29" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="CA29" t="inlineStr">
@@ -12876,22 +12876,22 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1145.3</t>
+          <t>857.193</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -12938,7 +12938,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>33.65</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -12948,17 +12948,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-25.49</t>
+          <t>-31.65</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -13023,7 +13023,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-9.30</t>
+          <t>-7.55</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -13033,17 +13033,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -13054,73 +13054,73 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>680</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>10.92</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>-6.49</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>34.11999999999999</t>
+          <t>34.16</t>
         </is>
       </c>
       <c r="AM30" t="n">
-        <v>36.49</v>
+        <v>36.33</v>
       </c>
       <c r="AN30" t="n">
-        <v>39.06</v>
+        <v>39</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>37.47</t>
+          <t>37.52</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>-26.04</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>-129.70</t>
+          <t>-131.18</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -13140,43 +13140,43 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>232357841.1296562</t>
+          <t>232075095.6437768</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>38774066.0</t>
+          <t>29401532.0</t>
         </is>
       </c>
       <c r="AX30" t="n">
-        <v>49474507.6</v>
+        <v>39796395.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>66401056.1</t>
+          <t>58228190.4</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>249662887.18</v>
+        <v>247556548.26</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>-16926548</t>
+          <t>-18431795</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>-24389144.70864711</t>
+          <t>-24012120.03861886</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>-22031901.26842704</t>
+          <t>-21938484.35346347</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>38774066.0</t>
+          <t>29401532.0</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
@@ -13196,7 +13196,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="BS30" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="BT30" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="BY30" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ30" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="CA30" t="inlineStr">
@@ -13306,22 +13306,22 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.55</t>
         </is>
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>33.65</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1345.621</t>
+          <t>1145.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>33.65</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -13378,17 +13378,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-27.63</t>
+          <t>-25.49</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-7.55</t>
+          <t>-9.30</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -13463,17 +13463,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -13484,17 +13484,17 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>680</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>13.92</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
@@ -13504,7 +13504,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
@@ -13514,43 +13514,43 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-6.2</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>34.33</t>
+          <t>34.11999999999999</t>
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>36.71</v>
+        <v>36.49</v>
       </c>
       <c r="AN31" t="n">
-        <v>39.14</v>
+        <v>39.06</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>37.43</t>
+          <t>37.47</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>-27.70</t>
+          <t>-26.04</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>-127.76</t>
+          <t>-129.70</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -13570,43 +13570,43 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>232357841.1296562</t>
+          <t>232075095.6437768</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>46179132.0</t>
+          <t>38774066.0</t>
         </is>
       </c>
       <c r="AX31" t="n">
-        <v>60997217.6</v>
+        <v>49474507.6</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>84286762.5</t>
+          <t>66401056.1</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>254822433.06</v>
+        <v>249662887.18</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>-23289544</t>
+          <t>-16926548</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>-24817734.42505076</t>
+          <t>-24389144.70864711</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>-22382700.45878832</t>
+          <t>-22031901.26842704</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>46179132.0</t>
+          <t>38774066.0</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -13671,7 +13671,7 @@
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="BS31" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="BT31" t="inlineStr">
@@ -13711,12 +13711,12 @@
       </c>
       <c r="BY31" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ31" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="CA31" t="inlineStr">
@@ -13736,22 +13736,22 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>34.05</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>33.65</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -13783,12 +13783,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1029.736</t>
+          <t>1345.621</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -13798,7 +13798,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13808,17 +13808,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-32.40</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-6.20</t>
+          <t>-7.55</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -13893,17 +13893,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -13914,73 +13914,73 @@
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>680</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>13.92</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-6.49</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-6.2</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>34.33</t>
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>36.88</v>
+        <v>36.71</v>
       </c>
       <c r="AN32" t="n">
-        <v>39.24</v>
+        <v>39.14</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>37.43</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>-32.46</t>
+          <t>-27.70</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>-125.84</t>
+          <t>-127.76</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -14000,43 +14000,43 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>232357841.1296562</t>
+          <t>232075095.6437768</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>35674323.0</t>
+          <t>46179132.0</t>
         </is>
       </c>
       <c r="AX32" t="n">
-        <v>63924345.6</v>
+        <v>60997217.6</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>94556424.4</t>
+          <t>84286762.5</t>
         </is>
       </c>
       <c r="AZ32" t="n">
-        <v>256700200.08</v>
+        <v>254822433.06</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>-30632078</t>
+          <t>-23289544</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>-25260467.87346211</t>
+          <t>-24817734.42505076</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>-22877859.92863344</t>
+          <t>-22382700.45878832</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>35674323.0</t>
+          <t>46179132.0</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
@@ -14101,7 +14101,7 @@
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="BS32" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="BT32" t="inlineStr">
@@ -14141,12 +14141,12 @@
       </c>
       <c r="BY32" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ32" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="CA32" t="inlineStr">
@@ -14166,22 +14166,22 @@
       </c>
       <c r="CD32" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.05</t>
         </is>
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>34.85</t>
         </is>
       </c>
       <c r="CF32" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="CG32" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CH32" t="inlineStr">
@@ -14213,12 +14213,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1450.779</t>
+          <t>1029.736</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -14238,17 +14238,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-37.05</t>
+          <t>-32.40</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-9.03</t>
+          <t>-6.20</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -14323,17 +14323,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -14344,73 +14344,73 @@
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>680</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>35.22000000000001</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AM33" t="n">
-        <v>37.06</v>
+        <v>36.88</v>
       </c>
       <c r="AN33" t="n">
-        <v>39.33</v>
+        <v>39.24</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>37.33</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>-41.33</t>
+          <t>-32.46</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -14420,7 +14420,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>-123.74</t>
+          <t>-125.84</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -14430,43 +14430,43 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>232357841.1296562</t>
+          <t>232075095.6437768</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>48952923.0</t>
+          <t>35674323.0</t>
         </is>
       </c>
       <c r="AX33" t="n">
-        <v>69615722.40000001</v>
+        <v>63924345.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>110580229.2</t>
+          <t>94556424.4</t>
         </is>
       </c>
       <c r="AZ33" t="n">
-        <v>258176781.58</v>
+        <v>256700200.08</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>-40964506</t>
+          <t>-30632078</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>-25693669.31797642</t>
+          <t>-25260467.87346211</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>-21642648.9238181</t>
+          <t>-22877859.92863344</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>48952923.0</t>
+          <t>35674323.0</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
@@ -14486,7 +14486,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR33" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
@@ -14571,12 +14571,12 @@
       </c>
       <c r="BY33" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ33" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="CA33" t="inlineStr">
@@ -14596,22 +14596,22 @@
       </c>
       <c r="CD33" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CE33" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="CF33" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CG33" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CH33" t="inlineStr">
@@ -14643,12 +14643,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2260.366</t>
+          <t>1450.779</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -14668,17 +14668,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-32.59</t>
+          <t>-37.05</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-8.09</t>
+          <t>-9.03</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -14753,17 +14753,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -14774,12 +14774,12 @@
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>680</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -14794,53 +14794,53 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>36.01000000000001</t>
+          <t>35.22000000000001</t>
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>37.29</v>
+        <v>37.06</v>
       </c>
       <c r="AN34" t="n">
-        <v>39.43</v>
+        <v>39.33</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.33</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>-37.57</t>
+          <t>-41.33</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>-121.29</t>
+          <t>-123.74</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -14860,43 +14860,43 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>232357841.1296562</t>
+          <t>232075095.6437768</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>77792094.0</t>
+          <t>48952923.0</t>
         </is>
       </c>
       <c r="AX34" t="n">
-        <v>76659985.59999999</v>
+        <v>69615722.40000001</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>113715310.1</t>
+          <t>110580229.2</t>
         </is>
       </c>
       <c r="AZ34" t="n">
-        <v>261926998.4</v>
+        <v>258176781.58</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>-37055324</t>
+          <t>-40964506</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>-26430218.48055065</t>
+          <t>-25693669.31797642</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>-20527817.16965982</t>
+          <t>-21642648.9238181</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>77792094.0</t>
+          <t>48952923.0</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
@@ -14961,7 +14961,7 @@
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
@@ -14971,7 +14971,7 @@
       </c>
       <c r="BS34" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="BT34" t="inlineStr">
@@ -15001,12 +15001,12 @@
       </c>
       <c r="BY34" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ34" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="CA34" t="inlineStr">
@@ -15026,22 +15026,22 @@
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CE34" t="inlineStr">
         <is>
-          <t>35.25</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="CF34" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="CG34" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CH34" t="inlineStr">

--- a/Result/checksun_type/玻璃基板.xlsx
+++ b/Result/checksun_type/玻璃基板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>405.481</t>
+          <t>195.468</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>7.20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>195</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>25.53</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>25.75</v>
+        <v>25.7</v>
       </c>
       <c r="AN2" t="n">
         <v>26.79</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>25.99</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>25.17</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-118.68</t>
+          <t>-117.58</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>60721536.49644886</t>
+          <t>60646486.5</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>10672887.0</t>
+          <t>5207526.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>3809271.8</v>
+        <v>4629628.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3609459.7</t>
+          <t>3696072.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>10245696.52</v>
+        <v>10084690.88</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>199812</t>
+          <t>933555</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1272664.425946395</t>
+          <t>-1139146.523469412</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-514216.6070431024</t>
+          <t>-404798.0598460007</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>10672887.0</t>
+          <t>5207526.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>27.05</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>103.242</t>
+          <t>405.481</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-24.98</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-10.54</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>195</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>25.78</v>
+        <v>25.75</v>
       </c>
       <c r="AN3" t="n">
-        <v>26.78</v>
+        <v>26.79</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>25.96</t>
+          <t>25.99</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-10.00</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-119.17</t>
+          <t>-118.68</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>60721536.49644886</t>
+          <t>60646486.5</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2585925.0</t>
+          <t>10672887.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2334426.2</v>
+        <v>3809271.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3111599.5</t>
+          <t>3609459.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>10171307.16</v>
+        <v>10245696.52</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-777173</t>
+          <t>199812</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1410564.029383358</t>
+          <t>-1272664.425946395</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1237738.331358852</t>
+          <t>-514216.6070431024</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2585925.0</t>
+          <t>10672887.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>27.05</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>57.864</t>
+          <t>103.242</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-24.98</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-11.61</t>
+          <t>-10.54</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>195</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>50.45</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>25.88</v>
+        <v>25.78</v>
       </c>
       <c r="AN4" t="n">
         <v>26.78</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>25.96</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-18.27</t>
+          <t>-10.00</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-118.69</t>
+          <t>-119.17</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>60721536.49644886</t>
+          <t>60646486.5</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1431397.0</t>
+          <t>2585925.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2725616.2</v>
+        <v>2334426.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3344499.9</t>
+          <t>3111599.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>10170725.72</v>
+        <v>10171307.16</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-618883</t>
+          <t>-777173</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1441986.883569631</t>
+          <t>-1410564.029383358</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1360675.639975678</t>
+          <t>-1237738.331358852</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1431397.0</t>
+          <t>2585925.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>129.907</t>
+          <t>57.864</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.82</t>
+          <t>-11.61</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,63 +2304,63 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>195</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>50.45</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>26.04</v>
+        <v>25.88</v>
       </c>
       <c r="AN5" t="n">
-        <v>26.79</v>
+        <v>26.78</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>25.92</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-23.75</t>
+          <t>-18.27</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-117.83</t>
+          <t>-118.69</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>60721536.49644886</t>
+          <t>60646486.5</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3250406.0</t>
+          <t>1431397.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>2820044.4</v>
+        <v>2725616.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3938171.4</t>
+          <t>3344499.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>10185422.26</v>
+        <v>10170725.72</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1118127</t>
+          <t>-618883</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1456770.746041259</t>
+          <t>-1441986.883569631</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1364005.379429155</t>
+          <t>-1360675.639975678</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>3250406.0</t>
+          <t>1431397.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>44.221</t>
+          <t>129.907</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-32.35</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-10.89</t>
+          <t>-9.82</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>195</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>26.18</v>
+        <v>26.04</v>
       </c>
       <c r="AN6" t="n">
-        <v>26.78</v>
+        <v>26.79</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-39.44</t>
+          <t>-23.75</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-116.78</t>
+          <t>-117.83</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>60721536.49644886</t>
+          <t>60646486.5</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1105744.0</t>
+          <t>3250406.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>2762517</v>
+        <v>2820044.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>4083544.5</t>
+          <t>3938171.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>10163096.92</v>
+        <v>10185422.26</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1321027</t>
+          <t>-1118127</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1473637.176334369</t>
+          <t>-1456770.746041259</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1514941.493668794</t>
+          <t>-1364005.379429155</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1105744.0</t>
+          <t>3250406.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>132.605</t>
+          <t>44.221</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-21.31</t>
+          <t>-32.35</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-11.07</t>
+          <t>-10.89</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,12 +3143,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>195</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>24.68</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>26.38</v>
+        <v>26.18</v>
       </c>
       <c r="AN7" t="n">
         <v>26.78</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-56.92</t>
+          <t>-39.44</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-115.12</t>
+          <t>-116.78</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>60721536.49644886</t>
+          <t>60646486.5</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3298659.0</t>
+          <t>1105744.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>3409647.6</v>
+        <v>2762517</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>4333083.4</t>
+          <t>4083544.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>10178782.26</v>
+        <v>10163096.92</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-923435</t>
+          <t>-1321027</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1466127.300455383</t>
+          <t>-1473637.176334369</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1446674.246380107</t>
+          <t>-1514941.493668794</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>3298659.0</t>
+          <t>1105744.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>182.531</t>
+          <t>132.605</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-11.85</t>
+          <t>-21.31</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-11.96</t>
+          <t>-11.07</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>195</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>24.78</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>26.62</v>
+        <v>26.38</v>
       </c>
       <c r="AN8" t="n">
-        <v>26.79</v>
+        <v>26.78</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-82.30</t>
+          <t>-56.92</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-112.97</t>
+          <t>-115.12</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>60721536.49644886</t>
+          <t>60646486.5</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>4541875.0</t>
+          <t>3298659.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>3888772.8</v>
+        <v>3409647.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4411562.6</t>
+          <t>4333083.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>10182869.32</v>
+        <v>10178782.26</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-522789</t>
+          <t>-923435</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1469664.21937816</t>
+          <t>-1466127.300455383</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1532437.84859698</t>
+          <t>-1446674.246380107</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>4541875.0</t>
+          <t>3298659.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>77.947</t>
+          <t>182.531</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-25.48</t>
+          <t>-11.85</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-13.04</t>
+          <t>-11.96</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>195</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-7.50</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.67</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>26.86</v>
+        <v>26.62</v>
       </c>
       <c r="AN9" t="n">
         <v>26.79</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>25.87</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-116.96</t>
+          <t>-82.30</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-110.30</t>
+          <t>-112.97</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>60721536.49644886</t>
+          <t>60646486.5</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1903538.0</t>
+          <t>4541875.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>3963383.6</v>
+        <v>3888772.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5318222.8</t>
+          <t>4411562.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>10129541.2</v>
+        <v>10182869.32</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1354839</t>
+          <t>-522789</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1458250.832247465</t>
+          <t>-1469664.21937816</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1733429.071456906</t>
+          <t>-1532437.84859698</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1903538.0</t>
+          <t>4541875.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>121.223</t>
+          <t>77.947</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-25.48</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-12.32</t>
+          <t>-13.04</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,17 +4454,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>195</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-7.61</t>
+          <t>-7.50</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>27.22</v>
+        <v>26.86</v>
       </c>
       <c r="AN10" t="n">
-        <v>26.8</v>
+        <v>26.79</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>25.87</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-165.59</t>
+          <t>-116.96</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-107.29</t>
+          <t>-110.30</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>60721536.49644886</t>
+          <t>60646486.5</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2962769.0</t>
+          <t>1903538.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>5056298.4</v>
+        <v>3963383.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5511802.7</t>
+          <t>5318222.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>10116244</v>
+        <v>10129541.2</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-455504</t>
+          <t>-1354839</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1408218.425118476</t>
+          <t>-1458250.832247465</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1675972.244419054</t>
+          <t>-1733429.071456906</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>2962769.0</t>
+          <t>1903538.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>171.268</t>
+          <t>121.223</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-9.11</t>
+          <t>-12.32</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,54 +4884,54 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>195</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-7.61</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>27.43</v>
+        <v>27.22</v>
       </c>
       <c r="AN11" t="n">
-        <v>26.81</v>
+        <v>26.8</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -4940,17 +4940,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-273.08</t>
+          <t>-165.59</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.27</t>
+          <t>-107.29</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>60721536.49644886</t>
+          <t>60646486.5</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>4341397.0</t>
+          <t>2962769.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>5404572</v>
+        <v>5056298.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5443936.9</t>
+          <t>5511802.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>10090356.22</v>
+        <v>10116244</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-39364</t>
+          <t>-455504</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1359535.912518371</t>
+          <t>-1408218.425118476</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1647523.947064298</t>
+          <t>-1675972.244419054</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>4341397.0</t>
+          <t>2962769.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>229.109</t>
+          <t>171.268</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-13.04</t>
+          <t>-9.11</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>195</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>27.58</v>
+        <v>27.43</v>
       </c>
       <c r="AN12" t="n">
         <v>26.81</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>25.84</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-960.20</t>
+          <t>-273.08</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-101.36</t>
+          <t>-104.27</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>60721536.49644886</t>
+          <t>60646486.5</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>5694285.0</t>
+          <t>4341397.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>5256519.2</v>
+        <v>5404572</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5382212.9</t>
+          <t>5443936.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>10042035.4</v>
+        <v>10090356.22</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-125693</t>
+          <t>-39364</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1307174.451691839</t>
+          <t>-1359535.912518371</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1695753.524162351</t>
+          <t>-1647523.947064298</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>5694285.0</t>
+          <t>4341397.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-18.88</t>
+          <t>-14.07</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-19.94</t>
+          <t>-21.39</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,49 +5749,49 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>86.11</t>
+          <t>84.64</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-6.16</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>13.52</t>
+          <t>13.57</t>
         </is>
       </c>
       <c r="AM13" t="n">
         <v>13.7</v>
       </c>
       <c r="AN13" t="n">
-        <v>14.21</v>
+        <v>14.17</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5800,17 +5800,17 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>18.80</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-111.58</t>
+          <t>-110.99</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>7312.167381974248</t>
+          <t>7302.072857142857</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>340.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>360</v>
+        <v>346.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>443.8</t>
+          <t>402.9</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>464.82</v>
+        <v>457.34</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-83</t>
+          <t>-56</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-13.94522520253159</t>
+          <t>-18.14714435386173</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-24.51747344201789</t>
+          <t>-41.25769968617749</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>340.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>30.78</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>90.83</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>515</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5991,27 +5991,27 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>-18.88</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-21.97</t>
+          <t>-19.94</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,49 +6179,49 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>75.85</t>
+          <t>86.11</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-6.16</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>13.52</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>13.71</v>
+        <v>13.7</v>
       </c>
       <c r="AN14" t="n">
-        <v>14.24</v>
+        <v>14.21</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6230,19 +6230,19 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>18.80</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
           <t>-0.27</t>
         </is>
       </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
       <c r="AS14" t="inlineStr">
         <is>
           <t>2.34</t>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-112.13</t>
+          <t>-111.58</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>7312.167381974248</t>
+          <t>7302.072857142857</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>516.0</t>
+          <t>340.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>534.6</v>
+        <v>360</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>437.4</t>
+          <t>443.8</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>468.04</v>
+        <v>464.82</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>-83</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-12.02299824989772</t>
+          <t>-13.94522520253159</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-18.58438332743214</t>
+          <t>-24.51747344201789</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>516.0</t>
+          <t>340.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>30.78</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>90.83</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>515</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6421,27 +6421,27 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>14.05</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-22.25</t>
+          <t>-21.97</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,49 +6609,49 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>60.36</t>
+          <t>75.85</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>13.42</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>13.74</v>
+        <v>13.71</v>
       </c>
       <c r="AN15" t="n">
-        <v>14.28</v>
+        <v>14.24</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6660,19 +6660,19 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
           <t>-0.28</t>
         </is>
       </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>-0.29</t>
-        </is>
-      </c>
       <c r="AS15" t="inlineStr">
         <is>
           <t>2.34</t>
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-112.32</t>
+          <t>-112.13</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>7312.167381974248</t>
+          <t>7302.072857142857</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>516.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>472.6</v>
+        <v>534.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>402.3</t>
+          <t>437.4</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>481.38</v>
+        <v>468.04</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>97</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-10.83001914489146</t>
+          <t>-12.02299824989772</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-28.30195518775838</t>
+          <t>-18.58438332743214</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>516.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>30.78</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>90.83</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>515</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6893,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,63 +7039,63 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>60.36</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.83</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>13.77</v>
+        <v>13.74</v>
       </c>
       <c r="AN16" t="n">
-        <v>14.31</v>
+        <v>14.28</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-112.36</t>
+          <t>-112.32</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>7312.167381974248</t>
+          <t>7302.072857142857</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>507.6</v>
+        <v>472.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>424.0</t>
+          <t>402.3</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>517.4400000000001</v>
+        <v>481.38</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-7.653303500733839</t>
+          <t>-10.83001914489146</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>3.719440554195444</t>
+          <t>-28.30195518775838</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>30.78</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>90.83</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>515</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7281,22 +7281,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-22.83</t>
+          <t>-22.25</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,49 +7469,49 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>13.8</v>
+        <v>13.77</v>
       </c>
       <c r="AN17" t="n">
-        <v>14.35</v>
+        <v>14.31</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7520,12 +7520,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-112.26</t>
+          <t>-112.36</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>7312.167381974248</t>
+          <t>7302.072857142857</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>459.6</v>
+        <v>507.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>420.3</t>
+          <t>424.0</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>554.86</v>
+        <v>517.4400000000001</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-9.721075147084617</t>
+          <t>-7.653303500733839</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-6.061402691377396</t>
+          <t>3.719440554195444</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-4.30</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>30.78</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>90.83</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>515</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7711,27 +7711,27 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-9.92</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,49 +7899,49 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.83</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>13.83</v>
+        <v>13.8</v>
       </c>
       <c r="AN18" t="n">
-        <v>14.41</v>
+        <v>14.35</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -7950,17 +7950,17 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-12.91</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-111.98</t>
+          <t>-112.26</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>7312.167381974248</t>
+          <t>7302.072857142857</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>1213.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>527.6</v>
+        <v>459.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>585.7</t>
+          <t>420.3</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>567.6799999999999</v>
+        <v>554.86</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-58</t>
+          <t>39</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-10.38647013903138</t>
+          <t>-9.721075147084617</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>21.00387133963898</t>
+          <t>-6.061402691377396</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>1213.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>30.78</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>90.83</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>515</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-31.65</t>
+          <t>-9.92</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,49 +8329,49 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>13.86</v>
+        <v>13.83</v>
       </c>
       <c r="AN19" t="n">
-        <v>14.48</v>
+        <v>14.41</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-16.60</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-111.60</t>
+          <t>-111.98</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>7312.167381974248</t>
+          <t>7302.072857142857</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>1213.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>340.2</v>
+        <v>527.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>497.7</t>
+          <t>585.7</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>555.26</v>
+        <v>567.6799999999999</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-157</t>
+          <t>-58</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-16.09380495333509</t>
+          <t>-10.38647013903138</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-46.08158973532466</t>
+          <t>21.00387133963898</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>1213.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>30.78</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>90.83</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>515</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8571,22 +8571,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-48.73</t>
+          <t>-31.65</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-24.86</t>
+          <t>-22.83</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,49 +8759,49 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>13.43</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>13.9</v>
+        <v>13.86</v>
       </c>
       <c r="AN20" t="n">
-        <v>14.55</v>
+        <v>14.48</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8810,17 +8810,17 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-19.79</t>
+          <t>-16.60</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-111.11</t>
+          <t>-111.60</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>7312.167381974248</t>
+          <t>7302.072857142857</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>332</v>
+        <v>340.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>647.5</t>
+          <t>497.7</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>577.0599999999999</v>
+        <v>555.26</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-315</t>
+          <t>-157</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-10.6414804475188</t>
+          <t>-16.09380495333509</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-32.37933449472541</t>
+          <t>-46.08158973532466</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-4.30</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>30.78</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>90.83</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>515</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9001,27 +9001,27 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
+          <t>12.9</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
           <t>13.4</t>
         </is>
       </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>13.55</t>
-        </is>
-      </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-45.61</t>
+          <t>-48.73</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-23.12</t>
+          <t>-24.86</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,34 +9204,34 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-3.20</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>13.62</t>
+          <t>13.43</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>13.95</v>
+        <v>13.9</v>
       </c>
       <c r="AN21" t="n">
-        <v>14.64</v>
+        <v>14.55</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9240,17 +9240,17 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-19.79</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-110.56</t>
+          <t>-111.11</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>7312.167381974248</t>
+          <t>7302.072857142857</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>374.0</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>340.4</v>
+        <v>332</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>625.9</t>
+          <t>647.5</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>605.1799999999999</v>
+        <v>577.0599999999999</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-285</t>
+          <t>-315</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-6.68914334802669</t>
+          <t>-10.6414804475188</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-18.71970791905761</t>
+          <t>-32.37933449472541</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>374.0</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,17 +9371,17 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>30.78</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>90.83</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>515</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9431,27 +9431,27 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>13.15</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9473,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-36.19</t>
+          <t>-45.61</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-21.39</t>
+          <t>-23.12</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,34 +9634,34 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>13.62</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>13.98</v>
+        <v>13.95</v>
       </c>
       <c r="AN22" t="n">
-        <v>14.71</v>
+        <v>14.64</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9670,17 +9670,17 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-110.37</t>
+          <t>-110.56</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>7312.167381974248</t>
+          <t>7302.072857142857</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>374.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>381</v>
+        <v>340.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>597.1</t>
+          <t>625.9</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>630.02</v>
+        <v>605.1799999999999</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-216</t>
+          <t>-285</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-4.501767971475612</t>
+          <t>-6.68914334802669</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-9.46596609956589</t>
+          <t>-18.71970791905761</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>374.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>30.78</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>90.83</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>515</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9861,27 +9861,27 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
+          <t>13.6</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
           <t>13.65</t>
         </is>
       </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>13.95</t>
-        </is>
-      </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>13.15</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>-36.19</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,58 +10059,58 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>14</v>
+        <v>13.98</v>
       </c>
       <c r="AN23" t="n">
-        <v>14.79</v>
+        <v>14.71</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-110.48</t>
+          <t>-110.37</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>7312.167381974248</t>
+          <t>7302.072857142857</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>276.0</t>
+          <t>573.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>643.8</v>
+        <v>381</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>572.3</t>
+          <t>597.1</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>643.84</v>
+        <v>630.02</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>-216</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-3.599186493641016</t>
+          <t>-4.501767971475612</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-17.22969328245046</t>
+          <t>-9.46596609956589</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>276.0</t>
+          <t>573.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>30.78</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>90.83</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>515</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10291,17 +10291,17 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.95</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
@@ -10343,12 +10343,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>680.189</t>
+          <t>1072.806</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-8.36</t>
+          <t>-6.74</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -10453,17 +10453,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -10474,73 +10474,73 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>34.57</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-7.85</t>
+          <t>-8.12</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>34.20999999999999</t>
         </is>
       </c>
       <c r="AM24" t="n">
-        <v>35.52</v>
+        <v>35.29</v>
       </c>
       <c r="AN24" t="n">
-        <v>38.55</v>
+        <v>38.41</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>37.82</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>-131.97</t>
+          <t>-131.38</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -10560,43 +10560,43 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>232075095.6437768</t>
+          <t>231823087.8107143</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>23145831.0</t>
+          <t>37113075.0</t>
         </is>
       </c>
       <c r="AX24" t="n">
-        <v>28055340.4</v>
+        <v>28180230.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>32565131.1</t>
+          <t>32709006.3</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>214383272.46</v>
+        <v>203000139.16</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>-4509790</t>
+          <t>-4528775</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>-20081972.26747796</t>
+          <t>-19086701.69794936</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-15669143.09806082</t>
+          <t>-13612713.56554211</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>23145831.0</t>
+          <t>37113075.0</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -10661,17 +10661,17 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS24" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BT24" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="BY24" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -10726,22 +10726,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>33.85</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -10773,12 +10773,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>908.595</t>
+          <t>680.189</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -10798,17 +10798,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-13.85</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -10873,7 +10873,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-9.03</t>
+          <t>-8.36</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -10883,17 +10883,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -10904,75 +10904,75 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-7.85</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>35.67</v>
+        <v>35.52</v>
       </c>
       <c r="AN25" t="n">
-        <v>38.71</v>
+        <v>38.55</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>37.74</t>
+          <t>37.78</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
           <t>-1.17</t>
         </is>
       </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>-1.17</t>
-        </is>
-      </c>
       <c r="AS25" t="inlineStr">
         <is>
           <t>3.65</t>
@@ -10980,7 +10980,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>-132.13</t>
+          <t>-131.97</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -10990,43 +10990,43 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>232075095.6437768</t>
+          <t>231823087.8107143</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>30779178.0</t>
+          <t>23145831.0</t>
         </is>
       </c>
       <c r="AX25" t="n">
-        <v>30495285.4</v>
+        <v>28055340.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>35145840.3</t>
+          <t>32565131.1</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>228943265.06</v>
+        <v>214383272.46</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>-4650554</t>
+          <t>-4509790</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>-20884304.84373562</t>
+          <t>-20081972.26747796</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-16550796.89101397</t>
+          <t>-15669143.09806082</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>30779178.0</t>
+          <t>23145831.0</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -11046,7 +11046,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="BS25" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BT25" t="inlineStr">
@@ -11131,12 +11131,12 @@
       </c>
       <c r="BY25" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
@@ -11166,12 +11166,12 @@
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -11203,12 +11203,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>797.737</t>
+          <t>908.595</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -11228,17 +11228,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-24.16</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-8.36</t>
+          <t>-9.03</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -11313,17 +11313,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -11334,63 +11334,63 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>60.49</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-7.74</t>
+          <t>-7.84</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>34.43</t>
         </is>
       </c>
       <c r="AM26" t="n">
-        <v>35.81</v>
+        <v>35.67</v>
       </c>
       <c r="AN26" t="n">
-        <v>38.81</v>
+        <v>38.71</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.74</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>-132.14</t>
+          <t>-132.13</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -11420,43 +11420,43 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>232075095.6437768</t>
+          <t>231823087.8107143</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>27224823.0</t>
+          <t>30779178.0</t>
         </is>
       </c>
       <c r="AX26" t="n">
-        <v>30219756.2</v>
+        <v>30495285.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>39847131.9</t>
+          <t>35145840.3</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>236001176.02</v>
+        <v>228943265.06</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>-9627375</t>
+          <t>-4650554</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>-21672215.3805941</t>
+          <t>-20884304.84373562</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-18037061.02769653</t>
+          <t>-16550796.89101397</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>27224823.0</t>
+          <t>30779178.0</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="BS26" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="BT26" t="inlineStr">
@@ -11561,12 +11561,12 @@
       </c>
       <c r="BY26" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -11586,22 +11586,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -11633,12 +11633,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>652.267</t>
+          <t>797.737</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11658,17 +11658,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-30.44</t>
+          <t>-24.16</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-6.47</t>
+          <t>-8.36</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -11743,17 +11743,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -11764,63 +11764,63 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>60.49</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-7.74</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>34.47</t>
+          <t>34.54</t>
         </is>
       </c>
       <c r="AM27" t="n">
-        <v>35.98</v>
+        <v>35.81</v>
       </c>
       <c r="AN27" t="n">
-        <v>38.91</v>
+        <v>38.81</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>37.67</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>-132.19</t>
+          <t>-132.14</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -11850,43 +11850,43 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>232075095.6437768</t>
+          <t>231823087.8107143</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>22638246.0</t>
+          <t>27224823.0</t>
         </is>
       </c>
       <c r="AX27" t="n">
-        <v>32529604.8</v>
+        <v>30219756.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>46763411.2</t>
+          <t>39847131.9</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>241442940.72</v>
+        <v>236001176.02</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>-14233806</t>
+          <t>-9627375</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>-22333152.53566639</t>
+          <t>-21672215.3805941</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-19135291.00768245</t>
+          <t>-18037061.02769653</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>22638246.0</t>
+          <t>27224823.0</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="BS27" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BT27" t="inlineStr">
@@ -11991,12 +11991,12 @@
       </c>
       <c r="BY27" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -12021,17 +12021,17 @@
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -12053,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1052.554</t>
+          <t>652.267</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -12088,17 +12088,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-26.38</t>
+          <t>-30.44</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -12173,17 +12173,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -12194,12 +12194,12 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -12209,53 +12209,53 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>48.28</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>34.39</t>
+          <t>34.47</t>
         </is>
       </c>
       <c r="AM28" t="n">
-        <v>36.08</v>
+        <v>35.98</v>
       </c>
       <c r="AN28" t="n">
-        <v>38.92</v>
+        <v>38.91</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>37.67</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>-132.25</t>
+          <t>-132.19</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -12280,43 +12280,43 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>232075095.6437768</t>
+          <t>231823087.8107143</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>36488624.0</t>
+          <t>22638246.0</t>
         </is>
       </c>
       <c r="AX28" t="n">
-        <v>37237782</v>
+        <v>32529604.8</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>50581063.8</t>
+          <t>46763411.2</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>242256442.44</v>
+        <v>241442940.72</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>-13343281</t>
+          <t>-14233806</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>-22914581.90439074</t>
+          <t>-22333152.53566639</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-19529368.76453082</t>
+          <t>-19135291.00768245</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>36488624.0</t>
+          <t>22638246.0</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="BY28" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -12446,17 +12446,17 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
@@ -12493,12 +12493,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1012.048</t>
+          <t>1052.554</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -12518,17 +12518,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-30.50</t>
+          <t>-26.38</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -12603,17 +12603,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -12624,73 +12624,73 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>48.21</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>48.28</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>34.41</t>
+          <t>34.39</t>
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>36.18</v>
+        <v>36.08</v>
       </c>
       <c r="AN29" t="n">
-        <v>38.94</v>
+        <v>38.92</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>37.63</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>-131.94</t>
+          <t>-132.25</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -12710,43 +12710,43 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>232075095.6437768</t>
+          <t>231823087.8107143</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>35345556.0</t>
+          <t>36488624.0</t>
         </is>
       </c>
       <c r="AX29" t="n">
-        <v>37074921.8</v>
+        <v>37237782</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>53345322.1</t>
+          <t>50581063.8</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>245778298.12</v>
+        <v>242256442.44</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>-16270400</t>
+          <t>-13343281</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>-23530075.2025471</t>
+          <t>-22914581.90439074</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>-20878828.60415238</t>
+          <t>-19529368.76453082</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>35345556.0</t>
+          <t>36488624.0</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS29" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="BT29" t="inlineStr">
@@ -12851,12 +12851,12 @@
       </c>
       <c r="BY29" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ29" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="CA29" t="inlineStr">
@@ -12876,22 +12876,22 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>857.193</t>
+          <t>1012.048</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -12938,7 +12938,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -12948,17 +12948,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-31.65</t>
+          <t>-30.50</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -13023,7 +13023,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-7.55</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -13033,17 +13033,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -13054,73 +13054,73 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>48.21</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>10.92</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>34.16</t>
+          <t>34.41</t>
         </is>
       </c>
       <c r="AM30" t="n">
-        <v>36.33</v>
+        <v>36.18</v>
       </c>
       <c r="AN30" t="n">
-        <v>39</v>
+        <v>38.94</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>37.52</t>
+          <t>37.58</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>-131.18</t>
+          <t>-131.94</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -13140,43 +13140,43 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>232075095.6437768</t>
+          <t>231823087.8107143</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>29401532.0</t>
+          <t>35345556.0</t>
         </is>
       </c>
       <c r="AX30" t="n">
-        <v>39796395.2</v>
+        <v>37074921.8</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>58228190.4</t>
+          <t>53345322.1</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>247556548.26</v>
+        <v>245778298.12</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>-18431795</t>
+          <t>-16270400</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>-24012120.03861886</t>
+          <t>-23530075.2025471</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>-21938484.35346347</t>
+          <t>-20878828.60415238</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>29401532.0</t>
+          <t>35345556.0</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
@@ -13196,7 +13196,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -13241,17 +13241,17 @@
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS30" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BT30" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="BY30" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ30" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="CA30" t="inlineStr">
@@ -13306,22 +13306,22 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1145.3</t>
+          <t>857.193</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>33.65</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -13378,17 +13378,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-25.49</t>
+          <t>-31.65</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-9.30</t>
+          <t>-7.55</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -13463,17 +13463,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -13484,73 +13484,73 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>10.92</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>-6.49</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>34.11999999999999</t>
+          <t>34.16</t>
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>36.49</v>
+        <v>36.33</v>
       </c>
       <c r="AN31" t="n">
-        <v>39.06</v>
+        <v>39</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>37.47</t>
+          <t>37.52</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>-26.04</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>-129.70</t>
+          <t>-131.18</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -13570,43 +13570,43 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>232075095.6437768</t>
+          <t>231823087.8107143</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>38774066.0</t>
+          <t>29401532.0</t>
         </is>
       </c>
       <c r="AX31" t="n">
-        <v>49474507.6</v>
+        <v>39796395.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>66401056.1</t>
+          <t>58228190.4</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>249662887.18</v>
+        <v>247556548.26</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>-16926548</t>
+          <t>-18431795</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>-24389144.70864711</t>
+          <t>-24012120.03861886</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>-22031901.26842704</t>
+          <t>-21938484.35346347</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>38774066.0</t>
+          <t>29401532.0</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -13671,7 +13671,7 @@
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="BS31" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="BT31" t="inlineStr">
@@ -13711,12 +13711,12 @@
       </c>
       <c r="BY31" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ31" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="CA31" t="inlineStr">
@@ -13736,22 +13736,22 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.55</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>33.65</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -13783,12 +13783,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1345.621</t>
+          <t>1145.3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -13798,7 +13798,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>33.65</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13808,17 +13808,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-27.63</t>
+          <t>-25.49</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-7.55</t>
+          <t>-9.30</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -13893,17 +13893,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -13914,17 +13914,17 @@
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>13.92</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
@@ -13934,7 +13934,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
@@ -13944,43 +13944,43 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>-6.2</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>34.33</t>
+          <t>34.11999999999999</t>
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>36.71</v>
+        <v>36.49</v>
       </c>
       <c r="AN32" t="n">
-        <v>39.14</v>
+        <v>39.06</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>37.43</t>
+          <t>37.47</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>-27.70</t>
+          <t>-26.04</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>-127.76</t>
+          <t>-129.70</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -14000,43 +14000,43 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>232075095.6437768</t>
+          <t>231823087.8107143</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>46179132.0</t>
+          <t>38774066.0</t>
         </is>
       </c>
       <c r="AX32" t="n">
-        <v>60997217.6</v>
+        <v>49474507.6</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>84286762.5</t>
+          <t>66401056.1</t>
         </is>
       </c>
       <c r="AZ32" t="n">
-        <v>254822433.06</v>
+        <v>249662887.18</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>-23289544</t>
+          <t>-16926548</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>-24817734.42505076</t>
+          <t>-24389144.70864711</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>-22382700.45878832</t>
+          <t>-22031901.26842704</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>46179132.0</t>
+          <t>38774066.0</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
@@ -14101,7 +14101,7 @@
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="BS32" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="BT32" t="inlineStr">
@@ -14141,12 +14141,12 @@
       </c>
       <c r="BY32" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ32" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="CA32" t="inlineStr">
@@ -14166,22 +14166,22 @@
       </c>
       <c r="CD32" t="inlineStr">
         <is>
-          <t>34.05</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="CF32" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="CG32" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>33.65</t>
         </is>
       </c>
       <c r="CH32" t="inlineStr">
@@ -14213,12 +14213,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1029.736</t>
+          <t>1345.621</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -14238,17 +14238,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-32.40</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-6.20</t>
+          <t>-7.55</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -14323,17 +14323,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -14344,73 +14344,73 @@
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>13.92</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-6.49</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-6.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>34.33</t>
         </is>
       </c>
       <c r="AM33" t="n">
-        <v>36.88</v>
+        <v>36.71</v>
       </c>
       <c r="AN33" t="n">
-        <v>39.24</v>
+        <v>39.14</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>37.43</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>-32.46</t>
+          <t>-27.70</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -14420,7 +14420,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>-125.84</t>
+          <t>-127.76</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -14430,43 +14430,43 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>232075095.6437768</t>
+          <t>231823087.8107143</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>35674323.0</t>
+          <t>46179132.0</t>
         </is>
       </c>
       <c r="AX33" t="n">
-        <v>63924345.6</v>
+        <v>60997217.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>94556424.4</t>
+          <t>84286762.5</t>
         </is>
       </c>
       <c r="AZ33" t="n">
-        <v>256700200.08</v>
+        <v>254822433.06</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>-30632078</t>
+          <t>-23289544</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>-25260467.87346211</t>
+          <t>-24817734.42505076</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>-22877859.92863344</t>
+          <t>-22382700.45878832</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>35674323.0</t>
+          <t>46179132.0</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
@@ -14486,7 +14486,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR33" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
@@ -14571,12 +14571,12 @@
       </c>
       <c r="BY33" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ33" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="CA33" t="inlineStr">
@@ -14596,22 +14596,22 @@
       </c>
       <c r="CD33" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.05</t>
         </is>
       </c>
       <c r="CE33" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>34.85</t>
         </is>
       </c>
       <c r="CF33" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="CG33" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CH33" t="inlineStr">
@@ -14643,12 +14643,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1450.779</t>
+          <t>1029.736</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -14668,17 +14668,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-37.05</t>
+          <t>-32.40</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-9.03</t>
+          <t>-6.20</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -14753,17 +14753,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -14774,73 +14774,73 @@
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>35.22000000000001</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>37.06</v>
+        <v>36.88</v>
       </c>
       <c r="AN34" t="n">
-        <v>39.33</v>
+        <v>39.24</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>37.33</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>-41.33</t>
+          <t>-32.46</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>-123.74</t>
+          <t>-125.84</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -14860,43 +14860,43 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>232075095.6437768</t>
+          <t>231823087.8107143</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>48952923.0</t>
+          <t>35674323.0</t>
         </is>
       </c>
       <c r="AX34" t="n">
-        <v>69615722.40000001</v>
+        <v>63924345.6</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>110580229.2</t>
+          <t>94556424.4</t>
         </is>
       </c>
       <c r="AZ34" t="n">
-        <v>258176781.58</v>
+        <v>256700200.08</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>-40964506</t>
+          <t>-30632078</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>-25693669.31797642</t>
+          <t>-25260467.87346211</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>-21642648.9238181</t>
+          <t>-22877859.92863344</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>48952923.0</t>
+          <t>35674323.0</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
@@ -14961,7 +14961,7 @@
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
@@ -14971,7 +14971,7 @@
       </c>
       <c r="BS34" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="BT34" t="inlineStr">
@@ -15001,12 +15001,12 @@
       </c>
       <c r="BY34" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ34" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="CA34" t="inlineStr">
@@ -15026,22 +15026,22 @@
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CE34" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="CF34" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CG34" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CH34" t="inlineStr">

--- a/Result/checksun_type/玻璃基板.xlsx
+++ b/Result/checksun_type/玻璃基板.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>96.636</t>
+          <t>31.793</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>22.72</t>
+          <t>23.03</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>-7.50</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>74.19</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>88.37</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>1.71</v>
+        <v>-0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.29</v>
+        <v>1.32</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>25.64</v>
+        <v>25.6</v>
       </c>
       <c r="AN2" t="n">
-        <v>26.74</v>
+        <v>26.71</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>26.04</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>34.57</t>
+          <t>38.28</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.32</v>
+        <v>-0.28</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.49</v>
+        <v>-0.45</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-116.18</t>
+          <t>-114.77</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>60565884.53966005</t>
+          <t>60481961.47807638</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2494335.0</t>
+          <t>821520.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>4478414</v>
+        <v>4356438.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3649229.2</t>
+          <t>3541027.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>9357524.42</v>
+        <v>9017458.68</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>829184</t>
+          <t>815411</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1044135.43529133</t>
+          <t>-993613.0125357707</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-521574.4503118787</t>
+          <t>-715739.6873801965</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2494335.0</t>
+          <t>821520.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1293,7 +1293,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>6405</t>
@@ -1301,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>195.468</t>
+          <t>96.636</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1316,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1326,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>22.72</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1401,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1411,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.20</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1432,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>3.02</v>
+        <v>1.71</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.67</v>
+        <v>0.29</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>25.7</v>
+        <v>25.64</v>
       </c>
       <c r="AN3" t="n">
-        <v>26.79</v>
+        <v>26.74</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>26.04</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>25.17</t>
+          <t>34.57</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.4</v>
+        <v>-0.32</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.53</v>
+        <v>-0.49</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1500,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-117.58</t>
+          <t>-116.18</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1510,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>60565884.53966005</t>
+          <t>60481961.47807638</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>5207526.0</t>
+          <t>2494335.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>4629628.2</v>
+        <v>4478414</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3696072.6</t>
+          <t>3649229.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>10084690.88</v>
+        <v>9357524.42</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>933555</t>
+          <t>829184</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1139146.523469412</t>
+          <t>-1044135.43529133</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-404798.0598460007</t>
+          <t>-521574.4503118787</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>5207526.0</t>
+          <t>2494335.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1566,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1651,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1676,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
+          <t>25.4</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>26.15</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>26.3</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1711,7 +1715,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>6405</t>
@@ -1719,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>405.481</t>
+          <t>195.468</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1744,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1829,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>7.20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1850,12 +1858,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1865,51 +1873,51 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>4.12</v>
+        <v>3.02</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1.9</v>
+        <v>-0.67</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>25.53</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>25.75</v>
+        <v>25.7</v>
       </c>
       <c r="AN4" t="n">
         <v>26.79</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>25.99</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>25.17</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.51</v>
+        <v>-0.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.53</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1918,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-118.68</t>
+          <t>-117.58</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1928,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>60565884.53966005</t>
+          <t>60481961.47807638</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>10672887.0</t>
+          <t>5207526.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3809271.8</v>
+        <v>4629628.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3609459.7</t>
+          <t>3696072.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>10245696.52</v>
+        <v>10084690.88</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>199812</t>
+          <t>933555</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1272664.425946395</t>
+          <t>-1139146.523469412</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-514216.6070431024</t>
+          <t>-404798.0598460007</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>10672887.0</t>
+          <t>5207526.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2029,12 +2037,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2044,7 +2052,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2069,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2094,17 +2102,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>27.05</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2131,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2141,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>103.242</t>
+          <t>405.481</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2156,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2166,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-24.98</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2241,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.54</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2251,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2272,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.28</v>
+        <v>4.12</v>
       </c>
       <c r="AI5" t="n">
-        <v>-3.11</v>
+        <v>-1.9</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>25.78</v>
+        <v>25.75</v>
       </c>
       <c r="AN5" t="n">
-        <v>26.78</v>
+        <v>26.79</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>25.96</t>
+          <t>25.99</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-10.00</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.64</v>
+        <v>-0.51</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.58</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2340,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-119.17</t>
+          <t>-118.68</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2350,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>60565884.53966005</t>
+          <t>60481961.47807638</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2585925.0</t>
+          <t>10672887.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>2334426.2</v>
+        <v>3809271.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3111599.5</t>
+          <t>3609459.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>10171307.16</v>
+        <v>10245696.52</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-777173</t>
+          <t>199812</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1410564.029383358</t>
+          <t>-1272664.425946395</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1237738.331358852</t>
+          <t>-514216.6070431024</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2585925.0</t>
+          <t>10672887.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2406,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2451,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2491,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2516,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>27.05</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2563,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>57.864</t>
+          <t>103.242</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2578,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2588,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-24.98</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2663,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-11.61</t>
+          <t>-10.54</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2673,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2694,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>50.45</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-0.6</v>
+        <v>0.28</v>
       </c>
       <c r="AI6" t="n">
-        <v>-3.79</v>
+        <v>-3.11</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>25.88</v>
+        <v>25.78</v>
       </c>
       <c r="AN6" t="n">
         <v>26.78</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>25.96</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-18.27</t>
+          <t>-10.00</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.67</v>
+        <v>-0.64</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.58</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2762,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-118.69</t>
+          <t>-119.17</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2772,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>60565884.53966005</t>
+          <t>60481961.47807638</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1431397.0</t>
+          <t>2585925.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>2725616.2</v>
+        <v>2334426.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3344499.9</t>
+          <t>3111599.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>10170725.72</v>
+        <v>10171307.16</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-618883</t>
+          <t>-777173</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1441986.883569631</t>
+          <t>-1410564.029383358</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1360675.639975678</t>
+          <t>-1237738.331358852</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1431397.0</t>
+          <t>2585925.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2828,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2883,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2913,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2938,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2985,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>129.907</t>
+          <t>57.864</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3000,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3010,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3085,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-9.82</t>
+          <t>-11.61</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3095,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3116,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>50.45</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>1.73</v>
+        <v>-0.6</v>
       </c>
       <c r="AI7" t="n">
-        <v>-4.69</v>
+        <v>-3.79</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>26.04</v>
+        <v>25.88</v>
       </c>
       <c r="AN7" t="n">
-        <v>26.79</v>
+        <v>26.78</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>25.92</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-23.75</t>
+          <t>-18.27</t>
         </is>
       </c>
       <c r="AQ7" t="n">
         <v>-0.67</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.54</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3184,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-117.83</t>
+          <t>-118.69</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3194,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>60565884.53966005</t>
+          <t>60481961.47807638</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3250406.0</t>
+          <t>1431397.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>2820044.4</v>
+        <v>2725616.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3938171.4</t>
+          <t>3344499.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>10185422.26</v>
+        <v>10170725.72</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1118127</t>
+          <t>-618883</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1456770.746041259</t>
+          <t>-1441986.883569631</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1364005.379429155</t>
+          <t>-1360675.639975678</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>3250406.0</t>
+          <t>1431397.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3250,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3305,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3335,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3360,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3407,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>44.221</t>
+          <t>129.907</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3422,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3432,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-32.35</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3507,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-10.89</t>
+          <t>-9.82</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3517,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3538,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>1.09</v>
+        <v>1.73</v>
       </c>
       <c r="AI8" t="n">
-        <v>-5.71</v>
+        <v>-4.69</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>26.18</v>
+        <v>26.04</v>
       </c>
       <c r="AN8" t="n">
-        <v>26.78</v>
+        <v>26.79</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-39.44</t>
+          <t>-23.75</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.71</v>
+        <v>-0.67</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.51</v>
+        <v>-0.54</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3606,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-116.78</t>
+          <t>-117.83</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3616,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>60565884.53966005</t>
+          <t>60481961.47807638</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1105744.0</t>
+          <t>3250406.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>2762517</v>
+        <v>2820044.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4083544.5</t>
+          <t>3938171.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>10163096.92</v>
+        <v>10185422.26</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1321027</t>
+          <t>-1118127</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1473637.176334369</t>
+          <t>-1456770.746041259</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1514941.493668794</t>
+          <t>-1364005.379429155</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1105744.0</t>
+          <t>3250406.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3672,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3727,12 +3735,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3757,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3782,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3829,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>132.605</t>
+          <t>44.221</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3844,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3854,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-21.31</t>
+          <t>-32.35</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3929,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-11.07</t>
+          <t>-10.89</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3939,12 +3947,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -3960,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.48</v>
+        <v>1.09</v>
       </c>
       <c r="AI9" t="n">
-        <v>-6.05</v>
+        <v>-5.71</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>24.68</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>26.38</v>
+        <v>26.18</v>
       </c>
       <c r="AN9" t="n">
         <v>26.78</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-56.92</t>
+          <t>-39.44</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.72</v>
+        <v>-0.71</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.46</v>
+        <v>-0.51</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4028,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-115.12</t>
+          <t>-116.78</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4038,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>60565884.53966005</t>
+          <t>60481961.47807638</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3298659.0</t>
+          <t>1105744.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>3409647.6</v>
+        <v>2762517</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4333083.4</t>
+          <t>4083544.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>10178782.26</v>
+        <v>10163096.92</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-923435</t>
+          <t>-1321027</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1466127.300455383</t>
+          <t>-1473637.176334369</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1446674.246380107</t>
+          <t>-1514941.493668794</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>3298659.0</t>
+          <t>1105744.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4094,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4139,12 +4147,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4154,7 +4162,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4179,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4204,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4251,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>182.531</t>
+          <t>132.605</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4266,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4276,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-11.85</t>
+          <t>-21.31</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4351,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-11.96</t>
+          <t>-11.07</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4361,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4382,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>-0.08</v>
+        <v>0.48</v>
       </c>
       <c r="AI10" t="n">
-        <v>-7.33</v>
+        <v>-6.05</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>24.78</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>26.62</v>
+        <v>26.38</v>
       </c>
       <c r="AN10" t="n">
-        <v>26.79</v>
+        <v>26.78</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-82.30</t>
+          <t>-56.92</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.71</v>
+        <v>-0.72</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.39</v>
+        <v>-0.46</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4450,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-112.97</t>
+          <t>-115.12</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4460,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>60565884.53966005</t>
+          <t>60481961.47807638</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>4541875.0</t>
+          <t>3298659.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>3888772.8</v>
+        <v>3409647.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4411562.6</t>
+          <t>4333083.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>10182869.32</v>
+        <v>10178782.26</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-522789</t>
+          <t>-923435</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1469664.21937816</t>
+          <t>-1466127.300455383</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1532437.84859698</t>
+          <t>-1446674.246380107</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>4541875.0</t>
+          <t>3298659.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4516,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4576,7 +4584,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4601,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4626,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4663,7 +4671,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4673,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>77.947</t>
+          <t>182.531</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4688,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4698,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-25.48</t>
+          <t>-11.85</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4773,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-13.04</t>
+          <t>-11.96</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4783,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4804,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-2.01</v>
+        <v>-0.08</v>
       </c>
       <c r="AI11" t="n">
-        <v>-7.5</v>
+        <v>-7.33</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.67</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>26.86</v>
+        <v>26.62</v>
       </c>
       <c r="AN11" t="n">
         <v>26.79</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>25.87</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-116.96</t>
+          <t>-82.30</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.67</v>
+        <v>-0.71</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.31</v>
+        <v>-0.39</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4872,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-110.30</t>
+          <t>-112.97</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4882,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>60565884.53966005</t>
+          <t>60481961.47807638</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1903538.0</t>
+          <t>4541875.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>3963383.6</v>
+        <v>3888772.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5318222.8</t>
+          <t>4411562.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>10129541.2</v>
+        <v>10182869.32</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1354839</t>
+          <t>-522789</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1458250.832247465</t>
+          <t>-1469664.21937816</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1733429.071456906</t>
+          <t>-1532437.84859698</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1903538.0</t>
+          <t>4541875.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4938,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4983,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -4993,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5023,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5048,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5095,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>121.223</t>
+          <t>77.947</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5110,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5120,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-25.48</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5195,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-12.32</t>
+          <t>-13.04</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5205,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5226,17 +5234,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5245,47 +5253,47 @@
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-2.39</v>
+        <v>-2.01</v>
       </c>
       <c r="AI12" t="n">
-        <v>-7.61</v>
+        <v>-7.5</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>27.22</v>
+        <v>26.86</v>
       </c>
       <c r="AN12" t="n">
-        <v>26.8</v>
+        <v>26.79</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>25.87</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-165.59</t>
+          <t>-116.96</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.58</v>
+        <v>-0.67</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.22</v>
+        <v>-0.31</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5294,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-107.29</t>
+          <t>-110.30</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5304,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>60565884.53966005</t>
+          <t>60481961.47807638</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2962769.0</t>
+          <t>1903538.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>5056298.4</v>
+        <v>3963383.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5511802.7</t>
+          <t>5318222.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>10116244</v>
+        <v>10129541.2</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-455504</t>
+          <t>-1354839</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1408218.425118476</t>
+          <t>-1458250.832247465</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1675972.244419054</t>
+          <t>-1733429.071456906</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>2962769.0</t>
+          <t>1903538.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5360,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5405,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5420,7 +5428,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5445,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5470,12 +5478,12 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5485,7 +5493,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5505,7 +5513,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>6246</t>
@@ -5513,12 +5525,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5528,7 +5540,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5543,12 +5555,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-30.96</t>
+          <t>-21.02</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5558,7 +5570,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5613,7 +5625,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-21.10</t>
+          <t>-21.68</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5623,17 +5635,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5644,50 +5656,50 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>76.86</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>0.29</v>
+        <v>-0.59</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0.57</v>
+        <v>-0.33</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-6.79</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>13.61</t>
+          <t>13.63</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>13.69</v>
+        <v>13.68</v>
       </c>
       <c r="AN13" t="n">
-        <v>14.14</v>
+        <v>14.1</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5696,14 +5708,14 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>24.93</t>
         </is>
       </c>
       <c r="AQ13" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="AR13" t="n">
-        <v>-0.24</v>
+        <v>-0.23</v>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
@@ -5712,7 +5724,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-110.34</t>
+          <t>-109.73</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5722,43 +5734,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>7292.129101283879</t>
+          <t>7282.384615384615</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>221.0</t>
+          <t>301.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>267.6</v>
+        <v>308.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>387.6</t>
+          <t>390.5</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>448.82</v>
+        <v>446.72</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-120</t>
+          <t>-82</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-22.68903223248835</t>
+          <t>-26.11623977994269</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-47.66941556493481</t>
+          <t>-44.96588129094152</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>221.0</t>
+          <t>301.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5778,7 +5790,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5823,7 +5835,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5833,7 +5845,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5848,7 +5860,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>30.33</t>
+          <t>30.11</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5863,12 +5875,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>513</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5883,7 +5895,7 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
@@ -5898,12 +5910,12 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.15</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -5923,7 +5935,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>6246</t>
@@ -5931,12 +5947,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5946,7 +5962,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5956,17 +5972,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-14.07</t>
+          <t>-30.96</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -5976,7 +5992,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6031,7 +6047,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-21.39</t>
+          <t>-21.10</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6041,17 +6057,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6062,66 +6078,66 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>84.64</t>
+          <t>76.86</t>
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0.91</v>
+        <v>-0.57</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>13.57</t>
+          <t>13.61</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>13.7</v>
+        <v>13.69</v>
       </c>
       <c r="AN14" t="n">
-        <v>14.17</v>
+        <v>14.14</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>15.13</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AQ14" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="AR14" t="n">
-        <v>-0.26</v>
+        <v>-0.24</v>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
@@ -6130,7 +6146,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-110.99</t>
+          <t>-110.34</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6140,43 +6156,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>7292.129101283879</t>
+          <t>7282.384615384615</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>221.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>346.2</v>
+        <v>267.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>402.9</t>
+          <t>387.6</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>457.34</v>
+        <v>448.82</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-56</t>
+          <t>-120</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-18.14714435386173</t>
+          <t>-22.68903223248835</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-41.25769968617749</t>
+          <t>-47.66941556493481</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>221.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6196,7 +6212,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6241,7 +6257,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6266,7 +6282,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>30.33</t>
+          <t>30.11</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6281,12 +6297,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>513</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6301,27 +6317,27 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6341,7 +6357,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>6246</t>
@@ -6349,12 +6369,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6364,7 +6384,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6374,17 +6394,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-18.88</t>
+          <t>-14.07</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6394,7 +6414,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6449,7 +6469,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-19.94</t>
+          <t>-21.39</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6459,17 +6479,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6480,50 +6500,50 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>86.11</t>
+          <t>84.64</t>
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>2.44</v>
+        <v>0.22</v>
       </c>
       <c r="AI15" t="n">
-        <v>-1.35</v>
+        <v>-0.91</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-6.16</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>13.52</t>
+          <t>13.57</t>
         </is>
       </c>
       <c r="AM15" t="n">
         <v>13.7</v>
       </c>
       <c r="AN15" t="n">
-        <v>14.21</v>
+        <v>14.17</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6532,14 +6552,14 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>18.80</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AQ15" t="n">
-        <v>-0.22</v>
+        <v>-0.2</v>
       </c>
       <c r="AR15" t="n">
-        <v>-0.27</v>
+        <v>-0.26</v>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
@@ -6548,7 +6568,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-111.58</t>
+          <t>-110.99</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6558,43 +6578,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>7292.129101283879</t>
+          <t>7282.384615384615</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>340.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>360</v>
+        <v>346.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>443.8</t>
+          <t>402.9</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>464.82</v>
+        <v>457.34</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-83</t>
+          <t>-56</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-13.94522520253159</t>
+          <t>-18.14714435386173</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-24.51747344201789</t>
+          <t>-41.25769968617749</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>340.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6614,7 +6634,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6659,7 +6679,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6669,7 +6689,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6684,7 +6704,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>30.33</t>
+          <t>30.11</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6699,12 +6719,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>513</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6719,27 +6739,27 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6759,7 +6779,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>6246</t>
@@ -6767,12 +6791,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6782,7 +6806,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6792,17 +6816,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>-18.88</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6812,7 +6836,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -6867,7 +6891,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-21.97</t>
+          <t>-19.94</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -6877,17 +6901,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -6898,50 +6922,50 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>75.85</t>
+          <t>86.11</t>
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>0.6</v>
+        <v>2.44</v>
       </c>
       <c r="AI16" t="n">
-        <v>-2.13</v>
+        <v>-1.35</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-6.16</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>13.52</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>13.71</v>
+        <v>13.7</v>
       </c>
       <c r="AN16" t="n">
-        <v>14.24</v>
+        <v>14.21</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -6950,15 +6974,15 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>18.80</t>
         </is>
       </c>
       <c r="AQ16" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="AR16" t="n">
         <v>-0.27</v>
       </c>
-      <c r="AR16" t="n">
-        <v>-0.28</v>
-      </c>
       <c r="AS16" t="inlineStr">
         <is>
           <t>2.34</t>
@@ -6966,7 +6990,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-112.13</t>
+          <t>-111.58</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -6976,43 +7000,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>7292.129101283879</t>
+          <t>7282.384615384615</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>516.0</t>
+          <t>340.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>534.6</v>
+        <v>360</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>437.4</t>
+          <t>443.8</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>468.04</v>
+        <v>464.82</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>-83</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-12.02299824989772</t>
+          <t>-13.94522520253159</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-18.58438332743214</t>
+          <t>-24.51747344201789</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>516.0</t>
+          <t>340.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7032,7 +7056,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7077,7 +7101,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7087,7 +7111,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7102,7 +7126,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>30.33</t>
+          <t>30.11</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7117,12 +7141,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>513</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7137,27 +7161,27 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>14.05</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7177,7 +7201,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>6246</t>
@@ -7185,12 +7213,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7200,7 +7228,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7210,17 +7238,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7230,7 +7258,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7285,7 +7313,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-22.25</t>
+          <t>-21.97</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7295,17 +7323,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7316,50 +7344,50 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>60.36</t>
+          <t>75.85</t>
         </is>
       </c>
       <c r="AH17" t="n">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="AI17" t="n">
-        <v>-2.53</v>
+        <v>-2.13</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>13.42</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>13.74</v>
+        <v>13.71</v>
       </c>
       <c r="AN17" t="n">
-        <v>14.28</v>
+        <v>14.24</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7368,15 +7396,15 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="AQ17" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="AR17" t="n">
         <v>-0.28</v>
       </c>
-      <c r="AR17" t="n">
-        <v>-0.29</v>
-      </c>
       <c r="AS17" t="inlineStr">
         <is>
           <t>2.34</t>
@@ -7384,7 +7412,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-112.32</t>
+          <t>-112.13</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7394,43 +7422,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>7292.129101283879</t>
+          <t>7282.384615384615</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>516.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>472.6</v>
+        <v>534.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>402.3</t>
+          <t>437.4</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>481.38</v>
+        <v>468.04</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>97</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-10.83001914489146</t>
+          <t>-12.02299824989772</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-28.30195518775838</t>
+          <t>-18.58438332743214</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>516.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7450,7 +7478,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7495,7 +7523,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7505,7 +7533,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7520,7 +7548,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>30.33</t>
+          <t>30.11</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7535,12 +7563,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>513</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7555,7 +7583,7 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
@@ -7565,7 +7593,7 @@
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
@@ -7575,7 +7603,7 @@
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7597,7 +7625,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7607,42 +7635,42 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>13.45</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>0.74</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>45.0</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>13.45</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7652,7 +7680,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7717,17 +7745,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7738,63 +7766,63 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>60.36</t>
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>1.13</v>
+        <v>0.45</v>
       </c>
       <c r="AI18" t="n">
-        <v>-3.41</v>
+        <v>-2.53</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.83</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>13.77</v>
+        <v>13.74</v>
       </c>
       <c r="AN18" t="n">
-        <v>14.31</v>
+        <v>14.28</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AQ18" t="n">
-        <v>-0.3</v>
+        <v>-0.28</v>
       </c>
       <c r="AR18" t="n">
         <v>-0.29</v>
@@ -7806,7 +7834,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-112.36</t>
+          <t>-112.32</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7816,43 +7844,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>7292.129101283879</t>
+          <t>7282.384615384615</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>507.6</v>
+        <v>472.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>424.0</t>
+          <t>402.3</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>517.4400000000001</v>
+        <v>481.38</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-7.653303500733839</t>
+          <t>-10.83001914489146</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>3.719440554195444</t>
+          <t>-28.30195518775838</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -7917,7 +7945,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -7942,7 +7970,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>30.33</t>
+          <t>30.11</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -7957,12 +7985,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>513</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -7977,22 +8005,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8029,12 +8057,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8044,7 +8072,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8054,17 +8082,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8074,7 +8102,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8129,7 +8157,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-22.83</t>
+          <t>-22.25</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8139,17 +8167,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8160,50 +8188,50 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>0.6</v>
+        <v>1.13</v>
       </c>
       <c r="AI19" t="n">
-        <v>-3.84</v>
+        <v>-3.41</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>13.8</v>
+        <v>13.77</v>
       </c>
       <c r="AN19" t="n">
-        <v>14.35</v>
+        <v>14.31</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8212,11 +8240,11 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AQ19" t="n">
-        <v>-0.31</v>
+        <v>-0.3</v>
       </c>
       <c r="AR19" t="n">
         <v>-0.29</v>
@@ -8228,7 +8256,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-112.26</t>
+          <t>-112.36</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8238,43 +8266,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>7292.129101283879</t>
+          <t>7282.384615384615</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>459.6</v>
+        <v>507.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>420.3</t>
+          <t>424.0</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>554.86</v>
+        <v>517.4400000000001</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-9.721075147084617</t>
+          <t>-7.653303500733839</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-6.061402691377396</t>
+          <t>3.719440554195444</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8294,7 +8322,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-4.30</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8339,7 +8367,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8349,7 +8377,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8364,7 +8392,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>30.33</t>
+          <t>30.11</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8379,12 +8407,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>513</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8399,27 +8427,27 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8456,7 +8484,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8476,17 +8504,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-9.92</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8496,7 +8524,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8561,17 +8589,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8582,50 +8610,50 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>0.23</v>
+        <v>0.6</v>
       </c>
       <c r="AI20" t="n">
-        <v>-3.71</v>
+        <v>-3.84</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.83</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>13.83</v>
+        <v>13.8</v>
       </c>
       <c r="AN20" t="n">
-        <v>14.41</v>
+        <v>14.35</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8634,14 +8662,14 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-12.91</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="AQ20" t="n">
-        <v>-0.32</v>
+        <v>-0.31</v>
       </c>
       <c r="AR20" t="n">
-        <v>-0.28</v>
+        <v>-0.29</v>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
@@ -8650,7 +8678,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-111.98</t>
+          <t>-112.26</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8660,43 +8688,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>7292.129101283879</t>
+          <t>7282.384615384615</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>1213.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>527.6</v>
+        <v>459.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>585.7</t>
+          <t>420.3</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>567.6799999999999</v>
+        <v>554.86</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-58</t>
+          <t>39</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-10.38647013903138</t>
+          <t>-9.721075147084617</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>21.00387133963898</t>
+          <t>-6.061402691377396</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>1213.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8761,12 +8789,12 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -8786,7 +8814,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>30.33</t>
+          <t>30.11</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8801,12 +8829,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>513</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -8821,12 +8849,12 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -8836,7 +8864,7 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -8873,12 +8901,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -8898,17 +8926,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-31.65</t>
+          <t>-9.92</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -8918,7 +8946,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -8983,17 +9011,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9004,50 +9032,50 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>-0.15</v>
+        <v>0.23</v>
       </c>
       <c r="AI21" t="n">
-        <v>-3.57</v>
+        <v>-3.71</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>13.86</v>
+        <v>13.83</v>
       </c>
       <c r="AN21" t="n">
-        <v>14.48</v>
+        <v>14.41</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9056,14 +9084,14 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-16.60</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AQ21" t="n">
         <v>-0.32</v>
       </c>
       <c r="AR21" t="n">
-        <v>-0.27</v>
+        <v>-0.28</v>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
@@ -9072,7 +9100,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-111.60</t>
+          <t>-111.98</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9082,43 +9110,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>7292.129101283879</t>
+          <t>7282.384615384615</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>1213.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>340.2</v>
+        <v>527.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>497.7</t>
+          <t>585.7</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>555.26</v>
+        <v>567.6799999999999</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-157</t>
+          <t>-58</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-16.09380495333509</t>
+          <t>-10.38647013903138</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-46.08158973532466</t>
+          <t>21.00387133963898</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>1213.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9183,7 +9211,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9208,7 +9236,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>30.33</t>
+          <t>30.11</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9223,12 +9251,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>513</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9243,22 +9271,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9295,12 +9323,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9310,7 +9338,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9320,17 +9348,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-48.73</t>
+          <t>-31.65</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9340,7 +9368,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9395,7 +9423,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-24.86</t>
+          <t>-22.83</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9405,17 +9433,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9426,50 +9454,50 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>-3.2</v>
+        <v>-0.15</v>
       </c>
       <c r="AI22" t="n">
-        <v>-3.38</v>
+        <v>-3.57</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>13.43</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>13.9</v>
+        <v>13.86</v>
       </c>
       <c r="AN22" t="n">
-        <v>14.55</v>
+        <v>14.48</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9478,14 +9506,14 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-19.79</t>
+          <t>-16.60</t>
         </is>
       </c>
       <c r="AQ22" t="n">
-        <v>-0.31</v>
+        <v>-0.32</v>
       </c>
       <c r="AR22" t="n">
-        <v>-0.26</v>
+        <v>-0.27</v>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
@@ -9494,7 +9522,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-111.11</t>
+          <t>-111.60</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9504,43 +9532,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>7292.129101283879</t>
+          <t>7282.384615384615</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>332</v>
+        <v>340.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>647.5</t>
+          <t>497.7</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>577.0599999999999</v>
+        <v>555.26</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-315</t>
+          <t>-157</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-10.6414804475188</t>
+          <t>-16.09380495333509</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-32.37933449472541</t>
+          <t>-46.08158973532466</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9560,7 +9588,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-4.30</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9605,7 +9633,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9615,7 +9643,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9630,7 +9658,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>30.33</t>
+          <t>30.11</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9645,12 +9673,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>513</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9665,27 +9693,27 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
+          <t>12.9</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
           <t>13.4</t>
         </is>
       </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>13.55</t>
-        </is>
-      </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9717,12 +9745,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9732,7 +9760,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9742,17 +9770,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-45.61</t>
+          <t>-48.73</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9762,7 +9790,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -9817,7 +9845,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-23.12</t>
+          <t>-24.86</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -9827,17 +9855,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -9848,12 +9876,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -9867,31 +9895,31 @@
         </is>
       </c>
       <c r="AH23" t="n">
-        <v>-2.35</v>
+        <v>-3.2</v>
       </c>
       <c r="AI23" t="n">
-        <v>-2.37</v>
+        <v>-3.38</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>13.62</t>
+          <t>13.43</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>13.95</v>
+        <v>13.9</v>
       </c>
       <c r="AN23" t="n">
-        <v>14.64</v>
+        <v>14.55</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -9900,14 +9928,14 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-19.79</t>
         </is>
       </c>
       <c r="AQ23" t="n">
-        <v>-0.27</v>
+        <v>-0.31</v>
       </c>
       <c r="AR23" t="n">
-        <v>-0.25</v>
+        <v>-0.26</v>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
@@ -9916,7 +9944,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-110.56</t>
+          <t>-111.11</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -9926,43 +9954,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>7292.129101283879</t>
+          <t>7282.384615384615</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>374.0</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>340.4</v>
+        <v>332</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>625.9</t>
+          <t>647.5</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>605.1799999999999</v>
+        <v>577.0599999999999</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-285</t>
+          <t>-315</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-6.68914334802669</t>
+          <t>-10.6414804475188</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-18.71970791905761</t>
+          <t>-32.37933449472541</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>374.0</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -9982,7 +10010,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10027,7 +10055,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10037,7 +10065,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10052,7 +10080,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>30.33</t>
+          <t>30.11</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10067,12 +10095,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>513</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10087,27 +10115,27 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>13.15</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10127,7 +10155,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>3149</t>
@@ -10135,12 +10167,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>879.422</t>
+          <t>1531.94</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10150,7 +10182,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>34.15</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -10165,12 +10197,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10235,7 +10267,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-8.76</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -10245,17 +10277,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -10266,66 +10298,66 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>719</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>42.77</t>
+          <t>36.79</t>
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>0.15</v>
+        <v>-0.65</v>
       </c>
       <c r="AI24" t="n">
-        <v>-2.75</v>
+        <v>-2.18</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-8.2</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.07</t>
         </is>
       </c>
       <c r="AM24" t="n">
-        <v>35.06</v>
+        <v>34.83</v>
       </c>
       <c r="AN24" t="n">
-        <v>38.2</v>
+        <v>37.99</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>8.91</t>
         </is>
       </c>
       <c r="AQ24" t="n">
-        <v>-1.02</v>
+        <v>-1</v>
       </c>
       <c r="AR24" t="n">
-        <v>-1.12</v>
+        <v>-1.1</v>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
@@ -10334,7 +10366,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>-130.68</t>
+          <t>-130.02</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -10344,43 +10376,43 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>231556527.4343795</t>
+          <t>231337595.1602564</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>29976176.0</t>
+          <t>51910714.0</t>
         </is>
       </c>
       <c r="AX24" t="n">
-        <v>29647816.6</v>
+        <v>34584994.8</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>31088710.7</t>
+          <t>32402375.5</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>187517443.84</v>
+        <v>168663097.68</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>-1440894</t>
+          <t>2182619</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>-18053080.27959415</t>
+          <t>-16743788.28363248</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-12368162.47864045</t>
+          <t>-9542682.305843279</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>29976176.0</t>
+          <t>51910714.0</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -10400,7 +10432,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -10445,7 +10477,7 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -10455,7 +10487,7 @@
       </c>
       <c r="BS24" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="BT24" t="inlineStr">
@@ -10485,12 +10517,12 @@
       </c>
       <c r="BY24" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -10510,22 +10542,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>34.05</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>34.15</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>33.65</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>34.15</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -10545,7 +10577,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>3149</t>
@@ -10553,12 +10589,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1072.806</t>
+          <t>879.422</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10568,7 +10604,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>34.15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -10578,17 +10614,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-13.85</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -10653,7 +10689,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-6.74</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -10663,17 +10699,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -10684,66 +10720,66 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>719</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>34.57</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="AH25" t="n">
-        <v>1.14</v>
+        <v>0.15</v>
       </c>
       <c r="AI25" t="n">
-        <v>-3.05</v>
+        <v>-2.75</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>-8.12</t>
+          <t>-8.2</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>34.20999999999999</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>35.29</v>
+        <v>35.06</v>
       </c>
       <c r="AN25" t="n">
-        <v>38.41</v>
+        <v>38.2</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>37.82</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="AQ25" t="n">
-        <v>-1.06</v>
+        <v>-1.02</v>
       </c>
       <c r="AR25" t="n">
-        <v>-1.15</v>
+        <v>-1.12</v>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
@@ -10752,7 +10788,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>-131.38</t>
+          <t>-130.68</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -10762,43 +10798,43 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>231556527.4343795</t>
+          <t>231337595.1602564</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>37113075.0</t>
+          <t>29976176.0</t>
         </is>
       </c>
       <c r="AX25" t="n">
-        <v>28180230.6</v>
+        <v>29647816.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>32709006.3</t>
+          <t>31088710.7</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>203000139.16</v>
+        <v>187517443.84</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>-4528775</t>
+          <t>-1440894</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>-19086701.69794936</t>
+          <t>-18053080.27959415</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-13612713.56554211</t>
+          <t>-12368162.47864045</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>37113075.0</t>
+          <t>29976176.0</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -10818,7 +10854,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
@@ -10863,17 +10899,17 @@
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS25" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="BT25" t="inlineStr">
@@ -10903,12 +10939,12 @@
       </c>
       <c r="BY25" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -10928,22 +10964,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>34.15</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -10963,7 +10999,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>3149</t>
@@ -10971,12 +11011,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>680.189</t>
+          <t>1072.806</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -10986,7 +11026,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -10996,12 +11036,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -11071,7 +11111,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-8.36</t>
+          <t>-6.74</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -11081,17 +11121,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -11102,66 +11142,66 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>719</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>34.57</t>
         </is>
       </c>
       <c r="AH26" t="n">
-        <v>-0.67</v>
+        <v>1.14</v>
       </c>
       <c r="AI26" t="n">
-        <v>-3.65</v>
+        <v>-3.05</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-7.85</t>
+          <t>-8.12</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>34.20999999999999</t>
         </is>
       </c>
       <c r="AM26" t="n">
-        <v>35.52</v>
+        <v>35.29</v>
       </c>
       <c r="AN26" t="n">
-        <v>38.55</v>
+        <v>38.41</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>37.82</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="AQ26" t="n">
-        <v>-1.14</v>
+        <v>-1.06</v>
       </c>
       <c r="AR26" t="n">
-        <v>-1.17</v>
+        <v>-1.15</v>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
@@ -11170,7 +11210,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>-131.97</t>
+          <t>-131.38</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -11180,43 +11220,43 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>231556527.4343795</t>
+          <t>231337595.1602564</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>23145831.0</t>
+          <t>37113075.0</t>
         </is>
       </c>
       <c r="AX26" t="n">
-        <v>28055340.4</v>
+        <v>28180230.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>32565131.1</t>
+          <t>32709006.3</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>214383272.46</v>
+        <v>203000139.16</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>-4509790</t>
+          <t>-4528775</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>-20081972.26747796</t>
+          <t>-19086701.69794936</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-15669143.09806082</t>
+          <t>-13612713.56554211</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>23145831.0</t>
+          <t>37113075.0</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
@@ -11236,7 +11276,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -11281,17 +11321,17 @@
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS26" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BT26" t="inlineStr">
@@ -11321,12 +11361,12 @@
       </c>
       <c r="BY26" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -11346,22 +11386,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>33.85</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -11381,7 +11421,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>3149</t>
@@ -11389,12 +11433,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>908.595</t>
+          <t>680.189</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11404,7 +11448,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11414,17 +11458,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-13.85</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -11489,7 +11533,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-9.03</t>
+          <t>-8.36</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -11499,17 +11543,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -11520,63 +11564,63 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>719</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>-1.98</v>
+        <v>-0.67</v>
       </c>
       <c r="AI27" t="n">
-        <v>-3.48</v>
+        <v>-3.65</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-7.85</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AM27" t="n">
-        <v>35.67</v>
+        <v>35.52</v>
       </c>
       <c r="AN27" t="n">
-        <v>38.71</v>
+        <v>38.55</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>37.74</t>
+          <t>37.78</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AQ27" t="n">
-        <v>-1.17</v>
+        <v>-1.14</v>
       </c>
       <c r="AR27" t="n">
         <v>-1.17</v>
@@ -11588,7 +11632,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>-132.13</t>
+          <t>-131.97</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -11598,43 +11642,43 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>231556527.4343795</t>
+          <t>231337595.1602564</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>30779178.0</t>
+          <t>23145831.0</t>
         </is>
       </c>
       <c r="AX27" t="n">
-        <v>30495285.4</v>
+        <v>28055340.4</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>35145840.3</t>
+          <t>32565131.1</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>228943265.06</v>
+        <v>214383272.46</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>-4650554</t>
+          <t>-4509790</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>-20884304.84373562</t>
+          <t>-20081972.26747796</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-16550796.89101397</t>
+          <t>-15669143.09806082</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>30779178.0</t>
+          <t>23145831.0</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -11654,7 +11698,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -11699,7 +11743,7 @@
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -11709,7 +11753,7 @@
       </c>
       <c r="BS27" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BT27" t="inlineStr">
@@ -11739,12 +11783,12 @@
       </c>
       <c r="BY27" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -11764,7 +11808,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -11774,12 +11818,12 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -11799,7 +11843,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>3149</t>
@@ -11807,12 +11855,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>797.737</t>
+          <t>908.595</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -11822,7 +11870,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -11832,17 +11880,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-24.16</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -11907,7 +11955,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-8.36</t>
+          <t>-9.03</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -11917,17 +11965,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -11938,59 +11986,59 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>719</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>60.49</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AH28" t="n">
-        <v>-1.56</v>
+        <v>-1.98</v>
       </c>
       <c r="AI28" t="n">
-        <v>-3.54</v>
+        <v>-3.48</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-7.74</t>
+          <t>-7.84</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>34.43</t>
         </is>
       </c>
       <c r="AM28" t="n">
-        <v>35.81</v>
+        <v>35.67</v>
       </c>
       <c r="AN28" t="n">
-        <v>38.81</v>
+        <v>38.71</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.74</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AQ28" t="n">
@@ -12006,7 +12054,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>-132.14</t>
+          <t>-132.13</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -12016,43 +12064,43 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>231556527.4343795</t>
+          <t>231337595.1602564</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>27224823.0</t>
+          <t>30779178.0</t>
         </is>
       </c>
       <c r="AX28" t="n">
-        <v>30219756.2</v>
+        <v>30495285.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>39847131.9</t>
+          <t>35145840.3</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>236001176.02</v>
+        <v>228943265.06</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>-9627375</t>
+          <t>-4650554</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>-21672215.3805941</t>
+          <t>-20884304.84373562</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-18037061.02769653</t>
+          <t>-16550796.89101397</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>27224823.0</t>
+          <t>30779178.0</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
@@ -12072,7 +12120,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -12117,7 +12165,7 @@
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -12127,7 +12175,7 @@
       </c>
       <c r="BS28" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="BT28" t="inlineStr">
@@ -12157,12 +12205,12 @@
       </c>
       <c r="BY28" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -12182,22 +12230,22 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -12217,7 +12265,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>3149</t>
@@ -12225,12 +12277,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>652.267</t>
+          <t>797.737</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12240,7 +12292,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -12250,17 +12302,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-30.44</t>
+          <t>-24.16</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -12325,7 +12377,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-6.47</t>
+          <t>-8.36</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -12335,17 +12387,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -12356,66 +12408,66 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>719</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>60.49</t>
         </is>
       </c>
       <c r="AH29" t="n">
-        <v>0.67</v>
+        <v>-1.56</v>
       </c>
       <c r="AI29" t="n">
-        <v>-4.2</v>
+        <v>-3.54</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-7.74</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>34.47</t>
+          <t>34.54</t>
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>35.98</v>
+        <v>35.81</v>
       </c>
       <c r="AN29" t="n">
-        <v>38.91</v>
+        <v>38.81</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>37.67</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AQ29" t="n">
         <v>-1.17</v>
       </c>
       <c r="AR29" t="n">
-        <v>-1.18</v>
+        <v>-1.17</v>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
@@ -12424,7 +12476,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>-132.19</t>
+          <t>-132.14</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -12434,43 +12486,43 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>231556527.4343795</t>
+          <t>231337595.1602564</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>22638246.0</t>
+          <t>27224823.0</t>
         </is>
       </c>
       <c r="AX29" t="n">
-        <v>32529604.8</v>
+        <v>30219756.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>46763411.2</t>
+          <t>39847131.9</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>241442940.72</v>
+        <v>236001176.02</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>-14233806</t>
+          <t>-9627375</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>-22333152.53566639</t>
+          <t>-21672215.3805941</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>-19135291.00768245</t>
+          <t>-18037061.02769653</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>22638246.0</t>
+          <t>27224823.0</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
@@ -12490,7 +12542,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -12535,7 +12587,7 @@
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
@@ -12545,7 +12597,7 @@
       </c>
       <c r="BS29" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BT29" t="inlineStr">
@@ -12575,12 +12627,12 @@
       </c>
       <c r="BY29" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ29" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="CA29" t="inlineStr">
@@ -12605,17 +12657,17 @@
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -12637,7 +12689,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -12647,12 +12699,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1052.554</t>
+          <t>652.267</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -12672,17 +12724,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-26.38</t>
+          <t>-30.44</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -12757,17 +12809,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -12778,12 +12830,12 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>719</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -12793,48 +12845,48 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>48.28</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AH30" t="n">
-        <v>0.9</v>
+        <v>0.67</v>
       </c>
       <c r="AI30" t="n">
-        <v>-4.68</v>
+        <v>-4.2</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>34.39</t>
+          <t>34.47</t>
         </is>
       </c>
       <c r="AM30" t="n">
-        <v>36.08</v>
+        <v>35.98</v>
       </c>
       <c r="AN30" t="n">
-        <v>38.92</v>
+        <v>38.91</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>37.67</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AQ30" t="n">
-        <v>-1.22</v>
+        <v>-1.17</v>
       </c>
       <c r="AR30" t="n">
         <v>-1.18</v>
@@ -12846,7 +12898,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>-132.25</t>
+          <t>-132.19</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -12856,43 +12908,43 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>231556527.4343795</t>
+          <t>231337595.1602564</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>36488624.0</t>
+          <t>22638246.0</t>
         </is>
       </c>
       <c r="AX30" t="n">
-        <v>37237782</v>
+        <v>32529604.8</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>50581063.8</t>
+          <t>46763411.2</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>242256442.44</v>
+        <v>241442940.72</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>-13343281</t>
+          <t>-14233806</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>-22914581.90439074</t>
+          <t>-22333152.53566639</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>-19529368.76453082</t>
+          <t>-19135291.00768245</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>36488624.0</t>
+          <t>22638246.0</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
@@ -12957,7 +13009,7 @@
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
@@ -12997,12 +13049,12 @@
       </c>
       <c r="BY30" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ30" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="CA30" t="inlineStr">
@@ -13022,17 +13074,17 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
@@ -13069,12 +13121,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1012.048</t>
+          <t>1052.554</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13084,7 +13136,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -13094,17 +13146,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-30.50</t>
+          <t>-26.38</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -13169,7 +13221,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -13179,17 +13231,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -13200,66 +13252,66 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>719</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>48.21</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>48.28</t>
         </is>
       </c>
       <c r="AH31" t="n">
-        <v>1.71</v>
+        <v>0.9</v>
       </c>
       <c r="AI31" t="n">
-        <v>-4.91</v>
+        <v>-4.68</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>34.41</t>
+          <t>34.39</t>
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>36.18</v>
+        <v>36.08</v>
       </c>
       <c r="AN31" t="n">
-        <v>38.94</v>
+        <v>38.92</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>37.63</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AQ31" t="n">
-        <v>-1.28</v>
+        <v>-1.22</v>
       </c>
       <c r="AR31" t="n">
-        <v>-1.17</v>
+        <v>-1.18</v>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
@@ -13268,7 +13320,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>-131.94</t>
+          <t>-132.25</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -13278,43 +13330,43 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>231556527.4343795</t>
+          <t>231337595.1602564</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>35345556.0</t>
+          <t>36488624.0</t>
         </is>
       </c>
       <c r="AX31" t="n">
-        <v>37074921.8</v>
+        <v>37237782</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>53345322.1</t>
+          <t>50581063.8</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>245778298.12</v>
+        <v>242256442.44</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>-16270400</t>
+          <t>-13343281</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>-23530075.2025471</t>
+          <t>-22914581.90439074</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>-20878828.60415238</t>
+          <t>-19529368.76453082</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>35345556.0</t>
+          <t>36488624.0</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -13334,7 +13386,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -13379,17 +13431,17 @@
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS31" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="BT31" t="inlineStr">
@@ -13419,12 +13471,12 @@
       </c>
       <c r="BY31" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ31" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="CA31" t="inlineStr">
@@ -13444,22 +13496,22 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -13491,12 +13543,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>857.193</t>
+          <t>1012.048</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -13506,7 +13558,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13516,17 +13568,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-31.65</t>
+          <t>-30.50</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -13591,7 +13643,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-7.55</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -13601,17 +13653,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -13622,66 +13674,66 @@
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>719</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>48.21</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>10.92</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AH32" t="n">
-        <v>0.41</v>
+        <v>1.71</v>
       </c>
       <c r="AI32" t="n">
-        <v>-5.97</v>
+        <v>-4.91</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>34.16</t>
+          <t>34.41</t>
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>36.33</v>
+        <v>36.18</v>
       </c>
       <c r="AN32" t="n">
-        <v>39</v>
+        <v>38.94</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>37.52</t>
+          <t>37.58</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AQ32" t="n">
-        <v>-1.36</v>
+        <v>-1.28</v>
       </c>
       <c r="AR32" t="n">
-        <v>-1.14</v>
+        <v>-1.17</v>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
@@ -13690,7 +13742,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>-131.18</t>
+          <t>-131.94</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -13700,43 +13752,43 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>231556527.4343795</t>
+          <t>231337595.1602564</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>29401532.0</t>
+          <t>35345556.0</t>
         </is>
       </c>
       <c r="AX32" t="n">
-        <v>39796395.2</v>
+        <v>37074921.8</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>58228190.4</t>
+          <t>53345322.1</t>
         </is>
       </c>
       <c r="AZ32" t="n">
-        <v>247556548.26</v>
+        <v>245778298.12</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>-18431795</t>
+          <t>-16270400</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>-24012120.03861886</t>
+          <t>-23530075.2025471</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>-21938484.35346347</t>
+          <t>-20878828.60415238</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>29401532.0</t>
+          <t>35345556.0</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
@@ -13756,7 +13808,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
@@ -13801,7 +13853,7 @@
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
@@ -13811,7 +13863,7 @@
       </c>
       <c r="BS32" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BT32" t="inlineStr">
@@ -13841,12 +13893,12 @@
       </c>
       <c r="BY32" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ32" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="CA32" t="inlineStr">
@@ -13866,22 +13918,22 @@
       </c>
       <c r="CD32" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="CF32" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="CG32" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CH32" t="inlineStr">
@@ -13913,12 +13965,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1145.3</t>
+          <t>857.193</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -13928,7 +13980,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>33.65</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -13938,17 +13990,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-25.49</t>
+          <t>-31.65</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -14013,7 +14065,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-9.30</t>
+          <t>-7.55</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -14023,17 +14075,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -14044,66 +14096,66 @@
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>719</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>10.92</t>
         </is>
       </c>
       <c r="AH33" t="n">
-        <v>-1.38</v>
+        <v>0.41</v>
       </c>
       <c r="AI33" t="n">
-        <v>-6.49</v>
+        <v>-5.97</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>34.11999999999999</t>
+          <t>34.16</t>
         </is>
       </c>
       <c r="AM33" t="n">
-        <v>36.49</v>
+        <v>36.33</v>
       </c>
       <c r="AN33" t="n">
-        <v>39.06</v>
+        <v>39</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>37.47</t>
+          <t>37.52</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>-26.04</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="AQ33" t="n">
-        <v>-1.37</v>
+        <v>-1.36</v>
       </c>
       <c r="AR33" t="n">
-        <v>-1.08</v>
+        <v>-1.14</v>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
@@ -14112,7 +14164,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>-129.70</t>
+          <t>-131.18</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -14122,43 +14174,43 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>231556527.4343795</t>
+          <t>231337595.1602564</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>38774066.0</t>
+          <t>29401532.0</t>
         </is>
       </c>
       <c r="AX33" t="n">
-        <v>49474507.6</v>
+        <v>39796395.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>66401056.1</t>
+          <t>58228190.4</t>
         </is>
       </c>
       <c r="AZ33" t="n">
-        <v>249662887.18</v>
+        <v>247556548.26</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>-16926548</t>
+          <t>-18431795</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>-24389144.70864711</t>
+          <t>-24012120.03861886</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>-22031901.26842704</t>
+          <t>-21938484.35346347</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>38774066.0</t>
+          <t>29401532.0</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
@@ -14178,7 +14230,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -14223,7 +14275,7 @@
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR33" t="inlineStr">
@@ -14233,7 +14285,7 @@
       </c>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
@@ -14263,12 +14315,12 @@
       </c>
       <c r="BY33" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ33" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="CA33" t="inlineStr">
@@ -14288,22 +14340,22 @@
       </c>
       <c r="CD33" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="CE33" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.55</t>
         </is>
       </c>
       <c r="CF33" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="CG33" t="inlineStr">
         <is>
-          <t>33.65</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CH33" t="inlineStr">
@@ -14335,12 +14387,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1345.621</t>
+          <t>1145.3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14350,7 +14402,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>33.65</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -14360,17 +14412,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-27.63</t>
+          <t>-25.49</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -14435,7 +14487,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-7.55</t>
+          <t>-9.30</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -14445,17 +14497,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -14466,17 +14518,17 @@
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>719</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>13.92</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
@@ -14485,47 +14537,47 @@
         </is>
       </c>
       <c r="AH34" t="n">
-        <v>-0.09</v>
+        <v>-1.38</v>
       </c>
       <c r="AI34" t="n">
         <v>-6.49</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>-6.2</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>34.33</t>
+          <t>34.11999999999999</t>
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>36.71</v>
+        <v>36.49</v>
       </c>
       <c r="AN34" t="n">
-        <v>39.14</v>
+        <v>39.06</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>37.43</t>
+          <t>37.47</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>-27.70</t>
+          <t>-26.04</t>
         </is>
       </c>
       <c r="AQ34" t="n">
-        <v>-1.3</v>
+        <v>-1.37</v>
       </c>
       <c r="AR34" t="n">
-        <v>-1.01</v>
+        <v>-1.08</v>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
@@ -14534,7 +14586,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>-127.76</t>
+          <t>-129.70</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -14544,43 +14596,43 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>231556527.4343795</t>
+          <t>231337595.1602564</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>46179132.0</t>
+          <t>38774066.0</t>
         </is>
       </c>
       <c r="AX34" t="n">
-        <v>60997217.6</v>
+        <v>49474507.6</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>84286762.5</t>
+          <t>66401056.1</t>
         </is>
       </c>
       <c r="AZ34" t="n">
-        <v>254822433.06</v>
+        <v>249662887.18</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>-23289544</t>
+          <t>-16926548</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>-24817734.42505076</t>
+          <t>-24389144.70864711</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>-22382700.45878832</t>
+          <t>-22031901.26842704</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>46179132.0</t>
+          <t>38774066.0</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
@@ -14600,7 +14652,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
@@ -14645,7 +14697,7 @@
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
@@ -14655,7 +14707,7 @@
       </c>
       <c r="BS34" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="BT34" t="inlineStr">
@@ -14685,12 +14737,12 @@
       </c>
       <c r="BY34" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ34" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="CA34" t="inlineStr">
@@ -14710,22 +14762,22 @@
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>34.05</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="CE34" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="CF34" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="CG34" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>33.65</t>
         </is>
       </c>
       <c r="CH34" t="inlineStr">

--- a/Result/checksun_type/玻璃基板.xlsx
+++ b/Result/checksun_type/玻璃基板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>31.793</t>
+          <t>54.328</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>23.03</t>
+          <t>27.65</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.50</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>74.19</t>
+          <t>70.97</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>88.37</t>
+          <t>78.69</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.15</v>
+        <v>-0.96</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.32</v>
+        <v>2.14</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>25.6</v>
+        <v>25.55</v>
       </c>
       <c r="AN2" t="n">
-        <v>26.71</v>
+        <v>26.69</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>38.28</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.28</v>
+        <v>-0.24</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.45</v>
+        <v>-0.4</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-114.77</t>
+          <t>-113.41</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>60481961.47807638</t>
+          <t>60399496.40677966</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>821520.0</t>
+          <t>1397794.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>4356438.6</v>
+        <v>4118812.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3541027.4</t>
+          <t>3226619.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>9017458.68</v>
+        <v>8922557.08</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>815411</t>
+          <t>892193</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-993613.0125357707</t>
+          <t>-962371.2123215774</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-715739.6873801965</t>
+          <t>-790541.3111435147</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>821520.0</t>
+          <t>1397794.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>79.72</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>96.636</t>
+          <t>31.793</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>22.72</t>
+          <t>23.03</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>-7.50</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>74.19</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>88.37</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>1.71</v>
+        <v>-0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.29</v>
+        <v>1.32</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>25.64</v>
+        <v>25.6</v>
       </c>
       <c r="AN3" t="n">
-        <v>26.74</v>
+        <v>26.71</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>26.04</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>34.57</t>
+          <t>38.28</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.32</v>
+        <v>-0.28</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.49</v>
+        <v>-0.45</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-116.18</t>
+          <t>-114.77</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>60481961.47807638</t>
+          <t>60399496.40677966</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2494335.0</t>
+          <t>821520.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>4478414</v>
+        <v>4356438.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3649229.2</t>
+          <t>3541027.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>9357524.42</v>
+        <v>9017458.68</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>829184</t>
+          <t>815411</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1044135.43529133</t>
+          <t>-993613.0125357707</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-521574.4503118787</t>
+          <t>-715739.6873801965</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2494335.0</t>
+          <t>821520.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>79.72</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1717,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>195.468</t>
+          <t>96.636</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>22.72</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.20</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>3.02</v>
+        <v>1.71</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.67</v>
+        <v>0.29</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>25.7</v>
+        <v>25.64</v>
       </c>
       <c r="AN4" t="n">
-        <v>26.79</v>
+        <v>26.74</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>26.04</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>25.17</t>
+          <t>34.57</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.4</v>
+        <v>-0.32</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.53</v>
+        <v>-0.49</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-117.58</t>
+          <t>-116.18</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>60481961.47807638</t>
+          <t>60399496.40677966</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>5207526.0</t>
+          <t>2494335.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>4629628.2</v>
+        <v>4478414</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3696072.6</t>
+          <t>3649229.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>10084690.88</v>
+        <v>9357524.42</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>933555</t>
+          <t>829184</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1139146.523469412</t>
+          <t>-1044135.43529133</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-404798.0598460007</t>
+          <t>-521574.4503118787</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>5207526.0</t>
+          <t>2494335.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,17 +2037,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>79.72</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
+          <t>25.4</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>26.15</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>26.3</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>405.481</t>
+          <t>195.468</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>7.20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,12 +2280,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2295,51 +2295,51 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>4.12</v>
+        <v>3.02</v>
       </c>
       <c r="AI5" t="n">
-        <v>-1.9</v>
+        <v>-0.67</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>25.53</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>25.75</v>
+        <v>25.7</v>
       </c>
       <c r="AN5" t="n">
         <v>26.79</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>25.99</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>25.17</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.51</v>
+        <v>-0.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.53</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-118.68</t>
+          <t>-117.58</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>60481961.47807638</t>
+          <t>60399496.40677966</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>10672887.0</t>
+          <t>5207526.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3809271.8</v>
+        <v>4629628.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3609459.7</t>
+          <t>3696072.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>10245696.52</v>
+        <v>10084690.88</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>199812</t>
+          <t>933555</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1272664.425946395</t>
+          <t>-1139146.523469412</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-514216.6070431024</t>
+          <t>-404798.0598460007</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>10672887.0</t>
+          <t>5207526.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>79.72</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,17 +2524,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>27.05</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2561,7 +2561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>103.242</t>
+          <t>405.481</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-24.98</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-10.54</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.28</v>
+        <v>4.12</v>
       </c>
       <c r="AI6" t="n">
-        <v>-3.11</v>
+        <v>-1.9</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>25.78</v>
+        <v>25.75</v>
       </c>
       <c r="AN6" t="n">
-        <v>26.78</v>
+        <v>26.79</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>25.96</t>
+          <t>25.99</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-10.00</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.64</v>
+        <v>-0.51</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.58</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-119.17</t>
+          <t>-118.68</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>60481961.47807638</t>
+          <t>60399496.40677966</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2585925.0</t>
+          <t>10672887.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>2334426.2</v>
+        <v>3809271.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3111599.5</t>
+          <t>3609459.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>10171307.16</v>
+        <v>10245696.52</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-777173</t>
+          <t>199812</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1410564.029383358</t>
+          <t>-1272664.425946395</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1237738.331358852</t>
+          <t>-514216.6070431024</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2585925.0</t>
+          <t>10672887.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,17 +2881,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>79.72</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>27.05</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>57.864</t>
+          <t>103.242</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-24.98</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-11.61</t>
+          <t>-10.54</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>50.45</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-0.6</v>
+        <v>0.28</v>
       </c>
       <c r="AI7" t="n">
-        <v>-3.79</v>
+        <v>-3.11</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>25.88</v>
+        <v>25.78</v>
       </c>
       <c r="AN7" t="n">
         <v>26.78</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>25.96</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-18.27</t>
+          <t>-10.00</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.67</v>
+        <v>-0.64</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.58</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-118.69</t>
+          <t>-119.17</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>60481961.47807638</t>
+          <t>60399496.40677966</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1431397.0</t>
+          <t>2585925.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>2725616.2</v>
+        <v>2334426.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3344499.9</t>
+          <t>3111599.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>10170725.72</v>
+        <v>10171307.16</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-618883</t>
+          <t>-777173</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1441986.883569631</t>
+          <t>-1410564.029383358</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1360675.639975678</t>
+          <t>-1237738.331358852</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1431397.0</t>
+          <t>2585925.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>79.72</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>129.907</t>
+          <t>57.864</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-9.82</t>
+          <t>-11.61</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>50.45</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>1.73</v>
+        <v>-0.6</v>
       </c>
       <c r="AI8" t="n">
-        <v>-4.69</v>
+        <v>-3.79</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>26.04</v>
+        <v>25.88</v>
       </c>
       <c r="AN8" t="n">
-        <v>26.79</v>
+        <v>26.78</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>25.92</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-23.75</t>
+          <t>-18.27</t>
         </is>
       </c>
       <c r="AQ8" t="n">
         <v>-0.67</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.54</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-117.83</t>
+          <t>-118.69</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>60481961.47807638</t>
+          <t>60399496.40677966</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>3250406.0</t>
+          <t>1431397.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>2820044.4</v>
+        <v>2725616.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3938171.4</t>
+          <t>3344499.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>10185422.26</v>
+        <v>10170725.72</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1118127</t>
+          <t>-618883</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1456770.746041259</t>
+          <t>-1441986.883569631</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1364005.379429155</t>
+          <t>-1360675.639975678</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>3250406.0</t>
+          <t>1431397.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>79.72</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>44.221</t>
+          <t>129.907</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-32.35</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-10.89</t>
+          <t>-9.82</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>1.09</v>
+        <v>1.73</v>
       </c>
       <c r="AI9" t="n">
-        <v>-5.71</v>
+        <v>-4.69</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>26.18</v>
+        <v>26.04</v>
       </c>
       <c r="AN9" t="n">
-        <v>26.78</v>
+        <v>26.79</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-39.44</t>
+          <t>-23.75</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.71</v>
+        <v>-0.67</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.51</v>
+        <v>-0.54</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-116.78</t>
+          <t>-117.83</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>60481961.47807638</t>
+          <t>60399496.40677966</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1105744.0</t>
+          <t>3250406.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>2762517</v>
+        <v>2820044.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4083544.5</t>
+          <t>3938171.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>10163096.92</v>
+        <v>10185422.26</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1321027</t>
+          <t>-1118127</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1473637.176334369</t>
+          <t>-1456770.746041259</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1514941.493668794</t>
+          <t>-1364005.379429155</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1105744.0</t>
+          <t>3250406.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>79.72</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>132.605</t>
+          <t>44.221</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-21.31</t>
+          <t>-32.35</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-11.07</t>
+          <t>-10.89</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.48</v>
+        <v>1.09</v>
       </c>
       <c r="AI10" t="n">
-        <v>-6.05</v>
+        <v>-5.71</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>24.68</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>26.38</v>
+        <v>26.18</v>
       </c>
       <c r="AN10" t="n">
         <v>26.78</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-56.92</t>
+          <t>-39.44</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.72</v>
+        <v>-0.71</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.46</v>
+        <v>-0.51</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-115.12</t>
+          <t>-116.78</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>60481961.47807638</t>
+          <t>60399496.40677966</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>3298659.0</t>
+          <t>1105744.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>3409647.6</v>
+        <v>2762517</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4333083.4</t>
+          <t>4083544.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>10178782.26</v>
+        <v>10163096.92</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-923435</t>
+          <t>-1321027</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1466127.300455383</t>
+          <t>-1473637.176334369</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1446674.246380107</t>
+          <t>-1514941.493668794</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>3298659.0</t>
+          <t>1105744.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>79.72</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>182.531</t>
+          <t>132.605</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-11.85</t>
+          <t>-21.31</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-11.96</t>
+          <t>-11.07</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-0.08</v>
+        <v>0.48</v>
       </c>
       <c r="AI11" t="n">
-        <v>-7.33</v>
+        <v>-6.05</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>24.78</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>26.62</v>
+        <v>26.38</v>
       </c>
       <c r="AN11" t="n">
-        <v>26.79</v>
+        <v>26.78</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-82.30</t>
+          <t>-56.92</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.71</v>
+        <v>-0.72</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.39</v>
+        <v>-0.46</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-112.97</t>
+          <t>-115.12</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>60481961.47807638</t>
+          <t>60399496.40677966</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>4541875.0</t>
+          <t>3298659.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>3888772.8</v>
+        <v>3409647.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4411562.6</t>
+          <t>4333083.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>10182869.32</v>
+        <v>10178782.26</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-522789</t>
+          <t>-923435</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1469664.21937816</t>
+          <t>-1466127.300455383</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1532437.84859698</t>
+          <t>-1446674.246380107</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>4541875.0</t>
+          <t>3298659.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>79.72</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5093,7 +5093,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>77.947</t>
+          <t>182.531</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-25.48</t>
+          <t>-11.85</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-13.04</t>
+          <t>-11.96</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-2.01</v>
+        <v>-0.08</v>
       </c>
       <c r="AI12" t="n">
-        <v>-7.5</v>
+        <v>-7.33</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.67</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>26.86</v>
+        <v>26.62</v>
       </c>
       <c r="AN12" t="n">
         <v>26.79</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>25.87</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-116.96</t>
+          <t>-82.30</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.67</v>
+        <v>-0.71</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.31</v>
+        <v>-0.39</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-110.30</t>
+          <t>-112.97</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>60481961.47807638</t>
+          <t>60399496.40677966</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1903538.0</t>
+          <t>4541875.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>3963383.6</v>
+        <v>3888772.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5318222.8</t>
+          <t>4411562.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>10129541.2</v>
+        <v>10182869.32</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1354839</t>
+          <t>-522789</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1458250.832247465</t>
+          <t>-1469664.21937816</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1733429.071456906</t>
+          <t>-1532437.84859698</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1903538.0</t>
+          <t>4541875.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>79.72</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-21.02</t>
+          <t>-41.84</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-21.68</t>
+          <t>-22.54</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5635,17 +5635,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5656,66 +5656,66 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>36.67</t>
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>-0.59</v>
+        <v>-1.54</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0.33</v>
+        <v>-0.24</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-6.79</t>
+          <t>-7.00</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>13.63</t>
+          <t>13.61</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>13.68</v>
+        <v>13.64</v>
       </c>
       <c r="AN13" t="n">
-        <v>14.1</v>
+        <v>14.06</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>15.13</t>
+          <t>15.12</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>24.93</t>
+          <t>20.21</t>
         </is>
       </c>
       <c r="AQ13" t="n">
         <v>-0.17</v>
       </c>
       <c r="AR13" t="n">
-        <v>-0.23</v>
+        <v>-0.22</v>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-109.73</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5734,43 +5734,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>7282.384615384615</t>
+          <t>7272.174964438123</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>301.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>308.4</v>
+        <v>219.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>390.5</t>
+          <t>376.9</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>446.72</v>
+        <v>441.78</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-82</t>
+          <t>-157</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-26.11623977994269</t>
+          <t>-31.21747370100885</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-44.96588129094152</t>
+          <t>-59.27426026687272</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>301.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>30.11</t>
+          <t>29.78</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>90.63</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>507</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5900,22 +5900,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>13.15</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -5947,12 +5947,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5972,17 +5972,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-30.96</t>
+          <t>-21.02</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-21.10</t>
+          <t>-21.68</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6057,17 +6057,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6078,50 +6078,50 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>76.86</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>0.29</v>
+        <v>-0.59</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0.57</v>
+        <v>-0.33</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-6.79</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>13.61</t>
+          <t>13.63</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>13.69</v>
+        <v>13.68</v>
       </c>
       <c r="AN14" t="n">
-        <v>14.14</v>
+        <v>14.1</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6130,14 +6130,14 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>24.93</t>
         </is>
       </c>
       <c r="AQ14" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="AR14" t="n">
-        <v>-0.24</v>
+        <v>-0.23</v>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-110.34</t>
+          <t>-109.73</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6156,43 +6156,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>7282.384615384615</t>
+          <t>7272.174964438123</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>221.0</t>
+          <t>301.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>267.6</v>
+        <v>308.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>387.6</t>
+          <t>390.5</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>448.82</v>
+        <v>446.72</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-120</t>
+          <t>-82</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-22.68903223248835</t>
+          <t>-26.11623977994269</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-47.66941556493481</t>
+          <t>-44.96588129094152</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>221.0</t>
+          <t>301.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>30.11</t>
+          <t>29.78</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>90.63</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>507</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6332,12 +6332,12 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.15</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6394,17 +6394,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-14.07</t>
+          <t>-30.96</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-21.39</t>
+          <t>-21.10</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6479,17 +6479,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6500,66 +6500,66 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>84.64</t>
+          <t>76.86</t>
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0.91</v>
+        <v>-0.57</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>13.57</t>
+          <t>13.61</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>13.7</v>
+        <v>13.69</v>
       </c>
       <c r="AN15" t="n">
-        <v>14.17</v>
+        <v>14.14</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>15.13</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AQ15" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="AR15" t="n">
-        <v>-0.26</v>
+        <v>-0.24</v>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-110.99</t>
+          <t>-110.34</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6578,43 +6578,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>7282.384615384615</t>
+          <t>7272.174964438123</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>221.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>346.2</v>
+        <v>267.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>402.9</t>
+          <t>387.6</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>457.34</v>
+        <v>448.82</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-56</t>
+          <t>-120</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-18.14714435386173</t>
+          <t>-22.68903223248835</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-41.25769968617749</t>
+          <t>-47.66941556493481</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>221.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>30.11</t>
+          <t>29.78</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>90.63</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>507</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6744,22 +6744,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-18.88</t>
+          <t>-14.07</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-19.94</t>
+          <t>-21.39</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -6901,17 +6901,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -6922,50 +6922,50 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>86.11</t>
+          <t>84.64</t>
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>2.44</v>
+        <v>0.22</v>
       </c>
       <c r="AI16" t="n">
-        <v>-1.35</v>
+        <v>-0.91</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-6.16</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>13.52</t>
+          <t>13.57</t>
         </is>
       </c>
       <c r="AM16" t="n">
         <v>13.7</v>
       </c>
       <c r="AN16" t="n">
-        <v>14.21</v>
+        <v>14.17</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -6974,14 +6974,14 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>18.80</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AQ16" t="n">
-        <v>-0.22</v>
+        <v>-0.2</v>
       </c>
       <c r="AR16" t="n">
-        <v>-0.27</v>
+        <v>-0.26</v>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-111.58</t>
+          <t>-110.99</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7000,43 +7000,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>7282.384615384615</t>
+          <t>7272.174964438123</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>340.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>360</v>
+        <v>346.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>443.8</t>
+          <t>402.9</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>464.82</v>
+        <v>457.34</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-83</t>
+          <t>-56</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-13.94522520253159</t>
+          <t>-18.14714435386173</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-24.51747344201789</t>
+          <t>-41.25769968617749</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>340.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>30.11</t>
+          <t>29.78</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>90.63</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>507</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7166,22 +7166,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7238,17 +7238,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>-18.88</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-21.97</t>
+          <t>-19.94</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7323,17 +7323,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7344,50 +7344,50 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>75.85</t>
+          <t>86.11</t>
         </is>
       </c>
       <c r="AH17" t="n">
-        <v>0.6</v>
+        <v>2.44</v>
       </c>
       <c r="AI17" t="n">
-        <v>-2.13</v>
+        <v>-1.35</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-6.16</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>13.52</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>13.71</v>
+        <v>13.7</v>
       </c>
       <c r="AN17" t="n">
-        <v>14.24</v>
+        <v>14.21</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7396,15 +7396,15 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>18.80</t>
         </is>
       </c>
       <c r="AQ17" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="AR17" t="n">
         <v>-0.27</v>
       </c>
-      <c r="AR17" t="n">
-        <v>-0.28</v>
-      </c>
       <c r="AS17" t="inlineStr">
         <is>
           <t>2.34</t>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-112.13</t>
+          <t>-111.58</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7422,43 +7422,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>7282.384615384615</t>
+          <t>7272.174964438123</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>516.0</t>
+          <t>340.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>534.6</v>
+        <v>360</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>437.4</t>
+          <t>443.8</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>468.04</v>
+        <v>464.82</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>-83</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-12.02299824989772</t>
+          <t>-13.94522520253159</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-18.58438332743214</t>
+          <t>-24.51747344201789</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>516.0</t>
+          <t>340.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>30.11</t>
+          <t>29.78</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7563,12 +7563,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>90.63</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>507</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7588,22 +7588,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>14.05</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7635,42 +7635,42 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>13.45</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>0.74</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-1.35</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-22.25</t>
+          <t>-21.97</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7745,17 +7745,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7766,50 +7766,50 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>60.36</t>
+          <t>75.85</t>
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="AI18" t="n">
-        <v>-2.53</v>
+        <v>-2.13</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>13.42</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>13.74</v>
+        <v>13.71</v>
       </c>
       <c r="AN18" t="n">
-        <v>14.28</v>
+        <v>14.24</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -7818,15 +7818,15 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="AQ18" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="AR18" t="n">
         <v>-0.28</v>
       </c>
-      <c r="AR18" t="n">
-        <v>-0.29</v>
-      </c>
       <c r="AS18" t="inlineStr">
         <is>
           <t>2.34</t>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-112.32</t>
+          <t>-112.13</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7844,43 +7844,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>7282.384615384615</t>
+          <t>7272.174964438123</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>516.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>472.6</v>
+        <v>534.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>402.3</t>
+          <t>437.4</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>481.38</v>
+        <v>468.04</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>97</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-10.83001914489146</t>
+          <t>-12.02299824989772</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-28.30195518775838</t>
+          <t>-18.58438332743214</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>516.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -7945,7 +7945,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>30.11</t>
+          <t>29.78</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>90.63</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>507</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
@@ -8025,7 +8025,7 @@
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8047,7 +8047,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8082,17 +8082,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8167,17 +8167,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8188,63 +8188,63 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>60.36</t>
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>1.13</v>
+        <v>0.45</v>
       </c>
       <c r="AI19" t="n">
-        <v>-3.41</v>
+        <v>-2.53</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.83</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>13.77</v>
+        <v>13.74</v>
       </c>
       <c r="AN19" t="n">
-        <v>14.31</v>
+        <v>14.28</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AQ19" t="n">
-        <v>-0.3</v>
+        <v>-0.28</v>
       </c>
       <c r="AR19" t="n">
         <v>-0.29</v>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-112.36</t>
+          <t>-112.32</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8266,43 +8266,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>7282.384615384615</t>
+          <t>7272.174964438123</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>507.6</v>
+        <v>472.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>424.0</t>
+          <t>402.3</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>517.4400000000001</v>
+        <v>481.38</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-7.653303500733839</t>
+          <t>-10.83001914489146</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>3.719440554195444</t>
+          <t>-28.30195518775838</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>30.11</t>
+          <t>29.78</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8407,12 +8407,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>90.63</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>507</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8432,17 +8432,17 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8479,42 +8479,42 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>13.45</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-0.37</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>13.35</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-1.35</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-22.83</t>
+          <t>-22.25</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8589,17 +8589,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8610,50 +8610,50 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>0.6</v>
+        <v>1.13</v>
       </c>
       <c r="AI20" t="n">
-        <v>-3.84</v>
+        <v>-3.41</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>13.8</v>
+        <v>13.77</v>
       </c>
       <c r="AN20" t="n">
-        <v>14.35</v>
+        <v>14.31</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8662,11 +8662,11 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AQ20" t="n">
-        <v>-0.31</v>
+        <v>-0.3</v>
       </c>
       <c r="AR20" t="n">
         <v>-0.29</v>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-112.26</t>
+          <t>-112.36</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8688,43 +8688,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>7282.384615384615</t>
+          <t>7272.174964438123</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>459.6</v>
+        <v>507.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>420.3</t>
+          <t>424.0</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>554.86</v>
+        <v>517.4400000000001</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-9.721075147084617</t>
+          <t>-7.653303500733839</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-6.061402691377396</t>
+          <t>3.719440554195444</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-4.30</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>30.11</t>
+          <t>29.78</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8829,12 +8829,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>90.63</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>507</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -8854,22 +8854,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -8926,17 +8926,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-9.92</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9011,17 +9011,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9032,50 +9032,50 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>0.23</v>
+        <v>0.6</v>
       </c>
       <c r="AI21" t="n">
-        <v>-3.71</v>
+        <v>-3.84</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.83</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>13.83</v>
+        <v>13.8</v>
       </c>
       <c r="AN21" t="n">
-        <v>14.41</v>
+        <v>14.35</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9084,14 +9084,14 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-12.91</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="AQ21" t="n">
-        <v>-0.32</v>
+        <v>-0.31</v>
       </c>
       <c r="AR21" t="n">
-        <v>-0.28</v>
+        <v>-0.29</v>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-111.98</t>
+          <t>-112.26</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9110,43 +9110,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>7282.384615384615</t>
+          <t>7272.174964438123</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>1213.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>527.6</v>
+        <v>459.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>585.7</t>
+          <t>420.3</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>567.6799999999999</v>
+        <v>554.86</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-58</t>
+          <t>39</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-10.38647013903138</t>
+          <t>-9.721075147084617</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>21.00387133963898</t>
+          <t>-6.061402691377396</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>1213.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>30.11</t>
+          <t>29.78</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>90.63</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>507</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9348,17 +9348,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-31.65</t>
+          <t>-9.92</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9433,17 +9433,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9454,50 +9454,50 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>-0.15</v>
+        <v>0.23</v>
       </c>
       <c r="AI22" t="n">
-        <v>-3.57</v>
+        <v>-3.71</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>13.86</v>
+        <v>13.83</v>
       </c>
       <c r="AN22" t="n">
-        <v>14.48</v>
+        <v>14.41</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9506,14 +9506,14 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-16.60</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AQ22" t="n">
         <v>-0.32</v>
       </c>
       <c r="AR22" t="n">
-        <v>-0.27</v>
+        <v>-0.28</v>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-111.60</t>
+          <t>-111.98</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9532,43 +9532,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>7282.384615384615</t>
+          <t>7272.174964438123</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>1213.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>340.2</v>
+        <v>527.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>497.7</t>
+          <t>585.7</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>555.26</v>
+        <v>567.6799999999999</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-157</t>
+          <t>-58</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-16.09380495333509</t>
+          <t>-10.38647013903138</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-46.08158973532466</t>
+          <t>21.00387133963898</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>1213.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>30.11</t>
+          <t>29.78</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>90.63</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>507</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9698,17 +9698,17 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9770,17 +9770,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-48.73</t>
+          <t>-31.65</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-24.86</t>
+          <t>-22.83</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -9855,17 +9855,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -9876,50 +9876,50 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="AH23" t="n">
-        <v>-3.2</v>
+        <v>-0.15</v>
       </c>
       <c r="AI23" t="n">
-        <v>-3.38</v>
+        <v>-3.57</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>13.43</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>13.9</v>
+        <v>13.86</v>
       </c>
       <c r="AN23" t="n">
-        <v>14.55</v>
+        <v>14.48</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -9928,14 +9928,14 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-19.79</t>
+          <t>-16.60</t>
         </is>
       </c>
       <c r="AQ23" t="n">
-        <v>-0.31</v>
+        <v>-0.32</v>
       </c>
       <c r="AR23" t="n">
-        <v>-0.26</v>
+        <v>-0.27</v>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-111.11</t>
+          <t>-111.60</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -9954,43 +9954,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>7282.384615384615</t>
+          <t>7272.174964438123</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>332</v>
+        <v>340.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>647.5</t>
+          <t>497.7</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>577.0599999999999</v>
+        <v>555.26</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-315</t>
+          <t>-157</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-10.6414804475188</t>
+          <t>-16.09380495333509</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-32.37933449472541</t>
+          <t>-46.08158973532466</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-4.30</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>30.11</t>
+          <t>29.78</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>90.63</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>507</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10120,22 +10120,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
+          <t>12.9</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
           <t>13.4</t>
         </is>
       </c>
-      <c r="CE23" t="inlineStr">
-        <is>
-          <t>13.55</t>
-        </is>
-      </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10167,12 +10167,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1531.94</t>
+          <t>1461.398</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>33.85</t>
+          <t>34.05</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -10197,12 +10197,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-8.76</t>
+          <t>-8.22</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -10277,17 +10277,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -10298,66 +10298,66 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>36.79</t>
+          <t>23.86</t>
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>-0.65</v>
+        <v>-0.23</v>
       </c>
       <c r="AI24" t="n">
-        <v>-2.18</v>
+        <v>-1.59</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>34.07</t>
+          <t>34.13</t>
         </is>
       </c>
       <c r="AM24" t="n">
-        <v>34.83</v>
+        <v>34.68</v>
       </c>
       <c r="AN24" t="n">
-        <v>37.99</v>
+        <v>37.82</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>8.91</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="AQ24" t="n">
-        <v>-1</v>
+        <v>-0.96</v>
       </c>
       <c r="AR24" t="n">
-        <v>-1.1</v>
+        <v>-1.07</v>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>-130.02</t>
+          <t>-129.24</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -10376,43 +10376,43 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>231337595.1602564</t>
+          <t>231115275.2069701</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>51910714.0</t>
+          <t>50031112.0</t>
         </is>
       </c>
       <c r="AX24" t="n">
-        <v>34584994.8</v>
+        <v>38435381.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>32402375.5</t>
+          <t>34465333.5</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>168663097.68</v>
+        <v>162114795.88</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>2182619</t>
+          <t>3970048</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>-16743788.28363248</t>
+          <t>-15316628.43649505</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-9542682.305843279</t>
+          <t>-7467249.277239181</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>51910714.0</t>
+          <t>50031112.0</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -10432,7 +10432,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="BS24" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BT24" t="inlineStr">
@@ -10517,12 +10517,12 @@
       </c>
       <c r="BY24" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>79.72</t>
         </is>
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>7658</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -10542,22 +10542,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
+          <t>33.95</t>
+        </is>
+      </c>
+      <c r="CE24" t="inlineStr">
+        <is>
+          <t>34.85</t>
+        </is>
+      </c>
+      <c r="CF24" t="inlineStr">
+        <is>
+          <t>33.75</t>
+        </is>
+      </c>
+      <c r="CG24" t="inlineStr">
+        <is>
           <t>34.05</t>
-        </is>
-      </c>
-      <c r="CE24" t="inlineStr">
-        <is>
-          <t>34.15</t>
-        </is>
-      </c>
-      <c r="CF24" t="inlineStr">
-        <is>
-          <t>33.65</t>
-        </is>
-      </c>
-      <c r="CG24" t="inlineStr">
-        <is>
-          <t>33.85</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -10589,12 +10589,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>879.422</t>
+          <t>1531.94</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>34.15</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -10614,17 +10614,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-8.76</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -10699,17 +10699,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -10720,66 +10720,66 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>42.77</t>
+          <t>36.79</t>
         </is>
       </c>
       <c r="AH25" t="n">
-        <v>0.15</v>
+        <v>-0.65</v>
       </c>
       <c r="AI25" t="n">
-        <v>-2.75</v>
+        <v>-2.18</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>-8.2</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.07</t>
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>35.06</v>
+        <v>34.83</v>
       </c>
       <c r="AN25" t="n">
-        <v>38.2</v>
+        <v>37.99</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>8.91</t>
         </is>
       </c>
       <c r="AQ25" t="n">
-        <v>-1.02</v>
+        <v>-1</v>
       </c>
       <c r="AR25" t="n">
-        <v>-1.12</v>
+        <v>-1.1</v>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>-130.68</t>
+          <t>-130.02</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -10798,43 +10798,43 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>231337595.1602564</t>
+          <t>231115275.2069701</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>29976176.0</t>
+          <t>51910714.0</t>
         </is>
       </c>
       <c r="AX25" t="n">
-        <v>29647816.6</v>
+        <v>34584994.8</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>31088710.7</t>
+          <t>32402375.5</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>187517443.84</v>
+        <v>168663097.68</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>-1440894</t>
+          <t>2182619</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>-18053080.27959415</t>
+          <t>-16743788.28363248</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-12368162.47864045</t>
+          <t>-9542682.305843279</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>29976176.0</t>
+          <t>51910714.0</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="BS25" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="BT25" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="BY25" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>79.72</t>
         </is>
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>7658</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -10964,22 +10964,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>34.05</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>34.15</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>33.65</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>34.15</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -11011,12 +11011,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1072.806</t>
+          <t>879.422</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>34.15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -11036,17 +11036,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-13.85</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -11111,7 +11111,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-6.74</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -11121,17 +11121,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -11142,66 +11142,66 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>34.57</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="AH26" t="n">
-        <v>1.14</v>
+        <v>0.15</v>
       </c>
       <c r="AI26" t="n">
-        <v>-3.05</v>
+        <v>-2.75</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-8.12</t>
+          <t>-8.2</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>34.20999999999999</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="AM26" t="n">
-        <v>35.29</v>
+        <v>35.06</v>
       </c>
       <c r="AN26" t="n">
-        <v>38.41</v>
+        <v>38.2</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>37.82</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="AQ26" t="n">
-        <v>-1.06</v>
+        <v>-1.02</v>
       </c>
       <c r="AR26" t="n">
-        <v>-1.15</v>
+        <v>-1.12</v>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>-131.38</t>
+          <t>-130.68</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -11220,43 +11220,43 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>231337595.1602564</t>
+          <t>231115275.2069701</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>37113075.0</t>
+          <t>29976176.0</t>
         </is>
       </c>
       <c r="AX26" t="n">
-        <v>28180230.6</v>
+        <v>29647816.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>32709006.3</t>
+          <t>31088710.7</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>203000139.16</v>
+        <v>187517443.84</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>-4528775</t>
+          <t>-1440894</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>-19086701.69794936</t>
+          <t>-18053080.27959415</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-13612713.56554211</t>
+          <t>-12368162.47864045</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>37113075.0</t>
+          <t>29976176.0</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -11321,17 +11321,17 @@
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS26" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="BT26" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="BY26" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>79.72</t>
         </is>
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>7658</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -11386,22 +11386,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>34.15</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>680.189</t>
+          <t>1072.806</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-8.36</t>
+          <t>-6.74</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -11543,17 +11543,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -11564,66 +11564,66 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>34.57</t>
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>-0.67</v>
+        <v>1.14</v>
       </c>
       <c r="AI27" t="n">
-        <v>-3.65</v>
+        <v>-3.05</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-7.85</t>
+          <t>-8.12</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>34.20999999999999</t>
         </is>
       </c>
       <c r="AM27" t="n">
-        <v>35.52</v>
+        <v>35.29</v>
       </c>
       <c r="AN27" t="n">
-        <v>38.55</v>
+        <v>38.41</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>37.82</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="AQ27" t="n">
-        <v>-1.14</v>
+        <v>-1.06</v>
       </c>
       <c r="AR27" t="n">
-        <v>-1.17</v>
+        <v>-1.15</v>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>-131.97</t>
+          <t>-131.38</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -11642,43 +11642,43 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>231337595.1602564</t>
+          <t>231115275.2069701</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>23145831.0</t>
+          <t>37113075.0</t>
         </is>
       </c>
       <c r="AX27" t="n">
-        <v>28055340.4</v>
+        <v>28180230.6</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>32565131.1</t>
+          <t>32709006.3</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>214383272.46</v>
+        <v>203000139.16</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>-4509790</t>
+          <t>-4528775</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>-20081972.26747796</t>
+          <t>-19086701.69794936</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-15669143.09806082</t>
+          <t>-13612713.56554211</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>23145831.0</t>
+          <t>37113075.0</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -11743,17 +11743,17 @@
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS27" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BT27" t="inlineStr">
@@ -11783,12 +11783,12 @@
       </c>
       <c r="BY27" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>79.72</t>
         </is>
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>7658</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -11808,22 +11808,22 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>33.85</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>908.595</t>
+          <t>680.189</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -11880,17 +11880,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-13.85</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-9.03</t>
+          <t>-8.36</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -11965,17 +11965,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -11986,63 +11986,63 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AH28" t="n">
-        <v>-1.98</v>
+        <v>-0.67</v>
       </c>
       <c r="AI28" t="n">
-        <v>-3.48</v>
+        <v>-3.65</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-7.85</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AM28" t="n">
-        <v>35.67</v>
+        <v>35.52</v>
       </c>
       <c r="AN28" t="n">
-        <v>38.71</v>
+        <v>38.55</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>37.74</t>
+          <t>37.78</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AQ28" t="n">
-        <v>-1.17</v>
+        <v>-1.14</v>
       </c>
       <c r="AR28" t="n">
         <v>-1.17</v>
@@ -12054,7 +12054,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>-132.13</t>
+          <t>-131.97</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -12064,43 +12064,43 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>231337595.1602564</t>
+          <t>231115275.2069701</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>30779178.0</t>
+          <t>23145831.0</t>
         </is>
       </c>
       <c r="AX28" t="n">
-        <v>30495285.4</v>
+        <v>28055340.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>35145840.3</t>
+          <t>32565131.1</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>228943265.06</v>
+        <v>214383272.46</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>-4650554</t>
+          <t>-4509790</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>-20884304.84373562</t>
+          <t>-20081972.26747796</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-16550796.89101397</t>
+          <t>-15669143.09806082</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>30779178.0</t>
+          <t>23145831.0</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="BS28" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BT28" t="inlineStr">
@@ -12205,12 +12205,12 @@
       </c>
       <c r="BY28" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>79.72</t>
         </is>
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>7658</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -12230,7 +12230,7 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>797.737</t>
+          <t>908.595</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -12302,17 +12302,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-24.16</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -12377,7 +12377,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-8.36</t>
+          <t>-9.03</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -12387,17 +12387,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -12408,59 +12408,59 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>60.49</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AH29" t="n">
-        <v>-1.56</v>
+        <v>-1.98</v>
       </c>
       <c r="AI29" t="n">
-        <v>-3.54</v>
+        <v>-3.48</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-7.74</t>
+          <t>-7.84</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>34.43</t>
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>35.81</v>
+        <v>35.67</v>
       </c>
       <c r="AN29" t="n">
-        <v>38.81</v>
+        <v>38.71</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.74</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AQ29" t="n">
@@ -12476,7 +12476,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>-132.14</t>
+          <t>-132.13</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -12486,43 +12486,43 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>231337595.1602564</t>
+          <t>231115275.2069701</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>27224823.0</t>
+          <t>30779178.0</t>
         </is>
       </c>
       <c r="AX29" t="n">
-        <v>30219756.2</v>
+        <v>30495285.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>39847131.9</t>
+          <t>35145840.3</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>236001176.02</v>
+        <v>228943265.06</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>-9627375</t>
+          <t>-4650554</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>-21672215.3805941</t>
+          <t>-20884304.84373562</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>-18037061.02769653</t>
+          <t>-16550796.89101397</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>27224823.0</t>
+          <t>30779178.0</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -12587,7 +12587,7 @@
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="BS29" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="BT29" t="inlineStr">
@@ -12627,12 +12627,12 @@
       </c>
       <c r="BY29" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>79.72</t>
         </is>
       </c>
       <c r="BZ29" t="inlineStr">
         <is>
-          <t>7658</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="CA29" t="inlineStr">
@@ -12652,22 +12652,22 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -12699,12 +12699,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>652.267</t>
+          <t>797.737</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -12724,17 +12724,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-30.44</t>
+          <t>-24.16</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -12799,7 +12799,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-6.47</t>
+          <t>-8.36</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -12809,17 +12809,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -12830,66 +12830,66 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>60.49</t>
         </is>
       </c>
       <c r="AH30" t="n">
-        <v>0.67</v>
+        <v>-1.56</v>
       </c>
       <c r="AI30" t="n">
-        <v>-4.2</v>
+        <v>-3.54</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-7.74</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>34.47</t>
+          <t>34.54</t>
         </is>
       </c>
       <c r="AM30" t="n">
-        <v>35.98</v>
+        <v>35.81</v>
       </c>
       <c r="AN30" t="n">
-        <v>38.91</v>
+        <v>38.81</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>37.67</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AQ30" t="n">
         <v>-1.17</v>
       </c>
       <c r="AR30" t="n">
-        <v>-1.18</v>
+        <v>-1.17</v>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>-132.19</t>
+          <t>-132.14</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -12908,43 +12908,43 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>231337595.1602564</t>
+          <t>231115275.2069701</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>22638246.0</t>
+          <t>27224823.0</t>
         </is>
       </c>
       <c r="AX30" t="n">
-        <v>32529604.8</v>
+        <v>30219756.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>46763411.2</t>
+          <t>39847131.9</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>241442940.72</v>
+        <v>236001176.02</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>-14233806</t>
+          <t>-9627375</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>-22333152.53566639</t>
+          <t>-21672215.3805941</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>-19135291.00768245</t>
+          <t>-18037061.02769653</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>22638246.0</t>
+          <t>27224823.0</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -13009,7 +13009,7 @@
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
@@ -13019,7 +13019,7 @@
       </c>
       <c r="BS30" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BT30" t="inlineStr">
@@ -13049,12 +13049,12 @@
       </c>
       <c r="BY30" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>79.72</t>
         </is>
       </c>
       <c r="BZ30" t="inlineStr">
         <is>
-          <t>7658</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="CA30" t="inlineStr">
@@ -13079,17 +13079,17 @@
       </c>
       <c r="CE30" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -13111,7 +13111,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13121,12 +13121,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1052.554</t>
+          <t>652.267</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13146,17 +13146,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-26.38</t>
+          <t>-30.44</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -13231,17 +13231,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -13252,12 +13252,12 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -13267,48 +13267,48 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>48.28</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AH31" t="n">
-        <v>0.9</v>
+        <v>0.67</v>
       </c>
       <c r="AI31" t="n">
-        <v>-4.68</v>
+        <v>-4.2</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>34.39</t>
+          <t>34.47</t>
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>36.08</v>
+        <v>35.98</v>
       </c>
       <c r="AN31" t="n">
-        <v>38.92</v>
+        <v>38.91</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>37.67</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AQ31" t="n">
-        <v>-1.22</v>
+        <v>-1.17</v>
       </c>
       <c r="AR31" t="n">
         <v>-1.18</v>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>-132.25</t>
+          <t>-132.19</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -13330,43 +13330,43 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>231337595.1602564</t>
+          <t>231115275.2069701</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>36488624.0</t>
+          <t>22638246.0</t>
         </is>
       </c>
       <c r="AX31" t="n">
-        <v>37237782</v>
+        <v>32529604.8</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>50581063.8</t>
+          <t>46763411.2</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>242256442.44</v>
+        <v>241442940.72</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>-13343281</t>
+          <t>-14233806</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>-22914581.90439074</t>
+          <t>-22333152.53566639</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>-19529368.76453082</t>
+          <t>-19135291.00768245</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>36488624.0</t>
+          <t>22638246.0</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
@@ -13471,12 +13471,12 @@
       </c>
       <c r="BY31" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>79.72</t>
         </is>
       </c>
       <c r="BZ31" t="inlineStr">
         <is>
-          <t>7658</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="CA31" t="inlineStr">
@@ -13496,17 +13496,17 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1012.048</t>
+          <t>1052.554</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13568,17 +13568,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-30.50</t>
+          <t>-26.38</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -13643,7 +13643,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -13674,66 +13674,66 @@
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>48.21</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>48.28</t>
         </is>
       </c>
       <c r="AH32" t="n">
-        <v>1.71</v>
+        <v>0.9</v>
       </c>
       <c r="AI32" t="n">
-        <v>-4.91</v>
+        <v>-4.68</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>34.41</t>
+          <t>34.39</t>
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>36.18</v>
+        <v>36.08</v>
       </c>
       <c r="AN32" t="n">
-        <v>38.94</v>
+        <v>38.92</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>37.63</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AQ32" t="n">
-        <v>-1.28</v>
+        <v>-1.22</v>
       </c>
       <c r="AR32" t="n">
-        <v>-1.17</v>
+        <v>-1.18</v>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>-131.94</t>
+          <t>-132.25</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -13752,43 +13752,43 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>231337595.1602564</t>
+          <t>231115275.2069701</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>35345556.0</t>
+          <t>36488624.0</t>
         </is>
       </c>
       <c r="AX32" t="n">
-        <v>37074921.8</v>
+        <v>37237782</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>53345322.1</t>
+          <t>50581063.8</t>
         </is>
       </c>
       <c r="AZ32" t="n">
-        <v>245778298.12</v>
+        <v>242256442.44</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>-16270400</t>
+          <t>-13343281</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>-23530075.2025471</t>
+          <t>-22914581.90439074</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>-20878828.60415238</t>
+          <t>-19529368.76453082</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>35345556.0</t>
+          <t>36488624.0</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
@@ -13808,7 +13808,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
@@ -13853,17 +13853,17 @@
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS32" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="BT32" t="inlineStr">
@@ -13893,12 +13893,12 @@
       </c>
       <c r="BY32" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>79.72</t>
         </is>
       </c>
       <c r="BZ32" t="inlineStr">
         <is>
-          <t>7658</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="CA32" t="inlineStr">
@@ -13918,22 +13918,22 @@
       </c>
       <c r="CD32" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="CF32" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="CG32" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="CH32" t="inlineStr">
@@ -13965,12 +13965,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>857.193</t>
+          <t>1012.048</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -13990,17 +13990,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-31.65</t>
+          <t>-30.50</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-7.55</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -14075,17 +14075,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -14096,66 +14096,66 @@
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>48.21</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>10.92</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AH33" t="n">
-        <v>0.41</v>
+        <v>1.71</v>
       </c>
       <c r="AI33" t="n">
-        <v>-5.97</v>
+        <v>-4.91</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>34.16</t>
+          <t>34.41</t>
         </is>
       </c>
       <c r="AM33" t="n">
-        <v>36.33</v>
+        <v>36.18</v>
       </c>
       <c r="AN33" t="n">
-        <v>39</v>
+        <v>38.94</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>37.52</t>
+          <t>37.58</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AQ33" t="n">
-        <v>-1.36</v>
+        <v>-1.28</v>
       </c>
       <c r="AR33" t="n">
-        <v>-1.14</v>
+        <v>-1.17</v>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>-131.18</t>
+          <t>-131.94</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -14174,43 +14174,43 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>231337595.1602564</t>
+          <t>231115275.2069701</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>29401532.0</t>
+          <t>35345556.0</t>
         </is>
       </c>
       <c r="AX33" t="n">
-        <v>39796395.2</v>
+        <v>37074921.8</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>58228190.4</t>
+          <t>53345322.1</t>
         </is>
       </c>
       <c r="AZ33" t="n">
-        <v>247556548.26</v>
+        <v>245778298.12</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>-18431795</t>
+          <t>-16270400</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>-24012120.03861886</t>
+          <t>-23530075.2025471</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>-21938484.35346347</t>
+          <t>-20878828.60415238</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>29401532.0</t>
+          <t>35345556.0</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
@@ -14230,7 +14230,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -14275,7 +14275,7 @@
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR33" t="inlineStr">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
@@ -14315,12 +14315,12 @@
       </c>
       <c r="BY33" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>79.72</t>
         </is>
       </c>
       <c r="BZ33" t="inlineStr">
         <is>
-          <t>7658</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="CA33" t="inlineStr">
@@ -14340,22 +14340,22 @@
       </c>
       <c r="CD33" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="CE33" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="CF33" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="CG33" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CH33" t="inlineStr">
@@ -14387,12 +14387,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1145.3</t>
+          <t>857.193</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14402,7 +14402,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>33.65</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -14412,17 +14412,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-25.49</t>
+          <t>-31.65</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-9.30</t>
+          <t>-7.55</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -14497,17 +14497,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -14518,66 +14518,66 @@
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>10.92</t>
         </is>
       </c>
       <c r="AH34" t="n">
-        <v>-1.38</v>
+        <v>0.41</v>
       </c>
       <c r="AI34" t="n">
-        <v>-6.49</v>
+        <v>-5.97</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>34.11999999999999</t>
+          <t>34.16</t>
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>36.49</v>
+        <v>36.33</v>
       </c>
       <c r="AN34" t="n">
-        <v>39.06</v>
+        <v>39</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>37.47</t>
+          <t>37.52</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>-26.04</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="AQ34" t="n">
-        <v>-1.37</v>
+        <v>-1.36</v>
       </c>
       <c r="AR34" t="n">
-        <v>-1.08</v>
+        <v>-1.14</v>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>-129.70</t>
+          <t>-131.18</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -14596,43 +14596,43 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>231337595.1602564</t>
+          <t>231115275.2069701</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>38774066.0</t>
+          <t>29401532.0</t>
         </is>
       </c>
       <c r="AX34" t="n">
-        <v>49474507.6</v>
+        <v>39796395.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>66401056.1</t>
+          <t>58228190.4</t>
         </is>
       </c>
       <c r="AZ34" t="n">
-        <v>249662887.18</v>
+        <v>247556548.26</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>-16926548</t>
+          <t>-18431795</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>-24389144.70864711</t>
+          <t>-24012120.03861886</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>-22031901.26842704</t>
+          <t>-21938484.35346347</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>38774066.0</t>
+          <t>29401532.0</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
@@ -14697,7 +14697,7 @@
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
@@ -14707,7 +14707,7 @@
       </c>
       <c r="BS34" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="BT34" t="inlineStr">
@@ -14737,12 +14737,12 @@
       </c>
       <c r="BY34" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>79.72</t>
         </is>
       </c>
       <c r="BZ34" t="inlineStr">
         <is>
-          <t>7658</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="CA34" t="inlineStr">
@@ -14762,22 +14762,22 @@
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="CE34" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.55</t>
         </is>
       </c>
       <c r="CF34" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="CG34" t="inlineStr">
         <is>
-          <t>33.65</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CH34" t="inlineStr">

--- a/Result/checksun_type/玻璃基板.xlsx
+++ b/Result/checksun_type/玻璃基板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>54.328</t>
+          <t>96.446</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>-21.13</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,61 +1019,61 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>70.97</t>
+          <t>58.06</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>78.69</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.96</v>
+        <v>-1.23</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>25.55</v>
+        <v>25.48</v>
       </c>
       <c r="AN2" t="n">
-        <v>26.69</v>
+        <v>26.66</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.12</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.24</v>
+        <v>-0.23</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.4</v>
+        <v>-0.37</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-113.41</t>
+          <t>-112.24</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>60399496.40677966</t>
+          <t>60319552.09379408</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1397794.0</t>
+          <t>2479319.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>4118812.4</v>
+        <v>2480098.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3226619.3</t>
+          <t>3144685.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>8922557.08</v>
+        <v>8888278.16</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>892193</t>
+          <t>-664586</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-962371.2123215774</t>
+          <t>-928471.7242719883</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-790541.3111435147</t>
+          <t>-742024.5399992489</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1397794.0</t>
+          <t>2479319.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>79.72</t>
+          <t>80.08</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>25.85</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
           <t>26.0</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>31.793</t>
+          <t>54.328</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>23.03</t>
+          <t>27.65</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.50</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1441,61 +1441,61 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>74.19</t>
+          <t>70.97</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>88.37</t>
+          <t>78.69</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-0.15</v>
+        <v>-0.96</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.32</v>
+        <v>2.14</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>25.6</v>
+        <v>25.55</v>
       </c>
       <c r="AN3" t="n">
-        <v>26.71</v>
+        <v>26.69</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>38.28</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.28</v>
+        <v>-0.24</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.45</v>
+        <v>-0.4</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-114.77</t>
+          <t>-113.41</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>60399496.40677966</t>
+          <t>60319552.09379408</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>821520.0</t>
+          <t>1397794.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>4356438.6</v>
+        <v>4118812.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3541027.4</t>
+          <t>3226619.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>9017458.68</v>
+        <v>8922557.08</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>815411</t>
+          <t>892193</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-993613.0125357707</t>
+          <t>-962371.2123215774</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-715739.6873801965</t>
+          <t>-790541.3111435147</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>821520.0</t>
+          <t>1397794.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>79.72</t>
+          <t>80.08</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>96.636</t>
+          <t>31.793</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>22.72</t>
+          <t>23.03</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>-7.50</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1863,61 +1863,61 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>74.19</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>88.37</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>1.71</v>
+        <v>-0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.29</v>
+        <v>1.32</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>25.64</v>
+        <v>25.6</v>
       </c>
       <c r="AN4" t="n">
-        <v>26.74</v>
+        <v>26.71</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>26.04</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>34.57</t>
+          <t>38.28</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.32</v>
+        <v>-0.28</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.49</v>
+        <v>-0.45</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-116.18</t>
+          <t>-114.77</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>60399496.40677966</t>
+          <t>60319552.09379408</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2494335.0</t>
+          <t>821520.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>4478414</v>
+        <v>4356438.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3649229.2</t>
+          <t>3541027.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>9357524.42</v>
+        <v>9017458.68</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>829184</t>
+          <t>815411</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1044135.43529133</t>
+          <t>-993613.0125357707</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-521574.4503118787</t>
+          <t>-715739.6873801965</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2494335.0</t>
+          <t>821520.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,12 +2037,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>79.72</t>
+          <t>80.08</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>195.468</t>
+          <t>96.636</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>22.72</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.20</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2285,61 +2285,61 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>3.02</v>
+        <v>1.71</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.67</v>
+        <v>0.29</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>25.7</v>
+        <v>25.64</v>
       </c>
       <c r="AN5" t="n">
-        <v>26.79</v>
+        <v>26.74</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>26.04</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>25.17</t>
+          <t>34.57</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.4</v>
+        <v>-0.32</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.53</v>
+        <v>-0.49</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-117.58</t>
+          <t>-116.18</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>60399496.40677966</t>
+          <t>60319552.09379408</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>5207526.0</t>
+          <t>2494335.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>4629628.2</v>
+        <v>4478414</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3696072.6</t>
+          <t>3649229.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>10084690.88</v>
+        <v>9357524.42</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>933555</t>
+          <t>829184</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1139146.523469412</t>
+          <t>-1044135.43529133</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-404798.0598460007</t>
+          <t>-521574.4503118787</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>5207526.0</t>
+          <t>2494335.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,17 +2459,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>79.72</t>
+          <t>80.08</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
+          <t>25.4</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>26.15</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>26.3</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>405.481</t>
+          <t>195.468</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>7.20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2717,51 +2717,51 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>4.12</v>
+        <v>3.02</v>
       </c>
       <c r="AI6" t="n">
-        <v>-1.9</v>
+        <v>-0.67</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>25.53</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>25.75</v>
+        <v>25.7</v>
       </c>
       <c r="AN6" t="n">
         <v>26.79</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>25.99</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>25.17</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.51</v>
+        <v>-0.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.53</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-118.68</t>
+          <t>-117.58</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>60399496.40677966</t>
+          <t>60319552.09379408</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>10672887.0</t>
+          <t>5207526.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3809271.8</v>
+        <v>4629628.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3609459.7</t>
+          <t>3696072.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>10245696.52</v>
+        <v>10084690.88</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>199812</t>
+          <t>933555</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1272664.425946395</t>
+          <t>-1139146.523469412</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-514216.6070431024</t>
+          <t>-404798.0598460007</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>10672887.0</t>
+          <t>5207526.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2881,12 +2881,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>79.72</t>
+          <t>80.08</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,17 +2946,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>27.05</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>103.242</t>
+          <t>405.481</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-24.98</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-10.54</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3129,61 +3129,61 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.28</v>
+        <v>4.12</v>
       </c>
       <c r="AI7" t="n">
-        <v>-3.11</v>
+        <v>-1.9</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>25.78</v>
+        <v>25.75</v>
       </c>
       <c r="AN7" t="n">
-        <v>26.78</v>
+        <v>26.79</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>25.96</t>
+          <t>25.99</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-10.00</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.64</v>
+        <v>-0.51</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.58</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-119.17</t>
+          <t>-118.68</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>60399496.40677966</t>
+          <t>60319552.09379408</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2585925.0</t>
+          <t>10672887.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>2334426.2</v>
+        <v>3809271.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3111599.5</t>
+          <t>3609459.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>10171307.16</v>
+        <v>10245696.52</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-777173</t>
+          <t>199812</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1410564.029383358</t>
+          <t>-1272664.425946395</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1237738.331358852</t>
+          <t>-514216.6070431024</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2585925.0</t>
+          <t>10672887.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,17 +3303,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>79.72</t>
+          <t>80.08</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>27.05</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>57.864</t>
+          <t>103.242</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-24.98</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-11.61</t>
+          <t>-10.54</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3551,61 +3551,61 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>50.45</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-0.6</v>
+        <v>0.28</v>
       </c>
       <c r="AI8" t="n">
-        <v>-3.79</v>
+        <v>-3.11</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>25.88</v>
+        <v>25.78</v>
       </c>
       <c r="AN8" t="n">
         <v>26.78</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>25.96</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-18.27</t>
+          <t>-10.00</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.67</v>
+        <v>-0.64</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.58</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-118.69</t>
+          <t>-119.17</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>60399496.40677966</t>
+          <t>60319552.09379408</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1431397.0</t>
+          <t>2585925.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>2725616.2</v>
+        <v>2334426.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3344499.9</t>
+          <t>3111599.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>10170725.72</v>
+        <v>10171307.16</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-618883</t>
+          <t>-777173</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1441986.883569631</t>
+          <t>-1410564.029383358</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1360675.639975678</t>
+          <t>-1237738.331358852</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1431397.0</t>
+          <t>2585925.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>79.72</t>
+          <t>80.08</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>129.907</t>
+          <t>57.864</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-9.82</t>
+          <t>-11.61</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3973,61 +3973,61 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>50.45</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>1.73</v>
+        <v>-0.6</v>
       </c>
       <c r="AI9" t="n">
-        <v>-4.69</v>
+        <v>-3.79</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>26.04</v>
+        <v>25.88</v>
       </c>
       <c r="AN9" t="n">
-        <v>26.79</v>
+        <v>26.78</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>25.92</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-23.75</t>
+          <t>-18.27</t>
         </is>
       </c>
       <c r="AQ9" t="n">
         <v>-0.67</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.54</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-117.83</t>
+          <t>-118.69</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>60399496.40677966</t>
+          <t>60319552.09379408</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3250406.0</t>
+          <t>1431397.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>2820044.4</v>
+        <v>2725616.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>3938171.4</t>
+          <t>3344499.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>10185422.26</v>
+        <v>10170725.72</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1118127</t>
+          <t>-618883</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1456770.746041259</t>
+          <t>-1441986.883569631</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1364005.379429155</t>
+          <t>-1360675.639975678</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>3250406.0</t>
+          <t>1431397.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>79.72</t>
+          <t>80.08</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.221</t>
+          <t>129.907</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-32.35</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-10.89</t>
+          <t>-9.82</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4395,61 +4395,61 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>1.09</v>
+        <v>1.73</v>
       </c>
       <c r="AI10" t="n">
-        <v>-5.71</v>
+        <v>-4.69</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>26.18</v>
+        <v>26.04</v>
       </c>
       <c r="AN10" t="n">
-        <v>26.78</v>
+        <v>26.79</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-39.44</t>
+          <t>-23.75</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.71</v>
+        <v>-0.67</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.51</v>
+        <v>-0.54</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-116.78</t>
+          <t>-117.83</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>60399496.40677966</t>
+          <t>60319552.09379408</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1105744.0</t>
+          <t>3250406.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>2762517</v>
+        <v>2820044.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4083544.5</t>
+          <t>3938171.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>10163096.92</v>
+        <v>10185422.26</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1321027</t>
+          <t>-1118127</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1473637.176334369</t>
+          <t>-1456770.746041259</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1514941.493668794</t>
+          <t>-1364005.379429155</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1105744.0</t>
+          <t>3250406.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>79.72</t>
+          <t>80.08</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>132.605</t>
+          <t>44.221</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-21.31</t>
+          <t>-32.35</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-11.07</t>
+          <t>-10.89</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -4817,61 +4817,61 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.48</v>
+        <v>1.09</v>
       </c>
       <c r="AI11" t="n">
-        <v>-6.05</v>
+        <v>-5.71</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>24.68</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>26.38</v>
+        <v>26.18</v>
       </c>
       <c r="AN11" t="n">
         <v>26.78</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-56.92</t>
+          <t>-39.44</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.72</v>
+        <v>-0.71</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.46</v>
+        <v>-0.51</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-115.12</t>
+          <t>-116.78</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>60399496.40677966</t>
+          <t>60319552.09379408</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3298659.0</t>
+          <t>1105744.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>3409647.6</v>
+        <v>2762517</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4333083.4</t>
+          <t>4083544.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>10178782.26</v>
+        <v>10163096.92</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-923435</t>
+          <t>-1321027</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1466127.300455383</t>
+          <t>-1473637.176334369</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1446674.246380107</t>
+          <t>-1514941.493668794</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>3298659.0</t>
+          <t>1105744.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>79.72</t>
+          <t>80.08</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>182.531</t>
+          <t>132.605</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-11.85</t>
+          <t>-21.31</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-11.96</t>
+          <t>-11.07</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5239,61 +5239,61 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-0.08</v>
+        <v>0.48</v>
       </c>
       <c r="AI12" t="n">
-        <v>-7.33</v>
+        <v>-6.05</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>24.78</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>26.62</v>
+        <v>26.38</v>
       </c>
       <c r="AN12" t="n">
-        <v>26.79</v>
+        <v>26.78</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-82.30</t>
+          <t>-56.92</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.71</v>
+        <v>-0.72</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.39</v>
+        <v>-0.46</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-112.97</t>
+          <t>-115.12</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>60399496.40677966</t>
+          <t>60319552.09379408</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>4541875.0</t>
+          <t>3298659.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>3888772.8</v>
+        <v>3409647.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4411562.6</t>
+          <t>4333083.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>10182869.32</v>
+        <v>10178782.26</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-522789</t>
+          <t>-923435</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1469664.21937816</t>
+          <t>-1466127.300455383</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1532437.84859698</t>
+          <t>-1446674.246380107</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>4541875.0</t>
+          <t>3298659.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>79.72</t>
+          <t>80.08</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-41.84</t>
+          <t>-29.87</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-22.54</t>
+          <t>-21.10</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5635,17 +5635,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5656,66 +5656,66 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>36.67</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>-1.54</v>
+        <v>0.59</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0.24</v>
+        <v>-0.29</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-7.00</t>
+          <t>-7.13</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>13.61</t>
+          <t>13.57</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>13.64</v>
+        <v>13.61</v>
       </c>
       <c r="AN13" t="n">
-        <v>14.06</v>
+        <v>14.03</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>15.12</t>
+          <t>15.11</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>20.21</t>
+          <t>25.17</t>
         </is>
       </c>
       <c r="AQ13" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="AR13" t="n">
-        <v>-0.22</v>
+        <v>-0.2</v>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-108.72</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5734,43 +5734,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>7272.174964438123</t>
+          <t>7262.305397727273</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>216.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>219.2</v>
+        <v>194.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>376.9</t>
+          <t>277.2</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>441.78</v>
+        <v>433.04</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-157</t>
+          <t>-82</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-31.21747370100885</t>
+          <t>-35.16221144598483</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-59.27426026687272</t>
+          <t>-56.85826904335272</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>216.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>29.78</t>
+          <t>30.33</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>90.63</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>517</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5895,27 +5895,27 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -5947,12 +5947,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-21.02</t>
+          <t>-41.84</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-21.68</t>
+          <t>-22.54</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6057,17 +6057,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6078,66 +6078,66 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>36.67</t>
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>-0.59</v>
+        <v>-1.54</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0.33</v>
+        <v>-0.24</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-6.79</t>
+          <t>-7.00</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>13.63</t>
+          <t>13.61</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>13.68</v>
+        <v>13.64</v>
       </c>
       <c r="AN14" t="n">
-        <v>14.1</v>
+        <v>14.06</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>15.13</t>
+          <t>15.12</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>24.93</t>
+          <t>20.21</t>
         </is>
       </c>
       <c r="AQ14" t="n">
         <v>-0.17</v>
       </c>
       <c r="AR14" t="n">
-        <v>-0.23</v>
+        <v>-0.22</v>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-109.73</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6156,43 +6156,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>7272.174964438123</t>
+          <t>7262.305397727273</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>301.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>308.4</v>
+        <v>219.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>390.5</t>
+          <t>376.9</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>446.72</v>
+        <v>441.78</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-82</t>
+          <t>-157</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-26.11623977994269</t>
+          <t>-31.21747370100885</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-44.96588129094152</t>
+          <t>-59.27426026687272</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>301.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>29.78</t>
+          <t>30.33</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>90.63</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>517</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6317,27 +6317,27 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>13.15</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-30.96</t>
+          <t>-21.02</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-21.10</t>
+          <t>-21.68</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6479,17 +6479,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6500,50 +6500,50 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>76.86</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>0.29</v>
+        <v>-0.59</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0.57</v>
+        <v>-0.33</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-6.79</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>13.61</t>
+          <t>13.63</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>13.69</v>
+        <v>13.68</v>
       </c>
       <c r="AN15" t="n">
-        <v>14.14</v>
+        <v>14.1</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6552,14 +6552,14 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>24.93</t>
         </is>
       </c>
       <c r="AQ15" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="AR15" t="n">
-        <v>-0.24</v>
+        <v>-0.23</v>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-110.34</t>
+          <t>-109.73</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6578,43 +6578,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>7272.174964438123</t>
+          <t>7262.305397727273</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>221.0</t>
+          <t>301.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>267.6</v>
+        <v>308.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>387.6</t>
+          <t>390.5</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>448.82</v>
+        <v>446.72</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-120</t>
+          <t>-82</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-22.68903223248835</t>
+          <t>-26.11623977994269</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-47.66941556493481</t>
+          <t>-44.96588129094152</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>221.0</t>
+          <t>301.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>29.78</t>
+          <t>30.33</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>90.63</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>517</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.15</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-14.07</t>
+          <t>-30.96</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-21.39</t>
+          <t>-21.10</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -6901,17 +6901,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -6922,66 +6922,66 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>84.64</t>
+          <t>76.86</t>
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="AI16" t="n">
-        <v>-0.91</v>
+        <v>-0.57</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>13.57</t>
+          <t>13.61</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>13.7</v>
+        <v>13.69</v>
       </c>
       <c r="AN16" t="n">
-        <v>14.17</v>
+        <v>14.14</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>15.13</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AQ16" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="AR16" t="n">
-        <v>-0.26</v>
+        <v>-0.24</v>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-110.99</t>
+          <t>-110.34</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7000,43 +7000,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>7272.174964438123</t>
+          <t>7262.305397727273</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>221.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>346.2</v>
+        <v>267.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>402.9</t>
+          <t>387.6</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>457.34</v>
+        <v>448.82</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-56</t>
+          <t>-120</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-18.14714435386173</t>
+          <t>-22.68903223248835</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-41.25769968617749</t>
+          <t>-47.66941556493481</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>221.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>29.78</t>
+          <t>30.33</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>90.63</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>517</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7161,27 +7161,27 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-18.88</t>
+          <t>-14.07</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-19.94</t>
+          <t>-21.39</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7323,17 +7323,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7344,50 +7344,50 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>86.11</t>
+          <t>84.64</t>
         </is>
       </c>
       <c r="AH17" t="n">
-        <v>2.44</v>
+        <v>0.22</v>
       </c>
       <c r="AI17" t="n">
-        <v>-1.35</v>
+        <v>-0.91</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-6.16</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>13.52</t>
+          <t>13.57</t>
         </is>
       </c>
       <c r="AM17" t="n">
         <v>13.7</v>
       </c>
       <c r="AN17" t="n">
-        <v>14.21</v>
+        <v>14.17</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7396,14 +7396,14 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>18.80</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AQ17" t="n">
-        <v>-0.22</v>
+        <v>-0.2</v>
       </c>
       <c r="AR17" t="n">
-        <v>-0.27</v>
+        <v>-0.26</v>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-111.58</t>
+          <t>-110.99</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7422,43 +7422,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>7272.174964438123</t>
+          <t>7262.305397727273</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>340.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>360</v>
+        <v>346.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>443.8</t>
+          <t>402.9</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>464.82</v>
+        <v>457.34</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-83</t>
+          <t>-56</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-13.94522520253159</t>
+          <t>-18.14714435386173</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-24.51747344201789</t>
+          <t>-41.25769968617749</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>340.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>29.78</t>
+          <t>30.33</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7563,12 +7563,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>90.63</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>517</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7583,27 +7583,27 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>-18.88</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-21.97</t>
+          <t>-19.94</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7745,17 +7745,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7766,50 +7766,50 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>75.85</t>
+          <t>86.11</t>
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>0.6</v>
+        <v>2.44</v>
       </c>
       <c r="AI18" t="n">
-        <v>-2.13</v>
+        <v>-1.35</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-6.16</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>13.52</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>13.71</v>
+        <v>13.7</v>
       </c>
       <c r="AN18" t="n">
-        <v>14.24</v>
+        <v>14.21</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -7818,15 +7818,15 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>18.80</t>
         </is>
       </c>
       <c r="AQ18" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="AR18" t="n">
         <v>-0.27</v>
       </c>
-      <c r="AR18" t="n">
-        <v>-0.28</v>
-      </c>
       <c r="AS18" t="inlineStr">
         <is>
           <t>2.34</t>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-112.13</t>
+          <t>-111.58</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7844,43 +7844,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>7272.174964438123</t>
+          <t>7262.305397727273</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>516.0</t>
+          <t>340.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>534.6</v>
+        <v>360</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>437.4</t>
+          <t>443.8</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>468.04</v>
+        <v>464.82</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>-83</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-12.02299824989772</t>
+          <t>-13.94522520253159</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-18.58438332743214</t>
+          <t>-24.51747344201789</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>516.0</t>
+          <t>340.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -7945,7 +7945,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>29.78</t>
+          <t>30.33</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>90.63</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>517</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8005,27 +8005,27 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>14.05</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8057,42 +8057,42 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>13.45</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>-0.37</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8102,7 +8102,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-22.25</t>
+          <t>-21.97</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8167,17 +8167,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8188,50 +8188,50 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>60.36</t>
+          <t>75.85</t>
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="AI19" t="n">
-        <v>-2.53</v>
+        <v>-2.13</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>13.42</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>13.74</v>
+        <v>13.71</v>
       </c>
       <c r="AN19" t="n">
-        <v>14.28</v>
+        <v>14.24</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8240,15 +8240,15 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="AQ19" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="AR19" t="n">
         <v>-0.28</v>
       </c>
-      <c r="AR19" t="n">
-        <v>-0.29</v>
-      </c>
       <c r="AS19" t="inlineStr">
         <is>
           <t>2.34</t>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-112.32</t>
+          <t>-112.13</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8266,43 +8266,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>7272.174964438123</t>
+          <t>7262.305397727273</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>516.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>472.6</v>
+        <v>534.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>402.3</t>
+          <t>437.4</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>481.38</v>
+        <v>468.04</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>97</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-10.83001914489146</t>
+          <t>-12.02299824989772</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-28.30195518775838</t>
+          <t>-18.58438332743214</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>516.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8377,7 +8377,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>29.78</t>
+          <t>30.33</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8407,12 +8407,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>90.63</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>517</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8469,7 +8469,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8479,12 +8479,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8589,17 +8589,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8610,63 +8610,63 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>60.36</t>
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>1.13</v>
+        <v>0.45</v>
       </c>
       <c r="AI20" t="n">
-        <v>-3.41</v>
+        <v>-2.53</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.83</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>13.77</v>
+        <v>13.74</v>
       </c>
       <c r="AN20" t="n">
-        <v>14.31</v>
+        <v>14.28</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AQ20" t="n">
-        <v>-0.3</v>
+        <v>-0.28</v>
       </c>
       <c r="AR20" t="n">
         <v>-0.29</v>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-112.36</t>
+          <t>-112.32</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8688,43 +8688,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>7272.174964438123</t>
+          <t>7262.305397727273</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>507.6</v>
+        <v>472.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>424.0</t>
+          <t>402.3</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>517.4400000000001</v>
+        <v>481.38</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-7.653303500733839</t>
+          <t>-10.83001914489146</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>3.719440554195444</t>
+          <t>-28.30195518775838</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>29.78</t>
+          <t>30.33</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8829,12 +8829,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>90.63</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>517</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -8849,22 +8849,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -8901,42 +8901,42 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>13.45</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>13.35</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -8946,7 +8946,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-22.83</t>
+          <t>-22.25</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9011,17 +9011,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9032,50 +9032,50 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>0.6</v>
+        <v>1.13</v>
       </c>
       <c r="AI21" t="n">
-        <v>-3.84</v>
+        <v>-3.41</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>13.8</v>
+        <v>13.77</v>
       </c>
       <c r="AN21" t="n">
-        <v>14.35</v>
+        <v>14.31</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9084,11 +9084,11 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AQ21" t="n">
-        <v>-0.31</v>
+        <v>-0.3</v>
       </c>
       <c r="AR21" t="n">
         <v>-0.29</v>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-112.26</t>
+          <t>-112.36</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9110,43 +9110,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>7272.174964438123</t>
+          <t>7262.305397727273</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>459.6</v>
+        <v>507.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>420.3</t>
+          <t>424.0</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>554.86</v>
+        <v>517.4400000000001</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-9.721075147084617</t>
+          <t>-7.653303500733839</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-6.061402691377396</t>
+          <t>3.719440554195444</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-4.30</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>29.78</t>
+          <t>30.33</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>90.63</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>517</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9271,27 +9271,27 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9358,7 +9358,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-9.92</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9433,17 +9433,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9454,50 +9454,50 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>0.23</v>
+        <v>0.6</v>
       </c>
       <c r="AI22" t="n">
-        <v>-3.71</v>
+        <v>-3.84</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.83</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>13.83</v>
+        <v>13.8</v>
       </c>
       <c r="AN22" t="n">
-        <v>14.41</v>
+        <v>14.35</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9506,14 +9506,14 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-12.91</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="AQ22" t="n">
-        <v>-0.32</v>
+        <v>-0.31</v>
       </c>
       <c r="AR22" t="n">
-        <v>-0.28</v>
+        <v>-0.29</v>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-111.98</t>
+          <t>-112.26</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9532,43 +9532,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>7272.174964438123</t>
+          <t>7262.305397727273</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>1213.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>527.6</v>
+        <v>459.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>585.7</t>
+          <t>420.3</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>567.6799999999999</v>
+        <v>554.86</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-58</t>
+          <t>39</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-10.38647013903138</t>
+          <t>-9.721075147084617</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>21.00387133963898</t>
+          <t>-6.061402691377396</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>1213.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>29.78</t>
+          <t>30.33</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>90.63</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>517</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9693,12 +9693,12 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-31.65</t>
+          <t>-9.92</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -9855,17 +9855,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -9876,50 +9876,50 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="AH23" t="n">
-        <v>-0.15</v>
+        <v>0.23</v>
       </c>
       <c r="AI23" t="n">
-        <v>-3.57</v>
+        <v>-3.71</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>13.86</v>
+        <v>13.83</v>
       </c>
       <c r="AN23" t="n">
-        <v>14.48</v>
+        <v>14.41</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -9928,14 +9928,14 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-16.60</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AQ23" t="n">
         <v>-0.32</v>
       </c>
       <c r="AR23" t="n">
-        <v>-0.27</v>
+        <v>-0.28</v>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-111.60</t>
+          <t>-111.98</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -9954,43 +9954,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>7272.174964438123</t>
+          <t>7262.305397727273</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>1213.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>340.2</v>
+        <v>527.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>497.7</t>
+          <t>585.7</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>555.26</v>
+        <v>567.6799999999999</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-157</t>
+          <t>-58</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-16.09380495333509</t>
+          <t>-10.38647013903138</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-46.08158973532466</t>
+          <t>21.00387133963898</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>1213.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>29.78</t>
+          <t>30.33</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>90.63</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>517</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10115,22 +10115,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
@@ -10167,12 +10167,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1461.398</t>
+          <t>1354.825</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>34.05</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -10197,12 +10197,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-8.22</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -10277,17 +10277,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -10298,66 +10298,66 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>23.86</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>-0.23</v>
+        <v>-1.79</v>
       </c>
       <c r="AI24" t="n">
-        <v>-1.59</v>
+        <v>-1.33</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>34.13</t>
+          <t>34.01000000000001</t>
         </is>
       </c>
       <c r="AM24" t="n">
-        <v>34.68</v>
+        <v>34.47</v>
       </c>
       <c r="AN24" t="n">
-        <v>37.82</v>
+        <v>37.64</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>37.92</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AQ24" t="n">
         <v>-0.96</v>
       </c>
       <c r="AR24" t="n">
-        <v>-1.07</v>
+        <v>-1.05</v>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>-129.24</t>
+          <t>-128.67</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -10376,43 +10376,43 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>231115275.2069701</t>
+          <t>230884472.3927557</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>50031112.0</t>
+          <t>45753396.0</t>
         </is>
       </c>
       <c r="AX24" t="n">
-        <v>38435381.6</v>
+        <v>42956894.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>34465333.5</t>
+          <t>35506117.5</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>162114795.88</v>
+        <v>158785914.18</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>3970048</t>
+          <t>7450777</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>-15316628.43649505</t>
+          <t>-13906161.54246278</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-7467249.277239181</t>
+          <t>-6148593.625285327</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>50031112.0</t>
+          <t>45753396.0</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -10432,7 +10432,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -10457,7 +10457,7 @@
       </c>
       <c r="BM24" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN24" t="inlineStr">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="BS24" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="BT24" t="inlineStr">
@@ -10517,12 +10517,12 @@
       </c>
       <c r="BY24" t="inlineStr">
         <is>
-          <t>79.72</t>
+          <t>80.08</t>
         </is>
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -10542,22 +10542,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>34.05</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -10589,12 +10589,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1531.94</t>
+          <t>1461.398</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>33.85</t>
+          <t>34.05</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -10614,17 +10614,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-8.76</t>
+          <t>-8.22</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -10699,17 +10699,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -10720,66 +10720,66 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>36.79</t>
+          <t>23.86</t>
         </is>
       </c>
       <c r="AH25" t="n">
-        <v>-0.65</v>
+        <v>-0.23</v>
       </c>
       <c r="AI25" t="n">
-        <v>-2.18</v>
+        <v>-1.59</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>34.07</t>
+          <t>34.13</t>
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>34.83</v>
+        <v>34.68</v>
       </c>
       <c r="AN25" t="n">
-        <v>37.99</v>
+        <v>37.82</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>8.91</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="AQ25" t="n">
-        <v>-1</v>
+        <v>-0.96</v>
       </c>
       <c r="AR25" t="n">
-        <v>-1.1</v>
+        <v>-1.07</v>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>-130.02</t>
+          <t>-129.24</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -10798,43 +10798,43 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>231115275.2069701</t>
+          <t>230884472.3927557</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>51910714.0</t>
+          <t>50031112.0</t>
         </is>
       </c>
       <c r="AX25" t="n">
-        <v>34584994.8</v>
+        <v>38435381.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>32402375.5</t>
+          <t>34465333.5</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>168663097.68</v>
+        <v>162114795.88</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>2182619</t>
+          <t>3970048</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>-16743788.28363248</t>
+          <t>-15316628.43649505</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-9542682.305843279</t>
+          <t>-7467249.277239181</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>51910714.0</t>
+          <t>50031112.0</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
@@ -10879,7 +10879,7 @@
       </c>
       <c r="BM25" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN25" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="BS25" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BT25" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="BY25" t="inlineStr">
         <is>
-          <t>79.72</t>
+          <t>80.08</t>
         </is>
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -10964,22 +10964,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
+          <t>33.95</t>
+        </is>
+      </c>
+      <c r="CE25" t="inlineStr">
+        <is>
+          <t>34.85</t>
+        </is>
+      </c>
+      <c r="CF25" t="inlineStr">
+        <is>
+          <t>33.75</t>
+        </is>
+      </c>
+      <c r="CG25" t="inlineStr">
+        <is>
           <t>34.05</t>
-        </is>
-      </c>
-      <c r="CE25" t="inlineStr">
-        <is>
-          <t>34.15</t>
-        </is>
-      </c>
-      <c r="CF25" t="inlineStr">
-        <is>
-          <t>33.65</t>
-        </is>
-      </c>
-      <c r="CG25" t="inlineStr">
-        <is>
-          <t>33.85</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -11011,12 +11011,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>879.422</t>
+          <t>1531.94</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>34.15</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -11036,102 +11036,102 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
+          <t>-1.35</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>6.74</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>37.7</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>37.1</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>41.9</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>42.55</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>-8.76</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>-11.40</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
           <t>-0.29</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>-4.63</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>37.7</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>37.1</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>42.55</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>-7.95</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>-11.40</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>-1.16</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -11142,66 +11142,66 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>42.77</t>
+          <t>36.79</t>
         </is>
       </c>
       <c r="AH26" t="n">
-        <v>0.15</v>
+        <v>-0.65</v>
       </c>
       <c r="AI26" t="n">
-        <v>-2.75</v>
+        <v>-2.18</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-8.2</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.07</t>
         </is>
       </c>
       <c r="AM26" t="n">
-        <v>35.06</v>
+        <v>34.83</v>
       </c>
       <c r="AN26" t="n">
-        <v>38.2</v>
+        <v>37.99</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>8.91</t>
         </is>
       </c>
       <c r="AQ26" t="n">
-        <v>-1.02</v>
+        <v>-1</v>
       </c>
       <c r="AR26" t="n">
-        <v>-1.12</v>
+        <v>-1.1</v>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>-130.68</t>
+          <t>-130.02</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -11220,43 +11220,43 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>231115275.2069701</t>
+          <t>230884472.3927557</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>29976176.0</t>
+          <t>51910714.0</t>
         </is>
       </c>
       <c r="AX26" t="n">
-        <v>29647816.6</v>
+        <v>34584994.8</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>31088710.7</t>
+          <t>32402375.5</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>187517443.84</v>
+        <v>168663097.68</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>-1440894</t>
+          <t>2182619</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>-18053080.27959415</t>
+          <t>-16743788.28363248</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-12368162.47864045</t>
+          <t>-9542682.305843279</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>29976176.0</t>
+          <t>51910714.0</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="BM26" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN26" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -11331,7 +11331,7 @@
       </c>
       <c r="BS26" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="BT26" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="BY26" t="inlineStr">
         <is>
-          <t>79.72</t>
+          <t>80.08</t>
         </is>
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -11386,22 +11386,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>34.05</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>34.15</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>33.65</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>34.15</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1072.806</t>
+          <t>879.422</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>34.15</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11458,17 +11458,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-13.85</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-6.74</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -11543,17 +11543,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -11564,66 +11564,66 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>34.57</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>1.14</v>
+        <v>0.15</v>
       </c>
       <c r="AI27" t="n">
-        <v>-3.05</v>
+        <v>-2.75</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-8.12</t>
+          <t>-8.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>34.20999999999999</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="AM27" t="n">
-        <v>35.29</v>
+        <v>35.06</v>
       </c>
       <c r="AN27" t="n">
-        <v>38.41</v>
+        <v>38.2</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>37.82</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="AQ27" t="n">
-        <v>-1.06</v>
+        <v>-1.02</v>
       </c>
       <c r="AR27" t="n">
-        <v>-1.15</v>
+        <v>-1.12</v>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>-131.38</t>
+          <t>-130.68</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -11642,43 +11642,43 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>231115275.2069701</t>
+          <t>230884472.3927557</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>37113075.0</t>
+          <t>29976176.0</t>
         </is>
       </c>
       <c r="AX27" t="n">
-        <v>28180230.6</v>
+        <v>29647816.6</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>32709006.3</t>
+          <t>31088710.7</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>203000139.16</v>
+        <v>187517443.84</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>-4528775</t>
+          <t>-1440894</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>-19086701.69794936</t>
+          <t>-18053080.27959415</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-13612713.56554211</t>
+          <t>-12368162.47864045</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>37113075.0</t>
+          <t>29976176.0</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="BM27" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN27" t="inlineStr">
@@ -11743,17 +11743,17 @@
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS27" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="BT27" t="inlineStr">
@@ -11783,12 +11783,12 @@
       </c>
       <c r="BY27" t="inlineStr">
         <is>
-          <t>79.72</t>
+          <t>80.08</t>
         </is>
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -11808,22 +11808,22 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>34.15</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>680.189</t>
+          <t>1072.806</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -11880,12 +11880,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-8.36</t>
+          <t>-6.74</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -11965,17 +11965,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -11986,66 +11986,66 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>34.57</t>
         </is>
       </c>
       <c r="AH28" t="n">
-        <v>-0.67</v>
+        <v>1.14</v>
       </c>
       <c r="AI28" t="n">
-        <v>-3.65</v>
+        <v>-3.05</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-7.85</t>
+          <t>-8.12</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>34.20999999999999</t>
         </is>
       </c>
       <c r="AM28" t="n">
-        <v>35.52</v>
+        <v>35.29</v>
       </c>
       <c r="AN28" t="n">
-        <v>38.55</v>
+        <v>38.41</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>37.82</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="AQ28" t="n">
-        <v>-1.14</v>
+        <v>-1.06</v>
       </c>
       <c r="AR28" t="n">
-        <v>-1.17</v>
+        <v>-1.15</v>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>-131.97</t>
+          <t>-131.38</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -12064,43 +12064,43 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>231115275.2069701</t>
+          <t>230884472.3927557</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>23145831.0</t>
+          <t>37113075.0</t>
         </is>
       </c>
       <c r="AX28" t="n">
-        <v>28055340.4</v>
+        <v>28180230.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>32565131.1</t>
+          <t>32709006.3</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>214383272.46</v>
+        <v>203000139.16</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>-4509790</t>
+          <t>-4528775</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>-20081972.26747796</t>
+          <t>-19086701.69794936</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-15669143.09806082</t>
+          <t>-13612713.56554211</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>23145831.0</t>
+          <t>37113075.0</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -12145,7 +12145,7 @@
       </c>
       <c r="BM28" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN28" t="inlineStr">
@@ -12165,17 +12165,17 @@
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS28" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BT28" t="inlineStr">
@@ -12205,12 +12205,12 @@
       </c>
       <c r="BY28" t="inlineStr">
         <is>
-          <t>79.72</t>
+          <t>80.08</t>
         </is>
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -12230,22 +12230,22 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>33.85</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>908.595</t>
+          <t>680.189</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -12302,17 +12302,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-13.85</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -12377,7 +12377,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-9.03</t>
+          <t>-8.36</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -12387,17 +12387,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -12408,63 +12408,63 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AH29" t="n">
-        <v>-1.98</v>
+        <v>-0.67</v>
       </c>
       <c r="AI29" t="n">
-        <v>-3.48</v>
+        <v>-3.65</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-7.85</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>35.67</v>
+        <v>35.52</v>
       </c>
       <c r="AN29" t="n">
-        <v>38.71</v>
+        <v>38.55</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>37.74</t>
+          <t>37.78</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AQ29" t="n">
-        <v>-1.17</v>
+        <v>-1.14</v>
       </c>
       <c r="AR29" t="n">
         <v>-1.17</v>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>-132.13</t>
+          <t>-131.97</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -12486,43 +12486,43 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>231115275.2069701</t>
+          <t>230884472.3927557</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>30779178.0</t>
+          <t>23145831.0</t>
         </is>
       </c>
       <c r="AX29" t="n">
-        <v>30495285.4</v>
+        <v>28055340.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>35145840.3</t>
+          <t>32565131.1</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>228943265.06</v>
+        <v>214383272.46</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>-4650554</t>
+          <t>-4509790</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>-20884304.84373562</t>
+          <t>-20081972.26747796</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>-16550796.89101397</t>
+          <t>-15669143.09806082</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>30779178.0</t>
+          <t>23145831.0</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -12567,7 +12567,7 @@
       </c>
       <c r="BM29" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN29" t="inlineStr">
@@ -12587,7 +12587,7 @@
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="BS29" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BT29" t="inlineStr">
@@ -12627,12 +12627,12 @@
       </c>
       <c r="BY29" t="inlineStr">
         <is>
-          <t>79.72</t>
+          <t>80.08</t>
         </is>
       </c>
       <c r="BZ29" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="CA29" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
@@ -12662,12 +12662,12 @@
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -12699,12 +12699,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>797.737</t>
+          <t>908.595</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -12724,17 +12724,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-24.16</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -12799,7 +12799,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-8.36</t>
+          <t>-9.03</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -12809,17 +12809,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -12830,59 +12830,59 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>60.49</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AH30" t="n">
-        <v>-1.56</v>
+        <v>-1.98</v>
       </c>
       <c r="AI30" t="n">
-        <v>-3.54</v>
+        <v>-3.48</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-7.74</t>
+          <t>-7.84</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>34.43</t>
         </is>
       </c>
       <c r="AM30" t="n">
-        <v>35.81</v>
+        <v>35.67</v>
       </c>
       <c r="AN30" t="n">
-        <v>38.81</v>
+        <v>38.71</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.74</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AQ30" t="n">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>-132.14</t>
+          <t>-132.13</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -12908,43 +12908,43 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>231115275.2069701</t>
+          <t>230884472.3927557</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>27224823.0</t>
+          <t>30779178.0</t>
         </is>
       </c>
       <c r="AX30" t="n">
-        <v>30219756.2</v>
+        <v>30495285.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>39847131.9</t>
+          <t>35145840.3</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>236001176.02</v>
+        <v>228943265.06</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>-9627375</t>
+          <t>-4650554</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>-21672215.3805941</t>
+          <t>-20884304.84373562</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>-18037061.02769653</t>
+          <t>-16550796.89101397</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>27224823.0</t>
+          <t>30779178.0</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="BM30" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN30" t="inlineStr">
@@ -13009,7 +13009,7 @@
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
@@ -13019,7 +13019,7 @@
       </c>
       <c r="BS30" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="BT30" t="inlineStr">
@@ -13049,12 +13049,12 @@
       </c>
       <c r="BY30" t="inlineStr">
         <is>
-          <t>79.72</t>
+          <t>80.08</t>
         </is>
       </c>
       <c r="BZ30" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="CA30" t="inlineStr">
@@ -13074,22 +13074,22 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -13121,12 +13121,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>652.267</t>
+          <t>797.737</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13136,7 +13136,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -13146,17 +13146,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-30.44</t>
+          <t>-24.16</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -13221,7 +13221,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-6.47</t>
+          <t>-8.36</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -13231,17 +13231,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -13252,66 +13252,66 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>60.49</t>
         </is>
       </c>
       <c r="AH31" t="n">
-        <v>0.67</v>
+        <v>-1.56</v>
       </c>
       <c r="AI31" t="n">
-        <v>-4.2</v>
+        <v>-3.54</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-7.74</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>34.47</t>
+          <t>34.54</t>
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>35.98</v>
+        <v>35.81</v>
       </c>
       <c r="AN31" t="n">
-        <v>38.91</v>
+        <v>38.81</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>37.67</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AQ31" t="n">
         <v>-1.17</v>
       </c>
       <c r="AR31" t="n">
-        <v>-1.18</v>
+        <v>-1.17</v>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>-132.19</t>
+          <t>-132.14</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -13330,43 +13330,43 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>231115275.2069701</t>
+          <t>230884472.3927557</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>22638246.0</t>
+          <t>27224823.0</t>
         </is>
       </c>
       <c r="AX31" t="n">
-        <v>32529604.8</v>
+        <v>30219756.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>46763411.2</t>
+          <t>39847131.9</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>241442940.72</v>
+        <v>236001176.02</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>-14233806</t>
+          <t>-9627375</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>-22333152.53566639</t>
+          <t>-21672215.3805941</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>-19135291.00768245</t>
+          <t>-18037061.02769653</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>22638246.0</t>
+          <t>27224823.0</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -13411,7 +13411,7 @@
       </c>
       <c r="BM31" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN31" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="BS31" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BT31" t="inlineStr">
@@ -13471,12 +13471,12 @@
       </c>
       <c r="BY31" t="inlineStr">
         <is>
-          <t>79.72</t>
+          <t>80.08</t>
         </is>
       </c>
       <c r="BZ31" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="CA31" t="inlineStr">
@@ -13501,17 +13501,17 @@
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -13533,7 +13533,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1052.554</t>
+          <t>652.267</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -13568,17 +13568,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-26.38</t>
+          <t>-30.44</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -13674,12 +13674,12 @@
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -13689,48 +13689,48 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>48.28</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AH32" t="n">
-        <v>0.9</v>
+        <v>0.67</v>
       </c>
       <c r="AI32" t="n">
-        <v>-4.68</v>
+        <v>-4.2</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>34.39</t>
+          <t>34.47</t>
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>36.08</v>
+        <v>35.98</v>
       </c>
       <c r="AN32" t="n">
-        <v>38.92</v>
+        <v>38.91</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>37.67</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AQ32" t="n">
-        <v>-1.22</v>
+        <v>-1.17</v>
       </c>
       <c r="AR32" t="n">
         <v>-1.18</v>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>-132.25</t>
+          <t>-132.19</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -13752,43 +13752,43 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>231115275.2069701</t>
+          <t>230884472.3927557</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>36488624.0</t>
+          <t>22638246.0</t>
         </is>
       </c>
       <c r="AX32" t="n">
-        <v>37237782</v>
+        <v>32529604.8</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>50581063.8</t>
+          <t>46763411.2</t>
         </is>
       </c>
       <c r="AZ32" t="n">
-        <v>242256442.44</v>
+        <v>241442940.72</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>-13343281</t>
+          <t>-14233806</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>-22914581.90439074</t>
+          <t>-22333152.53566639</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>-19529368.76453082</t>
+          <t>-19135291.00768245</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>36488624.0</t>
+          <t>22638246.0</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
@@ -13833,7 +13833,7 @@
       </c>
       <c r="BM32" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN32" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS32" t="inlineStr">
@@ -13893,12 +13893,12 @@
       </c>
       <c r="BY32" t="inlineStr">
         <is>
-          <t>79.72</t>
+          <t>80.08</t>
         </is>
       </c>
       <c r="BZ32" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="CA32" t="inlineStr">
@@ -13918,17 +13918,17 @@
       </c>
       <c r="CD32" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="CF32" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CG32" t="inlineStr">
@@ -13965,12 +13965,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1012.048</t>
+          <t>1052.554</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -13990,17 +13990,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-30.50</t>
+          <t>-26.38</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -14075,17 +14075,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -14096,66 +14096,66 @@
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>48.21</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>48.28</t>
         </is>
       </c>
       <c r="AH33" t="n">
-        <v>1.71</v>
+        <v>0.9</v>
       </c>
       <c r="AI33" t="n">
-        <v>-4.91</v>
+        <v>-4.68</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>34.41</t>
+          <t>34.39</t>
         </is>
       </c>
       <c r="AM33" t="n">
-        <v>36.18</v>
+        <v>36.08</v>
       </c>
       <c r="AN33" t="n">
-        <v>38.94</v>
+        <v>38.92</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>37.63</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AQ33" t="n">
-        <v>-1.28</v>
+        <v>-1.22</v>
       </c>
       <c r="AR33" t="n">
-        <v>-1.17</v>
+        <v>-1.18</v>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>-131.94</t>
+          <t>-132.25</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -14174,43 +14174,43 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>231115275.2069701</t>
+          <t>230884472.3927557</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>35345556.0</t>
+          <t>36488624.0</t>
         </is>
       </c>
       <c r="AX33" t="n">
-        <v>37074921.8</v>
+        <v>37237782</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>53345322.1</t>
+          <t>50581063.8</t>
         </is>
       </c>
       <c r="AZ33" t="n">
-        <v>245778298.12</v>
+        <v>242256442.44</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>-16270400</t>
+          <t>-13343281</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>-23530075.2025471</t>
+          <t>-22914581.90439074</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>-20878828.60415238</t>
+          <t>-19529368.76453082</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>35345556.0</t>
+          <t>36488624.0</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
@@ -14230,7 +14230,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -14255,7 +14255,7 @@
       </c>
       <c r="BM33" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN33" t="inlineStr">
@@ -14275,7 +14275,7 @@
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR33"